--- a/data/ships.xlsx
+++ b/data/ships.xlsx
@@ -3,10 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Read me" sheetId="1" r:id="rId1"/>
-    <sheet name="Hulls" sheetId="2" r:id="rId2"/>
-    <sheet name="Masts" sheetId="3" r:id="rId3"/>
-    <sheet name="Sails" sheetId="4" r:id="rId4"/>
-    <sheet name="Guns" sheetId="5" r:id="rId5"/>
+    <sheet name="Columns" sheetId="2" r:id="rId2"/>
+    <sheet name="Hulls" sheetId="3" r:id="rId3"/>
+    <sheet name="Masts" sheetId="4" r:id="rId4"/>
+    <sheet name="Sails" sheetId="5" r:id="rId5"/>
+    <sheet name="Guns" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -196,922 +197,1314 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Blank is not zero everywhere. On the hull sheet, speed, hand, canvas and tons left empty are</t>
+          <t xml:space="preserve">  A blank is a missing figure, not a sensible default. Left empty, a hull's speed, hand, canvas</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  worked out from the rest of the row; anywhere else a blank is a missing figure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Formulas are fine. What comes back into the table is the value a formula worked out, not the</t>
+          <t xml:space="preserve">  and tons each fall back to 1, which is right for no class above a boat, and every other</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  column but a blurb has to be filled.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  formula, so a column of prices scaled by a factor lands as prices.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Anything else Numbers can do is not read back: colours, comments, extra sheets, extra rows</t>
+          <t xml:space="preserve">  The Columns sheet is the legend: every column of every sheet, what it means, and whether the</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  fight reads it, the drawing reads it, or nothing reads it yet.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  below the table. Add a column and nothing will read it.</t>
+          <t xml:space="preserve">  Formulas are fine. What comes back into the table is the value a formula worked out, not the</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  formula, so a column of prices scaled by a factor lands as prices.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hulls, from data/hulls.tsv</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THE FLEET. One row per class, smallest to largest. Tab separated, so a blurb can hold commas and</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">apostrophes freely. Edit here (or in a spreadsheet, exported as TSV), then:</t>
+          <t xml:space="preserve">  Anything else Numbers can do is not read back: colours, comments, extra sheets, extra rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  below the table. Add a column and nothing will read it.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">    npm run import &amp;&amp; npm run catalogue</t>
+          <t xml:space="preserve">Hulls, from data/hulls.tsv</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lines starting with # are ignored, so notes and section breaks are fine.</t>
+          <t xml:space="preserve">THE FLEET. One row per class, smallest to largest. Tab separated, so a blurb can hold commas and</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">apostrophes freely. Edit here (or in a spreadsheet, exported as TSV), then:</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE GAMEPLAY COLUMNS. These are what the fight and the shipyard read.</t>
+          <t xml:space="preserve">    npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">id          a short camelCase name, unique. Becomes the key everything else refers to.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name        what a captain reads. Sentence case, no em dashes, no interpuncts.</t>
+          <t xml:space="preserve">Lines starting with # are ignored, so notes and section breaks are fine.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">price       coins to buy the bare hull. 0 for the ship she starts with.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hull, crew  maximum health in the same points the bars already use. Hull is the reference's own</t>
+          <t xml:space="preserve">THE GAMEPLAY COLUMNS. These are what the fight and the shipyard read.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">            timber formula; crew is her battle complement, floored at 25 because a crew bar is a</t>
+          <t xml:space="preserve">id          a short camelCase name, unique. Becomes the key everything else refers to.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">            health bar and a dozen points is four musket balls.</t>
+          <t xml:space="preserve">name        what a captain reads. Sentence case, no em dashes, no interpuncts.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">speed       her own pace before a stitch of canvas, off her working speed under sail.</t>
+          <t xml:space="preserve">price       coins to buy the bare hull. 0 for the ship she starts with.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">hand        how she answers her rudder, before canvas. From the reference's handling components</t>
+          <t xml:space="preserve">hull, crew  maximum health in the same points the bars already use. Hull is the reference's own</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">            less the rig and the crew: her sails carry the rig half themselves.</t>
+          <t xml:space="preserve">            timber formula; crew is her battle complement, floored at 25 because a crew bar is a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">canvas      how much sail she WANTS to get moving, as displacement to the two thirds. The most</t>
+          <t xml:space="preserve">            health bar and a dozen points is four musket balls.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">            important number here: it is why a half-rigged big ship is genuinely bad, and why the</t>
+          <t xml:space="preserve">speed       her own pace before a stitch of canvas, off her working speed under sail.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">            same suit drives a cutter hard.</t>
+          <t xml:space="preserve">hand        how she answers her rudder, before canvas. From the reference's handling components</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">tons        what she carries before her guns start telling on her handling. Set so a class with the</t>
+          <t xml:space="preserve">            less the rig and the crew: her sails carry the rig half themselves.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">            heaviest iron in every port sits at her limit, and moved by how fine she is: a beamy</t>
+          <t xml:space="preserve">canvas      how much sail she WANTS to get moving, as displacement to the two thirds. The most</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">            hull carries her guns better than a sharp one.</t>
+          <t xml:space="preserve">            important number here: it is why a half-rigged big ship is genuinely bad, and why the</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">broadside   guns A SIDE, mirrored. bow and swivel are totals.</t>
+          <t xml:space="preserve">            same suit drives a cutter hard.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">masts       where she can step one, "station/size", space separated, bow aft.</t>
+          <t xml:space="preserve">tons        what she carries before her guns start telling on her handling. Set so a class with the</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">            stations: bowsprit fore main mizzen bonaventure</t>
+          <t xml:space="preserve">            heaviest iron in every port sits at her limit, and moved by how fine she is: a beamy</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">            sizes:    boat small medium large heavy</t>
+          <t xml:space="preserve">            hull carries her guns better than a sharp one.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">            The bowsprit takes a SPAR rather than a mast, which is what her headsails hang on.</t>
+          <t xml:space="preserve">broadside   guns A SIDE, mirrored, because that is how a volley fires: one gun bought is one gun</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit    yes or no. Whether she carries the spar at all.</t>
+          <t xml:space="preserve">            each side and two aboard.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb       one line a captain reads. May be left empty.</t>
+          <t xml:space="preserve">bow         chasers on her bow. A total rather than a side, because she has only the one bow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">swivel      swivels on her rails, and a total as well. They fire in the volley with her muskets.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE REFERENCE COLUMNS. Everything from `era` rightward is what the class WAS rather than what she</t>
+          <t xml:space="preserve">masts       where she can step one, "station/size", space separated, bow aft.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">does in a fight: nothing reads it, `npm run import` writes it to src/shipref.js, and it is there</t>
+          <t xml:space="preserve">            stations: bowsprit fore main mizzen bonaventure</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">for whoever comes to model the hulls. Lengths are feet and weights are tons; bowFine, tumblehome,</t>
+          <t xml:space="preserve">            sizes:    boat small medium large heavy</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">deadrise, sheer and castle are 1 to 5 judgement scores, 1 for least and 5 for most.</t>
+          <t xml:space="preserve">            The bowsprit takes a SPAR rather than a mast, which is what her headsails hang on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowsprit    yes or no. Whether she carries the spar at all.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masts, from data/masts.tsv</t>
+          <t xml:space="preserve">blurb       one line a captain reads. May be left empty.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE MASTS. One row per type, and a type is a SHAPE OF RIG, not a size.</t>
+          <t xml:space="preserve">A BLANK IN speed, hand, canvas OR tons IS NOT A DERIVATION. Each falls back to 1, which describes</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A mast's berths are fixed the moment it is built and never change. That is the whole point of the</t>
+          <t xml:space="preserve">a quick, handy, easily driven ship that can carry nothing, and is right for no class above a boat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fill them in. Every other gameplay column has to be filled as well.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">part: buying a mast is choosing what she will be able to carry, so a mast with one lugsail berth</t>
+          <t xml:space="preserve">THE REFERENCE COLUMNS. Everything from `era` rightward is what the class WAS rather than what she</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">will never carry two square ones however much a captain spends. It is why the fleet wants a type</t>
+          <t xml:space="preserve">does in a fight: no fight reads any of it, `npm run import` writes it to src/shipref.js, and</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">per configuration rather than one mast with a number of slots.</t>
+          <t xml:space="preserve">`hullform.js` is the one reader. The thirteen marked (drawn) are how she is DRAWN, in the menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">model and at sea. The rest are recorded for whoever comes to refine her form and are read by</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">A TYPE IS NOT TIED TO A STATION. A mast that carries three square sails is that mast wherever she</t>
+          <t xml:space="preserve">nothing yet, which is not the same as being free to invent: a wrong figure here is a wrong hull</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">steps it, so the fore and main of a brig are one part bought twice rather than two parts. What</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">decides where it can go is the size rung and nothing else.</t>
+          <t xml:space="preserve">the day somebody does read it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lengths are feet and weights are tons. bowFine, tumblehome, deadrise, sheer and castle are 1 to 5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERTHS RUN DECK UPWARD, and a fore-and-aft driving sail sharing the lowest level with a course</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">takes berth 0 with the square canvas above it. A spanker and a course are both set at the deck, one</t>
+          <t xml:space="preserve">judgement scores, 1 for least and 5 for most.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">abaft the mast and one on a yard across it, and the model has one sail to a band: putting the</t>
+          <t xml:space="preserve">era         the years she was in service, written as a range. Text rather than a number.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">spanker lowest is what keeps a brig's rig reading bottom to top the way she is really rigged.</t>
+          <t xml:space="preserve">region      where she was built and sailed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">role        what she was for.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">id       short camelCase name, unique.</t>
+          <t xml:space="preserve">lod         (drawn) length on deck, feet. With beam, how big she is drawn in both views. Sizes are</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">name     what a captain reads.</t>
+          <t xml:space="preserve">            compressed around the galleon, so twice the length is not twice the ship on screen.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">price    coins.</t>
+          <t xml:space="preserve">lbp         length between perpendiculars, feet. The measured length, shorter than on deck.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">size     the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor</t>
+          <t xml:space="preserve">beam        (drawn) extreme breadth, feet. Her drawn width, and with her length her collision</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">         choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
+          <t xml:space="preserve">            ellipse in a fight.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">spar     yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the</t>
+          <t xml:space="preserve">draft       how deep she floats, feet.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">         bowsprit and nowhere else. A spar and a mast are different sorts of thing and are</t>
+          <t xml:space="preserve">depth       depth of hold, feet: keelson to the deck above it.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">         matched as such, or a jibboom would be legal as somebody's main mast.</t>
+          <t xml:space="preserve">freeboard   (drawn) height of side above the water amidships, feet. The depth of side in the model.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">height   how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts</t>
+          <t xml:space="preserve">lb          length to beam, as a ratio. High is long and lean, low is short and beamy.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">         the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
+          <t xml:space="preserve">bd          beam to depth, as a ratio. High is shallow and beamy, low is deep and narrow.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">berths   the sails she can carry, DECK UPWARD, as category labels separated by spaces.</t>
+          <t xml:space="preserve">burthen     builder's old measurement tons: what she was rated to carry.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">         LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail</t>
+          <t xml:space="preserve">disp        displacement, tons: what she actually weighs afloat.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Five is the most the renderer can place up one mast in bands of their own, and the bench</t>
+          <t xml:space="preserve">bowFine     (drawn) how fine her entry is. 5 is a clipper's bow and 1 a carrack's. It narrows her</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">         fails a mast that asks for more.</t>
+          <t xml:space="preserve">            bow and pulls her shoulders aft.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">         STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set,</t>
+          <t xml:space="preserve">tumblehome  (drawn) how far her sides roll inward above the waterline. 5 is a fluyt.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">         so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
+          <t xml:space="preserve">deadrise    how sharply her bottom rises from the keel. 1 is a flat floor.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb    one line a captain reads.</t>
+          <t xml:space="preserve">sheer       (drawn) how much her deck sweeps up towards bow and stern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">castle      (drawn) how built up her ends are. 1 is an open boat, 2 raises a quarterdeck, 3 and up</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sails, from data/sails.tsv</t>
+          <t xml:space="preserve">            add a forecastle. It is also what a windowed stern needs before it shows any lights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stern       (drawn) the shape of her stern, as one of the named types. Scow, Round, Pear,</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE SAILS. One row per sail a captain can buy.</t>
+          <t xml:space="preserve">            Elliptical, Raking transom, Overhanging and Square each have geometry of their own,</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+          <t xml:space="preserve">            and any other name draws a plain transom, which is what Transom and Gallery do. A name</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            holding "gallery" or "castle" lights her stern windows if her castle is 3 or more.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">A sail belongs to ONE category and fits a berth of that category. That is the whole fitting rule.</t>
+          <t xml:space="preserve">mastHeight  (drawn) how tall her rig stands, as a multiple of the galleon's. Scales her masts in</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Area is not the category: a topgallant is nearly four times a skysail and both are SSQ.</t>
+          <t xml:space="preserve">            both views.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decks       (drawn) how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LSQ  Large square    courses, lower topsails            driving power, low on the mast</t>
+          <t xml:space="preserve">            not a number. A 3 or a 2-3 with four ports a side or more draws two tiers of them.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SSQ  Small square    topgallants, royals, skysails,     light-air lift, high up</t>
+          <t xml:space="preserve">wale        the thickness of her main wale, inches: the heavy belt of timber along her side.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       spritsails, sprit-topsails</t>
+          <t xml:space="preserve">topside     the thickness of her topside planking, inches.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TRI  Headsail        jibs, flying jibs, staysails       set on a stay forward: balance, pointing</t>
+          <t xml:space="preserve">roomSpace   room and space, feet: from one frame to the next.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LAT  Lateen          lateen yards, Bermuda mainsails    triangular canvas driving from a mast</t>
+          <t xml:space="preserve">species     (drawn) what she was built of, which is also her colour: Oak, Live oak, Teak, Cedar or</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">  GAF  Gaff            gaff mainsails, spankers,          fore-and-aft drive aft, manoeuvre</t>
+          <t xml:space="preserve">            Pine. Any other name is painted as oak.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       drivers, trysails, gaff topsails</t>
+          <t xml:space="preserve">timber      (drawn) how dense that timber is, oak being 1. Denser timber reads a little darker.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LUG  Lugsail         dipping and standing lug,          the main drive of a lugger</t>
+          <t xml:space="preserve">crewMin     the fewest hands she could be worked with, as against the battle complement in `crew`.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       lug topsail</t>
+          <t xml:space="preserve">cruise      her everyday speed, knots.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STU  Studdingsail    boomed-out extensions             ADDITIVE. Not a berth: see below.</t>
+          <t xml:space="preserve">topSpeed    the best she was ever driven, knots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manoeuvre   how handy she was, 0 to 100. The reference's own score, and what `hand` came out of.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">A LATEEN IS NOT A HEADSAIL. Both are triangles and they were one category until the bowsprit became</t>
+          <t xml:space="preserve">histGuns    (drawn) how many guns she really carried, of every sort. She shows one gunport a side</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">a station: the moment a jib had a berth of its own a lateen fitted it and pulled better, so the</t>
+          <t xml:space="preserve">            per dozen of them, up to seven. It is not the game's armament: that is the three</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice made itself. They do different work, so they are different categories.</t>
+          <t xml:space="preserve">            bearing columns above, and they are deliberately smaller.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU does not go in a berth. A studdingsail booms out beyond a square sail that is already set and</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its area comes off that sail, so it is an attachment rather than a place in the rig: a square sail</t>
+          <t xml:space="preserve">Masts, from data/masts.tsv</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">carries at most one, matched by LEVEL, and `npm run catalogue` still refuses a berth that asks for</t>
+          <t xml:space="preserve">THE MASTS. One row per type, and a type is a SHAPE OF RIG, not a size.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">one, deliberately, so that a mast cannot pretend to carry studdingsails in a slot.</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">id      short camelCase name, unique.</t>
+          <t xml:space="preserve">A mast's berths are fixed the moment it is built and never change. That is the whole point of the</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">name    what a captain reads.</t>
+          <t xml:space="preserve">part: buying a mast is choosing what she will be able to carry, so a mast with one lugsail berth</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind    one of the seven labels above.</t>
+          <t xml:space="preserve">will never carry two square ones however much a captain spends. It is why the fleet wants a type</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">price   coins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">drive   what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area</t>
+          <t xml:space="preserve">per configuration rather than one mast with a number of slots.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">        is where this number starts and the proportions are: course 1.00, lower topsail 0.70,</t>
+          <t xml:space="preserve">A TYPE IS NOT TIED TO A STATION. A mast that carries three square sails is that mast wherever she</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">        topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it,</t>
+          <t xml:space="preserve">steps it, so the fore and main of a brig are one part bought twice rather than two parts. What</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">        which is why two sails of one area can differ here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80),</t>
+          <t xml:space="preserve">decides where it can go is the size rung and nothing else.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">        because its area comes off that sail rather than off a place in the rig.</t>
+          <t xml:space="preserve">BERTHS RUN DECK UPWARD, and a fore-and-aft driving sail sharing the lowest level with a course</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">hand    what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft</t>
+          <t xml:space="preserve">takes berth 0 with the square canvas above it. A spanker and a course are both set at the deck, one</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">        canvas helps her round, so it is positive.</t>
+          <t xml:space="preserve">abaft the mast and one on a yard across it, and the model has one sail to a band: putting the</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">level   STU only, and blank everywhere else. Which square sail up the mast it booms out from,</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it;</t>
+          <t xml:space="preserve">spanker lowest is what keeps a brig's rig reading bottom to top the way she is really rigged.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2 the topgallant. The berth number is not the level, because a driver mast's course sits</t>
+          <t xml:space="preserve">id       short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">        at berth 1 with a spanker under it.</t>
+          <t xml:space="preserve">name     what a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb   one line a captain reads.</t>
+          <t xml:space="preserve">price    coins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">size     the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two grades of most of them: the plain one a captain can afford early, and a fine one in heavier</t>
+          <t xml:space="preserve">         choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">cloth that is strictly better and priced for it. Prices are placed against each other and have not</t>
+          <t xml:space="preserve">spar     yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">been tuned against what a voyage actually pays.</t>
+          <t xml:space="preserve">         bowsprit and nowhere else. A spar and a mast are different sorts of thing and are</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         matched as such, or a jibboom would be legal as somebody's main mast.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guns, from data/guns.tsv</t>
+          <t xml:space="preserve">height   how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE GUNS. One row per piece a captain can buy.</t>
+          <t xml:space="preserve">berths   the sails she can carry, DECK UPWARD, as category labels separated by spaces.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+          <t xml:space="preserve">         LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         Five is the most the renderer can place up one mast in bands of their own, and the bench</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guns fit BY THE PIECE up to what the hull bears, and `mount` says which of her counts a gun draws</t>
+          <t xml:space="preserve">         fails a mast that asks for more.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">against. Broadside is counted A SIDE and mirrored, because that is how a volley fires: one</t>
+          <t xml:space="preserve">         STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set,</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">carriage gun bought is one gun each side and two guns aboard.</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Muskets are not in this table and never will be. Small arms come off the crew she musters, with the</t>
+          <t xml:space="preserve">         so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blurb    one line a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">swivels on her rail firing in the same volley, which is `rate()`'s business.</t>
+          <t xml:space="preserve">Sails, from data/sails.tsv</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">id      short camelCase name, unique.</t>
+          <t xml:space="preserve">THE SAILS. One row per sail a captain can buy.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">name    what a captain reads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">price   coins.</t>
+          <t xml:space="preserve">A sail belongs to ONE category and fits a berth of that category. That is the whole fitting rule.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
+          <t xml:space="preserve">Area is not the category: a topgallant is nearly four times a skysail and both are SSQ.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
+          <t xml:space="preserve">  LSQ  Large square    courses, lower topsails            driving power, low on the mast</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">        to leave a port empty.</t>
+          <t xml:space="preserve">  SSQ  Small square    topgallants, royals, skysails,     light-air lift, high up</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
+          <t xml:space="preserve">                       spritsails, sprit-topsails</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
+          <t xml:space="preserve">  TRI  Headsail        jibs, flying jibs, staysails       set on a stay forward: balance, pointing</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+          <t xml:space="preserve">  LAT  Lateen          lateen yards, Bermuda mainsails    triangular canvas driving from a mast</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+          <t xml:space="preserve">  GAF  Gaff            gaff mainsails, spankers,          fore-and-aft drive aft, manoeuvre</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                       drivers, trysails, gaff topsails</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LUG  Lugsail         dipping and standing lug,          the main drive of a lugger</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                       lug topsail</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STU  Studdingsail    boomed-out extensions             ADDITIVE. Not a berth: see below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A LATEEN IS NOT A HEADSAIL. Both are triangles and they were one category until the bowsprit became</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a station: the moment a jib had a berth of its own a lateen fitted it and pulled better, so the</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">choice made itself. They do different work, so they are different categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STU does not go in a berth. A studdingsail booms out beyond a square sail that is already set and</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its area comes off that sail, so it is an attachment rather than a place in the rig: a square sail</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carries at most one, matched by LEVEL, and `npm run catalogue` still refuses a berth that asks for</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one, deliberately, so that a mast cannot pretend to carry studdingsails in a slot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id      short camelCase name, unique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name    what a captain reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind    one of the seven labels above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price   coins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">drive   what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        is where this number starts and the proportions are: course 1.00, lower topsail 0.70,</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it,</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        which is why two sails of one area can differ here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80),</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        because its area comes off that sail rather than off a place in the rig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hand    what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        canvas helps her round, so it is positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">level   STU only, and blank everywhere else. Which square sail up the mast it booms out from,</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it;</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        2 the topgallant. The berth number is not the level, because a driver mast's course sits</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        at berth 1 with a spanker under it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blurb   one line a captain reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two grades of most of them: the plain one a captain can afford early, and a fine one in heavier</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cloth that is strictly better and priced for it. Prices are placed against each other and have not</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">been tuned against what a voyage actually pays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns, from data/guns.tsv</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THE GUNS. One row per piece a captain can buy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns fit BY THE PIECE up to what the hull bears, and `mount` says which of her counts a gun draws</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">against. Broadside is counted A SIDE and mirrored, because that is how a volley fires: one</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carriage gun bought is one gun each side and two guns aboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Muskets are not in this table and never will be. Small arms come off the crew she musters, with the</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">swivels on her rail firing in the same volley, which is `rate()`'s business.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id      short camelCase name, unique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name    what a captain reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price   coins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        to leave a port empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
         <is>
           <t xml:space="preserve">blurb   one line a captain reads.</t>
         </is>
@@ -1122,6 +1515,1603 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="9.00" customWidth="1"/>
+    <col min="2" max="2" width="13.00" customWidth="1"/>
+    <col min="3" max="3" width="15.00" customWidth="1"/>
+    <col min="4" max="4" width="100.00" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Column</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read by</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What it is</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a short camelCase name, unique. Becomes the key everything else refers to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what a captain reads. Sentence case, no em dashes, no interpuncts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coins to buy the bare hull. 0 for the ship she starts with.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hull</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maximum health in the same points the bars already use. Hull is the reference's own timber formula; crew is her battle complement, floored at 25 because a crew bar is a health bar and a dozen points is four musket balls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crew</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maximum health in the same points the bars already use. Hull is the reference's own timber formula; crew is her battle complement, floored at 25 because a crew bar is a health bar and a dozen points is four musket balls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">speed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">her own pace before a stitch of canvas, off her working speed under sail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hand</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">how she answers her rudder, before canvas. From the reference's handling components less the rig and the crew: her sails carry the rig half themselves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">canvas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">how much sail she WANTS to get moving, as displacement to the two thirds. The most important number here: it is why a half-rigged big ship is genuinely bad, and why the same suit drives a cutter hard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tons</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what she carries before her guns start telling on her handling. Set so a class with the heaviest iron in every port sits at her limit, and moved by how fine she is: a beamy hull carries her guns better than a sharp one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">broadside</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guns A SIDE, mirrored, because that is how a volley fires: one gun bought is one gun each side and two aboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bow</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chasers on her bow. A total rather than a side, because she has only the one bow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">swivel</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">swivels on her rails, and a total as well. They fire in the volley with her muskets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">masts</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">where she can step one, "station/size", space separated, bow aft. stations: bowsprit fore main mizzen bonaventure sizes:    boat small medium large heavy The bowsprit takes a SPAR rather than a mast, which is what her headsails hang on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowsprit</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes or no. Whether she carries the spar at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blurb</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one line a captain reads. May be left empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">era</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the years she was in service, written as a range. Text rather than a number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">region</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">where she was built and sailed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">role</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what she was for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lod</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Her drawing</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">length on deck, feet. With beam, how big she is drawn in both views. Sizes are compressed around the galleon, so twice the length is not twice the ship on screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lbp</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">length between perpendiculars, feet. The measured length, shorter than on deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beam</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Her drawing</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">extreme breadth, feet. Her drawn width, and with her length her collision ellipse in a fight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">draft</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">how deep she floats, feet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">depth</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">depth of hold, feet: keelson to the deck above it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freeboard</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Her drawing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">height of side above the water amidships, feet. The depth of side in the model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lb</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">length to beam, as a ratio. High is long and lean, low is short and beamy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bd</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beam to depth, as a ratio. High is shallow and beamy, low is deep and narrow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burthen</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">builder's old measurement tons: what she was rated to carry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">disp</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displacement, tons: what she actually weighs afloat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowFine</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Her drawing</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">how fine her entry is. 5 is a clipper's bow and 1 a carrack's. It narrows her bow and pulls her shoulders aft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tumblehome</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Her drawing</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">how far her sides roll inward above the waterline. 5 is a fluyt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deadrise</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">how sharply her bottom rises from the keel. 1 is a flat floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sheer</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Her drawing</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">how much her deck sweeps up towards bow and stern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">castle</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Her drawing</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">how built up her ends are. 1 is an open boat, 2 raises a quarterdeck, 3 and up add a forecastle. It is also what a windowed stern needs before it shows any lights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stern</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Her drawing</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the shape of her stern, as one of the named types. Scow, Round, Pear, Elliptical, Raking transom, Overhanging and Square each have geometry of their own, and any other name draws a plain transom, which is what Transom and Gallery do. A name holding "gallery" or "castle" lights her stern windows if her castle is 3 or more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mastHeight</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Her drawing</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">how tall her rig stands, as a multiple of the galleon's. Scales her masts in both views.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decks</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Her drawing</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is not a number. A 3 or a 2-3 with four ports a side or more draws two tiers of them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wale</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the thickness of her main wale, inches: the heavy belt of timber along her side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">topside</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the thickness of her topside planking, inches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roomSpace</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">room and space, feet: from one frame to the next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">species</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Her drawing</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what she was built of, which is also her colour: Oak, Live oak, Teak, Cedar or Pine. Any other name is painted as oak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timber</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Her drawing</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">how dense that timber is, oak being 1. Denser timber reads a little darker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crewMin</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the fewest hands she could be worked with, as against the battle complement in `crew`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cruise</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">her everyday speed, knots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">topSpeed</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the best she was ever driven, knots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manoeuvre</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded only</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">how handy she was, 0 to 100. The reference's own score, and what `hand` came out of.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hulls</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">histGuns</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Her drawing</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">how many guns she really carried, of every sort. She shows one gunport a side per dozen of them, up to seven. It is not the game's armament: that is the three bearing columns above, and they are deliberately smaller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Masts</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">short camelCase name, unique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Masts</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what a captain reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Masts</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Masts</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">size</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Masts</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spar</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the bowsprit and nowhere else. A spar and a mast are different sorts of thing and are matched as such, or a jibboom would be legal as somebody's main mast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Masts</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">height</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Masts</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">berths</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the sails she can carry, DECK UPWARD, as category labels separated by spaces. LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail Five is the most the renderer can place up one mast in bands of their own, and the bench fails a mast that asks for more. STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set, so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Masts</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blurb</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one line a captain reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sails</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">short camelCase name, unique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sails</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what a captain reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sails</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of the seven labels above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sails</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sails</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">drive</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area is where this number starts and the proportions are: course 1.00, lower topsail 0.70, topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it, which is why two sails of one area can differ here. FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80), because its area comes off that sail rather than off a place in the rig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sails</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hand</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft canvas helps her round, so it is positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sails</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">level</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STU only, and blank everywhere else. Which square sail up the mast it booms out from, counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it; 2 the topgallant. The berth number is not the level, because a driver mast's course sits at berth 1 with a spanker under it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sails</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blurb</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one line a captain reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">short camelCase name, unique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what a captain reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mount</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">broadside, bow or swivel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damage</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what one ball takes off a hull.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reload</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weight</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what she carries for it. Enough of it takes the edge off her handling, which is the reason to leave a port empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">group</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">swivels only, and blank everywhere else. How true one throws, as a share of a musket's own scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel never adds a ball to the volley; what quality buys is that the volley hits harder and lands closer to where the bow points, and this is the second half of that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blurb</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one line a captain reads.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="18.00" customWidth="1"/>
@@ -7306,7 +9296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="18.00" customWidth="1"/>
@@ -8239,7 +10229,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="20.00" customWidth="1"/>
@@ -9516,7 +11506,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="14.00" customWidth="1"/>

--- a/data/ships.xlsx
+++ b/data/ships.xlsx
@@ -1499,82 +1499,103 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">name    what a captain reads.</t>
+          <t xml:space="preserve">name    what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`,</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
+          <t xml:space="preserve">        not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">price   coins.</t>
+          <t xml:space="preserve">        them is arithmetic she should not have to do in words. It is the game's own rule about</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
+          <t xml:space="preserve">        numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
+          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
+          <t xml:space="preserve">price   coins.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t xml:space="preserve">        to leave a port empty.</t>
+          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
+          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
+          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+          <t xml:space="preserve">        to leave a port empty.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
         <is>
           <t xml:space="preserve">blurb   one line a captain reads.</t>
         </is>
@@ -3041,7 +3062,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">what a captain reads.</t>
+          <t xml:space="preserve">what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`, not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing them is arithmetic she should not have to do in words. It is the game's own rule about numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14396,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="14.00" customWidth="1"/>
-    <col min="2" max="2" width="25.00" customWidth="1"/>
+    <col min="2" max="2" width="23.00" customWidth="1"/>
     <col min="3" max="3" width="11.00" customWidth="1"/>
     <col min="4" max="4" width="7.00" customWidth="1"/>
     <col min="5" max="5" width="8.00" customWidth="1"/>
@@ -14440,7 +14461,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Three pounder</t>
+          <t xml:space="preserve">3-pounder</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -14474,7 +14495,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four pounder</t>
+          <t xml:space="preserve">4-pounder</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -14508,7 +14529,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Six pounder</t>
+          <t xml:space="preserve">6-pounder</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -14542,7 +14563,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eight pounder</t>
+          <t xml:space="preserve">8-pounder</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -14576,7 +14597,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Long nine</t>
+          <t xml:space="preserve">Long 9-pounder</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -14610,7 +14631,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Twelve pounder</t>
+          <t xml:space="preserve">12-pounder</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14644,7 +14665,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eighteen pounder</t>
+          <t xml:space="preserve">18-pounder</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14678,7 +14699,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Twenty four pounder</t>
+          <t xml:space="preserve">24-pounder</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14712,7 +14733,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thirty two pounder</t>
+          <t xml:space="preserve">32-pounder</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -14746,7 +14767,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thirty six pounder</t>
+          <t xml:space="preserve">36-pounder</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -14780,7 +14801,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Six pounder chaser</t>
+          <t xml:space="preserve">6-pounder chaser</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -14814,7 +14835,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eight pounder chaser</t>
+          <t xml:space="preserve">8-pounder chaser</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -14848,7 +14869,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Long nine chaser</t>
+          <t xml:space="preserve">Long 9-pounder chaser</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -14882,7 +14903,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Twelve pounder chaser</t>
+          <t xml:space="preserve">12-pounder chaser</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -14916,7 +14937,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eighteen pounder chaser</t>
+          <t xml:space="preserve">18-pounder chaser</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/data/ships.xlsx
+++ b/data/ships.xlsx
@@ -141,1461 +141,1489 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Each row's id is its key. Adding a row adds a ship or a part; deleting a row removes it.</t>
+          <t xml:space="preserve">  Each row's id is its key. Adding a row adds a ship or a part; deleting the row removes it.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  An id is a short camelCase word, unique in its sheet, and it must be a plain word: letters</t>
+          <t xml:space="preserve">  A row left blank is left blank: space between two groups of ships survives coming back.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t xml:space="preserve">  An id is a short camelCase word, unique in its sheet, and it must be a plain word: letters</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t xml:space="preserve">  and digits, no spaces or punctuation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Changing an id is the same as deleting one ship and adding another. Any saved captain who</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Changing an id is the same as deleting one ship and adding another. Any saved captain who</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t xml:space="preserve">  owned the old one loses her, so rename in the name column and leave the id alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A ship's tier is measured, never declared. Nothing here sets how strong a class is directly:</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  it comes out of her figures, so a class you make faster and better armed climbs the ladder</t>
+          <t xml:space="preserve">  A ship's tier is measured, never declared. Nothing here sets how strong a class is directly:</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t xml:space="preserve">  it comes out of her figures, so a class you make faster and better armed climbs the ladder</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t xml:space="preserve">  by herself and starts meeting harder opponents.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A blank is a missing figure, not a sensible default. Left empty, a hull's speed, hand, canvas</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  and tons each fall back to 1, which is right for no class above a boat, and every other</t>
+          <t xml:space="preserve">  A blank is a missing figure, not a sensible default. Left empty, a hull's speed, hand, canvas</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t xml:space="preserve">  and tons each fall back to 1, which is right for no class above a boat, and every other</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t xml:space="preserve">  column but a blurb has to be filled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  The Columns sheet is the legend: every column of every sheet, what it means, and whether the</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t xml:space="preserve">  The Columns sheet is the legend: every column of every sheet, what it means, and whether the</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t xml:space="preserve">  fight reads it, the drawing reads it, or nothing reads it yet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Formulas are fine. What comes back into the table is the value a formula worked out, not the</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Formulas are fine. What comes back into the table is the value a formula worked out, not the</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t xml:space="preserve">  formula, so a column of prices scaled by a factor lands as prices.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Anything else Numbers can do is not read back: colours, comments, extra sheets, extra rows</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Anything else Numbers can do is not read back: colours, comments, extra sheets, extra rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t xml:space="preserve">  below the table. Add a column and nothing will read it.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t xml:space="preserve">Hulls, from data/hulls.tsv</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THE FLEET. One row per class, smallest to largest. Tab separated, so a blurb can hold commas and</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">apostrophes freely. Edit here (or in a spreadsheet, exported as TSV), then:</t>
+          <t xml:space="preserve">THE FLEET. One row per class, smallest to largest. Tab separated, so a blurb can hold commas and</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t xml:space="preserve">apostrophes freely. Edit here (or in a spreadsheet, exported as TSV), then:</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t xml:space="preserve">    npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t xml:space="preserve">Lines starting with # are ignored, so notes and section breaks are fine.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t xml:space="preserve">THE GAMEPLAY COLUMNS. These are what the fight and the shipyard read.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">active      yes if she is in the game. Anything else, blank included, lays her up: her row stays</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">            here with her figures as they stood and she comes back the day the column says yes.</t>
+          <t xml:space="preserve">active      yes if she is in the game. Anything else, blank included, lays her up: her row stays</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">            So the table is the fleet's whole history and the game is the part of it at sea, and a</t>
+          <t xml:space="preserve">            here with her figures as they stood and she comes back the day the column says yes.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">            class rebuilt keeps her old row beside her new one. That is why two rows may share an</t>
+          <t xml:space="preserve">            So the table is the fleet's whole history and the game is the part of it at sea, and a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">            id, as long as only one of them sails.</t>
+          <t xml:space="preserve">            class rebuilt keeps her old row beside her new one. That is why two rows may share an</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">id          a short camelCase name, unique among the ships that sail. Becomes the key everything</t>
+          <t xml:space="preserve">            id, as long as only one of them sails.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">            else refers to, so renaming one is retiring a ship and commissioning another.</t>
+          <t xml:space="preserve">id          a short camelCase name, unique among the ships that sail. Becomes the key everything</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">name        what a captain reads. No em dashes, no interpuncts. The fleet's own names are written</t>
+          <t xml:space="preserve">            else refers to, so renaming one is retiring a ship and commissioning another.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">            as the captain who drew up the table wrote them, capitals and all, which is why the</t>
+          <t xml:space="preserve">name        what a captain reads. No em dashes, no interpuncts. The fleet's own names are written</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">            sentence-case rule that governs the rest of the game's copy stops at this column.</t>
+          <t xml:space="preserve">            as the captain who drew up the table wrote them, capitals and all, which is why the</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">price       coins to buy the bare hull. 0 for the ship she starts with.</t>
+          <t xml:space="preserve">            sentence-case rule that governs the rest of the game's copy stops at this column.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">hull, crew  maximum health in the same points the bars already use. Hull is the reference's own</t>
+          <t xml:space="preserve">price       coins to buy the bare hull. 0 for the ship she starts with.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">            timber formula; crew is her battle complement, floored at 25 because a crew bar is a</t>
+          <t xml:space="preserve">hull, crew  maximum health in the same points the bars already use. Hull is the reference's own</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">            health bar and a dozen points is four musket balls.</t>
+          <t xml:space="preserve">            timber formula; crew is her battle complement, floored at 25 because a crew bar is a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">speed       her own pace before a stitch of canvas, off her working speed under sail.</t>
+          <t xml:space="preserve">            health bar and a dozen points is four musket balls.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">hand        how she answers her rudder, before canvas. From the reference's handling components</t>
+          <t xml:space="preserve">speed       her own pace before a stitch of canvas, off her working speed under sail.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">            less the rig and the crew: her sails carry the rig half themselves.</t>
+          <t xml:space="preserve">hand        how she answers her rudder, before canvas. From the reference's handling components</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">canvas      how much sail she WANTS to get moving, as displacement to the two thirds. The most</t>
+          <t xml:space="preserve">            less the rig and the crew: her sails carry the rig half themselves.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">            important number here: it is why a half-rigged big ship is genuinely bad, and why the</t>
+          <t xml:space="preserve">canvas      how much sail she WANTS to get moving, as displacement to the two thirds. The most</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">            same suit drives a cutter hard.</t>
+          <t xml:space="preserve">            important number here: it is why a half-rigged big ship is genuinely bad, and why the</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">tons        the weight of iron she can bear, in the same tons her guns are weighed in: a full</t>
+          <t xml:space="preserve">            same suit drives a cutter hard.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">            battery of the gun she was built around, both sides, plus her chasers and her rail.</t>
+          <t xml:space="preserve">tons        the weight of iron she can bear, in the same tons her guns are weighed in: a full</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">            It is a real limit rather than a penalty. The shipyard steps her battery down a grade</t>
+          <t xml:space="preserve">            battery of the gun she was built around, both sides, plus her chasers and her rail.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">            at a time until it fits under this, so a raft cannot mount thirty-six pounders, and</t>
+          <t xml:space="preserve">            It is a real limit rather than a penalty. The shipyard steps her battery down a grade</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">            what she does carry costs her in handling in proportion to how close to it she is.</t>
+          <t xml:space="preserve">            at a time until it fits under this, so a raft cannot mount thirty-six pounders, and</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">broadside   guns A SIDE, mirrored, because that is how a volley fires: one gun bought is one gun</t>
+          <t xml:space="preserve">            what she does carry costs her in handling in proportion to how close to it she is.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">            each side and two aboard.</t>
+          <t xml:space="preserve">broadside   guns A SIDE, mirrored, because that is how a volley fires: one gun bought is one gun</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">bow         chasers on her bow. A total rather than a side, because she has only the one bow.</t>
+          <t xml:space="preserve">            each side and two aboard.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">swivel      swivels on her rails, and a total as well. They fire in the volley with her muskets.</t>
+          <t xml:space="preserve">bow         chasers on her bow. A total rather than a side, because she has only the one bow.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">masts       where she can step one, "station/size", space separated, bow aft.</t>
+          <t xml:space="preserve">swivel      swivels on her rails, and a total as well. They fire in the volley with her muskets.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">            stations: bowsprit fore main mizzen bonaventure</t>
+          <t xml:space="preserve">masts       where she can step one, "station/size", space separated, bow aft.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">            sizes:    boat small medium large heavy</t>
+          <t xml:space="preserve">            stations: bowsprit fore main mizzen bonaventure</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">            The bowsprit takes a SPAR rather than a mast, which is what her headsails hang on.</t>
+          <t xml:space="preserve">            sizes:    boat small medium large heavy</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit    yes or no. Whether she carries the spar at all.</t>
+          <t xml:space="preserve">            The bowsprit takes a SPAR rather than a mast, which is what her headsails hang on.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t xml:space="preserve">bowsprit    yes or no. Whether she carries the spar at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t xml:space="preserve">blurb       one line a captain reads. May be left empty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A BLANK IN speed, hand, canvas OR tons IS NOT A DERIVATION. Each falls back to 1, which describes</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">a quick, handy, easily driven ship that can carry nothing, and is right for no class above a boat.</t>
+          <t xml:space="preserve">A BLANK IN speed, hand, canvas OR tons IS NOT A DERIVATION. Each falls back to 1, which describes</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t xml:space="preserve">a quick, handy, easily driven ship that can carry nothing, and is right for no class above a boat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t xml:space="preserve">Fill them in. Every other gameplay column has to be filled as well.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THE REFERENCE COLUMNS. Everything from `era` rightward is what the class WAS rather than what she</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">does in a fight: no fight reads any of it, `npm run import` writes it to src/shipref.js, and</t>
+          <t xml:space="preserve">THE REFERENCE COLUMNS. Everything from `era` rightward is what the class WAS rather than what she</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">`hullform.js` is the one reader. The thirteen marked (drawn) are how she is DRAWN, in the menu</t>
+          <t xml:space="preserve">does in a fight: no fight reads any of it, `npm run import` writes it to src/shipref.js, and</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">model and at sea. The rest are recorded for whoever comes to refine her form and are read by</t>
+          <t xml:space="preserve">`hullform.js` is the one reader. The thirteen marked (drawn) are how she is DRAWN, in the menu</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">nothing yet, which is not the same as being free to invent: a wrong figure here is a wrong hull</t>
+          <t xml:space="preserve">model and at sea. The rest are recorded for whoever comes to refine her form and are read by</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t xml:space="preserve">nothing yet, which is not the same as being free to invent: a wrong figure here is a wrong hull</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t xml:space="preserve">the day somebody does read it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lengths are feet and weights are tons. bowFine, tumblehome, deadrise, sheer and castle are 1 to 5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lengths are feet and weights are tons. bowFine, tumblehome, deadrise, sheer and castle are 1 to 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t xml:space="preserve">judgement scores, 1 for least and 5 for most.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">era         the years she was in service, written as a range. Text rather than a number.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">region      where she was built and sailed.</t>
+          <t xml:space="preserve">era         the years she was in service, written as a range. Text rather than a number.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">role        what she was for.</t>
+          <t xml:space="preserve">region      where she was built and sailed.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">lod         (drawn) length on deck, feet. With beam, how big she is drawn in both views. Sizes are</t>
+          <t xml:space="preserve">role        what she was for.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">            compressed around the galleon, so twice the length is not twice the ship on screen.</t>
+          <t xml:space="preserve">lod         (drawn) length on deck, feet. With beam, how big she is drawn in both views. Sizes are</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">lbp         length between perpendiculars, feet. The measured length, shorter than on deck.</t>
+          <t xml:space="preserve">            compressed around the galleon, so twice the length is not twice the ship on screen.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">beam        (drawn) extreme breadth, feet. Her drawn width, and with her length her collision</t>
+          <t xml:space="preserve">lbp         length between perpendiculars, feet. The measured length, shorter than on deck.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ellipse in a fight.</t>
+          <t xml:space="preserve">beam        (drawn) extreme breadth, feet. Her drawn width, and with her length her collision</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">draft       how deep she floats, feet.</t>
+          <t xml:space="preserve">            ellipse in a fight.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">depth       depth of hold, feet: keelson to the deck above it.</t>
+          <t xml:space="preserve">draft       how deep she floats, feet.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">freeboard   (drawn) height of side above the water amidships, feet. The depth of side in the model.</t>
+          <t xml:space="preserve">depth       depth of hold, feet: keelson to the deck above it.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">lb          length to beam, as a ratio. High is long and lean, low is short and beamy.</t>
+          <t xml:space="preserve">freeboard   (drawn) height of side above the water amidships, feet. The depth of side in the model.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd          beam to depth, as a ratio. High is shallow and beamy, low is deep and narrow.</t>
+          <t xml:space="preserve">lb          length to beam, as a ratio. High is long and lean, low is short and beamy.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">burthen     builder's old measurement tons: what she was rated to carry.</t>
+          <t xml:space="preserve">bd          beam to depth, as a ratio. High is shallow and beamy, low is deep and narrow.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">disp        displacement, tons: what she actually weighs afloat.</t>
+          <t xml:space="preserve">burthen     builder's old measurement tons: what she was rated to carry.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowFine     (drawn) how fine her entry is. 5 is a clipper's bow and 1 a carrack's. It narrows her</t>
+          <t xml:space="preserve">disp        displacement, tons: what she actually weighs afloat.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">            bow and pulls her shoulders aft.</t>
+          <t xml:space="preserve">bowFine     (drawn) how fine her entry is. 5 is a clipper's bow and 1 a carrack's. It narrows her</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">tumblehome  (drawn) how far her sides roll inward above the waterline. 5 is a fluyt.</t>
+          <t xml:space="preserve">            bow and pulls her shoulders aft.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">deadrise    how sharply her bottom rises from the keel. 1 is a flat floor.</t>
+          <t xml:space="preserve">tumblehome  (drawn) how far her sides roll inward above the waterline. 5 is a fluyt.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">sheer       (drawn) how much her deck sweeps up towards bow and stern.</t>
+          <t xml:space="preserve">deadrise    how sharply her bottom rises from the keel. 1 is a flat floor.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">castle      (drawn) how built up her ends are. 1 is an open boat, 2 raises a quarterdeck, 3 and up</t>
+          <t xml:space="preserve">sheer       (drawn) how much her deck sweeps up towards bow and stern.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">            add a forecastle. It is also what a windowed stern needs before it shows any lights.</t>
+          <t xml:space="preserve">castle      (drawn) how built up her ends are. 1 is an open boat, 2 raises a quarterdeck, 3 and up</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">stern       (drawn) the shape of her stern, as one of the named types. Scow, Round, Pear,</t>
+          <t xml:space="preserve">            add a forecastle. It is also what a windowed stern needs before it shows any lights.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Elliptical, Raking transom, Overhanging and Square each have geometry of their own,</t>
+          <t xml:space="preserve">stern       (drawn) the shape of her stern, as one of the named types. Scow, Round, Pear,</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">            and any other name draws a plain transom, which is what Transom and Gallery do. A name</t>
+          <t xml:space="preserve">            Elliptical, Raking transom, Overhanging and Square each have geometry of their own,</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">            holding "gallery" or "castle" lights her stern windows if her castle is 3 or more.</t>
+          <t xml:space="preserve">            and any other name draws a plain transom, which is what Transom and Gallery do. A name</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">mastHeight  (drawn) how tall her rig stands, as a multiple of the galleon's. Scales her masts in</t>
+          <t xml:space="preserve">            holding "gallery" or "castle" lights her stern windows if her castle is 3 or more.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">            both views.</t>
+          <t xml:space="preserve">mastHeight  (drawn) how tall her rig stands, as a multiple of the galleon's. Scales her masts in</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">decks       (drawn) how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is</t>
+          <t xml:space="preserve">            both views.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">            not a number. A 3 or a 2-3 with four ports a side or more draws two tiers of them.</t>
+          <t xml:space="preserve">decks       (drawn) how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">wale        the thickness of her main wale, inches: the heavy belt of timber along her side.</t>
+          <t xml:space="preserve">            not a number. It is how many tiers her ports are drawn on, the last figure counting, so</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">topside     the thickness of her topside planking, inches.</t>
+          <t xml:space="preserve">            a 2-3 is a three-decker and her battery is split three ways up her side.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">roomSpace   room and space, feet: from one frame to the next.</t>
+          <t xml:space="preserve">wale        the thickness of her main wale, inches: the heavy belt of timber along her side.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">species     (drawn) what she was built of, which is also her colour: Oak, Live oak, Teak, Cedar or</t>
+          <t xml:space="preserve">topside     the thickness of her topside planking, inches.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Pine. Any other name is painted as oak.</t>
+          <t xml:space="preserve">roomSpace   room and space, feet: from one frame to the next.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">timber      (drawn) how dense that timber is, oak being 1. Denser timber reads a little darker.</t>
+          <t xml:space="preserve">species     (drawn) what she was built of, which is also her colour: Oak, Live oak, Teak, Cedar or</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">crewMin     the fewest hands she could be worked with, as against the battle complement in `crew`.</t>
+          <t xml:space="preserve">            Pine. Any other name is painted as oak.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">cruise      her everyday speed, knots.</t>
+          <t xml:space="preserve">timber      (drawn) how dense that timber is, oak being 1. Denser timber reads a little darker.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">topSpeed    the best she was ever driven, knots.</t>
+          <t xml:space="preserve">crewMin     the fewest hands she could be worked with, as against the battle complement in `crew`.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">manoeuvre   how handy she was, 0 to 100. The reference's own score, and what `hand` came out of.</t>
+          <t xml:space="preserve">cruise      her everyday speed, knots.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">histGuns    (drawn) how many guns she really carried, of every sort. She shows one gunport a side</t>
+          <t xml:space="preserve">topSpeed    the best she was ever driven, knots.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">            per dozen of them, up to seven. It is not the game's armament: that is the three</t>
+          <t xml:space="preserve">manoeuvre   how handy she was, 0 to 100. The reference's own score, and what `hand` came out of.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">            bearing columns above, and they are deliberately smaller.</t>
+          <t xml:space="preserve">histGuns    (drawn) how many guns she really carried, of every sort. She shows HALF OF THEM as</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            gunports a side, spread over the tiers `decks` gives her, so a first rate's hundred</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masts, from data/masts.tsv</t>
+          <t xml:space="preserve">            guns are fifty ports a side over three decks. That half is exactly her `broadside`</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            bearing for every class in the fleet, which is how the ports and the guns that fire</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE MASTS. One row per type, and a type is a SHAPE OF RIG, not a size.</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A mast's berths are fixed the moment it is built and never change. That is the whole point of the</t>
+          <t xml:space="preserve">            out of them agree without the catalogue and the reference ever meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Masts, from data/masts.tsv</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">part: buying a mast is choosing what she will be able to carry, so a mast with one lugsail berth</t>
+          <t xml:space="preserve">THE MASTS. One row per type, and a type is a SHAPE OF RIG, not a size.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">will never carry two square ones however much a captain spends. It is why the fleet wants a type</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">per configuration rather than one mast with a number of slots.</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A mast's berths are fixed the moment it is built and never change. That is the whole point of the</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">A TYPE IS NOT TIED TO A STATION. A mast that carries three square sails is that mast wherever she</t>
+          <t xml:space="preserve">part: buying a mast is choosing what she will be able to carry, so a mast with one lugsail berth</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">steps it, so the fore and main of a brig are one part bought twice rather than two parts. What</t>
+          <t xml:space="preserve">will never carry two square ones however much a captain spends. It is why the fleet wants a type</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">decides where it can go is the size rung and nothing else.</t>
+          <t xml:space="preserve">per configuration rather than one mast with a number of slots.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERTHS RUN DECK UPWARD, and a fore-and-aft driving sail sharing the lowest level with a course</t>
+          <t xml:space="preserve">A TYPE IS NOT TIED TO A STATION. A mast that carries three square sails is that mast wherever she</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">takes berth 0 with the square canvas above it. A spanker and a course are both set at the deck, one</t>
+          <t xml:space="preserve">steps it, so the fore and main of a brig are one part bought twice rather than two parts. What</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">abaft the mast and one on a yard across it, and the model has one sail to a band: putting the</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spanker lowest is what keeps a brig's rig reading bottom to top the way she is really rigged.</t>
+          <t xml:space="preserve">decides where it can go is the size rung and nothing else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BERTHS RUN DECK UPWARD, and a fore-and-aft driving sail sharing the lowest level with a course</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">id       short camelCase name, unique.</t>
+          <t xml:space="preserve">takes berth 0 with the square canvas above it. A spanker and a course are both set at the deck, one</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">name     what a captain reads.</t>
+          <t xml:space="preserve">abaft the mast and one on a yard across it, and the model has one sail to a band: putting the</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">price    coins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">size     the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor</t>
+          <t xml:space="preserve">spanker lowest is what keeps a brig's rig reading bottom to top the way she is really rigged.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">         choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
+          <t xml:space="preserve">id       short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">spar     yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the</t>
+          <t xml:space="preserve">name     what a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">         bowsprit and nowhere else. A spar and a mast are different sorts of thing and are</t>
+          <t xml:space="preserve">price    coins.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">         matched as such, or a jibboom would be legal as somebody's main mast.</t>
+          <t xml:space="preserve">size     the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">height   how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts</t>
+          <t xml:space="preserve">         choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">         the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
+          <t xml:space="preserve">spar     yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">berths   the sails she can carry, DECK UPWARD, as category labels separated by spaces.</t>
+          <t xml:space="preserve">         bowsprit and nowhere else. A spar and a mast are different sorts of thing and are</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">         LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail</t>
+          <t xml:space="preserve">         matched as such, or a jibboom would be legal as somebody's main mast.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Five is the most the renderer can place up one mast in bands of their own, and the bench</t>
+          <t xml:space="preserve">height   how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">         fails a mast that asks for more.</t>
+          <t xml:space="preserve">         the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">         STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set,</t>
+          <t xml:space="preserve">berths   the sails she can carry, DECK UPWARD, as category labels separated by spaces.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">         so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
+          <t xml:space="preserve">         LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb    one line a captain reads.</t>
+          <t xml:space="preserve">         Five is the most the renderer can place up one mast in bands of their own, and the bench</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         fails a mast that asks for more.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sails, from data/sails.tsv</t>
+          <t xml:space="preserve">         STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set,</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE SAILS. One row per sail a captain can buy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A sail belongs to ONE category and fits a berth of that category. That is the whole fitting rule.</t>
+          <t xml:space="preserve">blurb    one line a captain reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sails, from data/sails.tsv</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Area is not the category: a topgallant is nearly four times a skysail and both are SSQ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  LSQ  Large square    courses, lower topsails            driving power, low on the mast</t>
+          <t xml:space="preserve">THE SAILS. One row per sail a captain can buy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SSQ  Small square    topgallants, royals, skysails,     light-air lift, high up</t>
+          <t xml:space="preserve">A sail belongs to ONE category and fits a berth of that category. That is the whole fitting rule.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       spritsails, sprit-topsails</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TRI  Headsail        jibs, flying jibs, staysails       set on a stay forward: balance, pointing</t>
+          <t xml:space="preserve">Area is not the category: a topgallant is nearly four times a skysail and both are SSQ.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LAT  Lateen          lateen yards, Bermuda mainsails    triangular canvas driving from a mast</t>
+          <t xml:space="preserve">  LSQ  Large square    courses, lower topsails            driving power, low on the mast</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">  GAF  Gaff            gaff mainsails, spankers,          fore-and-aft drive aft, manoeuvre</t>
+          <t xml:space="preserve">  SSQ  Small square    topgallants, royals, skysails,     light-air lift, high up</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       drivers, trysails, gaff topsails</t>
+          <t xml:space="preserve">                       spritsails, sprit-topsails</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LUG  Lugsail         dipping and standing lug,          the main drive of a lugger</t>
+          <t xml:space="preserve">  TRI  Headsail        jibs, flying jibs, staysails       set on a stay forward: balance, pointing</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       lug topsail</t>
+          <t xml:space="preserve">  LAT  Lateen          lateen yards, Bermuda mainsails    triangular canvas driving from a mast</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STU  Studdingsail    boomed-out extensions             ADDITIVE. Not a berth: see below.</t>
+          <t xml:space="preserve">  GAF  Gaff            gaff mainsails, spankers,          fore-and-aft drive aft, manoeuvre</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                       drivers, trysails, gaff topsails</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">A LATEEN IS NOT A HEADSAIL. Both are triangles and they were one category until the bowsprit became</t>
+          <t xml:space="preserve">  LUG  Lugsail         dipping and standing lug,          the main drive of a lugger</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">a station: the moment a jib had a berth of its own a lateen fitted it and pulled better, so the</t>
+          <t xml:space="preserve">                       lug topsail</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice made itself. They do different work, so they are different categories.</t>
+          <t xml:space="preserve">  STU  Studdingsail    boomed-out extensions             ADDITIVE. Not a berth: see below.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU does not go in a berth. A studdingsail booms out beyond a square sail that is already set and</t>
+          <t xml:space="preserve">A LATEEN IS NOT A HEADSAIL. Both are triangles and they were one category until the bowsprit became</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">its area comes off that sail, so it is an attachment rather than a place in the rig: a square sail</t>
+          <t xml:space="preserve">a station: the moment a jib had a berth of its own a lateen fitted it and pulled better, so the</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">carries at most one, matched by LEVEL, and `npm run catalogue` still refuses a berth that asks for</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one, deliberately, so that a mast cannot pretend to carry studdingsails in a slot.</t>
+          <t xml:space="preserve">choice made itself. They do different work, so they are different categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STU does not go in a berth. A studdingsail booms out beyond a square sail that is already set and</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">id      short camelCase name, unique.</t>
+          <t xml:space="preserve">its area comes off that sail, so it is an attachment rather than a place in the rig: a square sail</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">name    what a captain reads.</t>
+          <t xml:space="preserve">carries at most one, matched by LEVEL, and `npm run catalogue` still refuses a berth that asks for</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind    one of the seven labels above.</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">price   coins.</t>
+          <t xml:space="preserve">one, deliberately, so that a mast cannot pretend to carry studdingsails in a slot.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">drive   what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area</t>
+          <t xml:space="preserve">id      short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">        is where this number starts and the proportions are: course 1.00, lower topsail 0.70,</t>
+          <t xml:space="preserve">name    what a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">        topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it,</t>
+          <t xml:space="preserve">kind    one of the seven labels above.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">        which is why two sails of one area can differ here.</t>
+          <t xml:space="preserve">price   coins.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">        FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80),</t>
+          <t xml:space="preserve">drive   what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">        because its area comes off that sail rather than off a place in the rig.</t>
+          <t xml:space="preserve">        is where this number starts and the proportions are: course 1.00, lower topsail 0.70,</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">hand    what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft</t>
+          <t xml:space="preserve">        topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it,</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">        canvas helps her round, so it is positive.</t>
+          <t xml:space="preserve">        which is why two sails of one area can differ here.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">level   STU only, and blank everywhere else. Which square sail up the mast it booms out from,</t>
+          <t xml:space="preserve">        FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80),</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">        counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it;</t>
+          <t xml:space="preserve">        because its area comes off that sail rather than off a place in the rig.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2 the topgallant. The berth number is not the level, because a driver mast's course sits</t>
+          <t xml:space="preserve">hand    what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">        at berth 1 with a spanker under it.</t>
+          <t xml:space="preserve">        canvas helps her round, so it is positive.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb   one line a captain reads.</t>
+          <t xml:space="preserve">level   STU only, and blank everywhere else. Which square sail up the mast it booms out from,</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it;</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two grades of most of them: the plain one a captain can afford early, and a fine one in heavier</t>
+          <t xml:space="preserve">        2 the topgallant. The berth number is not the level, because a driver mast's course sits</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">cloth that is strictly better and priced for it. Prices are placed against each other and have not</t>
+          <t xml:space="preserve">        at berth 1 with a spanker under it.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">been tuned against what a voyage actually pays.</t>
+          <t xml:space="preserve">blurb   one line a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guns, from data/guns.tsv</t>
+          <t xml:space="preserve">Two grades of most of them: the plain one a captain can afford early, and a fine one in heavier</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cloth that is strictly better and priced for it. Prices are placed against each other and have not</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE GUNS. One row per piece a captain can buy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Guns fit BY THE PIECE up to what the hull bears, and `mount` says which of her counts a gun draws</t>
+          <t xml:space="preserve">been tuned against what a voyage actually pays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns, from data/guns.tsv</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">against. Broadside is counted A SIDE and mirrored, because that is how a volley fires: one</t>
+          <t xml:space="preserve">THE GUNS. One row per piece a captain can buy.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">carriage gun bought is one gun each side and two guns aboard.</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Muskets are not in this table and never will be. Small arms come off the crew she musters, with the</t>
+          <t xml:space="preserve">Guns fit BY THE PIECE up to what the hull bears, and `mount` says which of her counts a gun draws</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t xml:space="preserve">swivels on her rail firing in the same volley, which is `rate()`'s business.</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id      short camelCase name, unique.</t>
+          <t xml:space="preserve">against. Broadside is counted A SIDE and mirrored, because that is how a volley fires: one</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carriage gun bought is one gun each side and two guns aboard.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">name    what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`,</t>
+          <t xml:space="preserve">Muskets are not in this table and never will be. Small arms come off the crew she musters, with the</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t xml:space="preserve">        not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        them is arithmetic she should not have to do in words. It is the game's own rule about</t>
+          <t xml:space="preserve">swivels on her rail firing in the same volley, which is `rate()`'s business.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">        numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
+          <t xml:space="preserve">id      short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
+          <t xml:space="preserve">name    what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`,</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">price   coins.</t>
+          <t xml:space="preserve">        not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
+          <t xml:space="preserve">        them is arithmetic she should not have to do in words. It is the game's own rule about</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
+          <t xml:space="preserve">        numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
+          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t xml:space="preserve">        to leave a port empty.</t>
+          <t xml:space="preserve">price   coins.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
+          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
+          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+          <t xml:space="preserve">        to leave a port empty.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
         <is>
           <t xml:space="preserve">blurb   one line a captain reads.</t>
         </is>
@@ -2446,7 +2474,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is not a number. A 3 or a 2-3 with four ports a side or more draws two tiers of them.</t>
+          <t xml:space="preserve">how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is not a number. It is how many tiers her ports are drawn on, the last figure counting, so a 2-3 is a three-decker and her battery is split three ways up her side.</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2694,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">how many guns she really carried, of every sort. She shows one gunport a side per dozen of them, up to seven. It is not the game's armament: that is the three bearing columns above, and they are deliberately smaller.</t>
+          <t xml:space="preserve">how many guns she really carried, of every sort. She shows HALF OF THEM as gunports a side, spread over the tiers `decks` gives her, so a first rate's hundred guns are fifty ports a side over three decks. That half is exactly her `broadside` bearing for every class in the fleet, which is how the ports and the guns that fire out of them agree without the catalogue and the reference ever meeting.</t>
         </is>
       </c>
     </row>
@@ -6155,326 +6183,6 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">launch</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Armed launch</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>100</v>
-      </c>
-      <c r="F18">
-        <v>30</v>
-      </c>
-      <c r="G18">
-        <v>0.58</v>
-      </c>
-      <c r="H18">
-        <v>1.28</v>
-      </c>
-      <c r="I18">
-        <v>0.1</v>
-      </c>
-      <c r="J18">
-        <v>0.21</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bowsprit/boat main/boat</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1650-1865</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Global</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Boarding and inshore harassment</t>
-        </is>
-      </c>
-      <c r="T18">
-        <v>32</v>
-      </c>
-      <c r="U18">
-        <v>30</v>
-      </c>
-      <c r="V18">
-        <v>8</v>
-      </c>
-      <c r="W18">
-        <v>2.5</v>
-      </c>
-      <c r="X18">
-        <v>3</v>
-      </c>
-      <c r="Y18">
-        <v>1.5</v>
-      </c>
-      <c r="Z18">
-        <v>4</v>
-      </c>
-      <c r="AA18">
-        <v>3.2</v>
-      </c>
-      <c r="AB18">
-        <v>6</v>
-      </c>
-      <c r="AC18">
-        <v>8</v>
-      </c>
-      <c r="AD18">
-        <v>3</v>
-      </c>
-      <c r="AE18">
-        <v>1</v>
-      </c>
-      <c r="AF18">
-        <v>2</v>
-      </c>
-      <c r="AG18">
-        <v>2</v>
-      </c>
-      <c r="AH18">
-        <v>1</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>0.9</v>
-      </c>
-      <c r="AK18">
-        <v>1</v>
-      </c>
-      <c r="AL18">
-        <v>1.5</v>
-      </c>
-      <c r="AM18">
-        <v>1</v>
-      </c>
-      <c r="AN18">
-        <v>1.2</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pine</t>
-        </is>
-      </c>
-      <c r="AP18">
-        <v>0.85</v>
-      </c>
-      <c r="AQ18">
-        <v>6</v>
-      </c>
-      <c r="AR18">
-        <v>2</v>
-      </c>
-      <c r="AS18">
-        <v>5</v>
-      </c>
-      <c r="AT18">
-        <v>92</v>
-      </c>
-      <c r="AU18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shallop</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Armed shallop</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>130</v>
-      </c>
-      <c r="E19">
-        <v>117</v>
-      </c>
-      <c r="F19">
-        <v>25</v>
-      </c>
-      <c r="G19">
-        <v>0.64</v>
-      </c>
-      <c r="H19">
-        <v>1.28</v>
-      </c>
-      <c r="I19">
-        <v>0.18</v>
-      </c>
-      <c r="J19">
-        <v>0.47</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bowsprit/boat fore/boat main/boat</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1600-1720</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">North Europe</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coastal and colonial patrol</t>
-        </is>
-      </c>
-      <c r="T19">
-        <v>34</v>
-      </c>
-      <c r="U19">
-        <v>32</v>
-      </c>
-      <c r="V19">
-        <v>10</v>
-      </c>
-      <c r="W19">
-        <v>3.5</v>
-      </c>
-      <c r="X19">
-        <v>4</v>
-      </c>
-      <c r="Y19">
-        <v>2</v>
-      </c>
-      <c r="Z19">
-        <v>3.4</v>
-      </c>
-      <c r="AA19">
-        <v>2.9</v>
-      </c>
-      <c r="AB19">
-        <v>15</v>
-      </c>
-      <c r="AC19">
-        <v>20</v>
-      </c>
-      <c r="AD19">
-        <v>3</v>
-      </c>
-      <c r="AE19">
-        <v>1</v>
-      </c>
-      <c r="AF19">
-        <v>2</v>
-      </c>
-      <c r="AG19">
-        <v>2</v>
-      </c>
-      <c r="AH19">
-        <v>1</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>0.8</v>
-      </c>
-      <c r="AK19">
-        <v>1</v>
-      </c>
-      <c r="AL19">
-        <v>2</v>
-      </c>
-      <c r="AM19">
-        <v>1.25</v>
-      </c>
-      <c r="AN19">
-        <v>1.4</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oak</t>
-        </is>
-      </c>
-      <c r="AP19">
-        <v>1</v>
-      </c>
-      <c r="AQ19">
-        <v>4</v>
-      </c>
-      <c r="AR19">
-        <v>3</v>
-      </c>
-      <c r="AS19">
-        <v>6</v>
-      </c>
-      <c r="AT19">
-        <v>92</v>
-      </c>
-      <c r="AU19">
-        <v>2</v>
-      </c>
-    </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -6483,34 +6191,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">yawl</t>
+          <t xml:space="preserve">launch</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yawl</t>
+          <t xml:space="preserve">Armed launch</t>
         </is>
       </c>
       <c r="D20">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>100</v>
       </c>
       <c r="F20">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G20">
         <v>0.58</v>
       </c>
       <c r="H20">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="I20">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="J20">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -6543,38 +6251,38 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ship's boat and dispatch</t>
+          <t xml:space="preserve">Boarding and inshore harassment</t>
         </is>
       </c>
       <c r="T20">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="U20">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>2.5</v>
       </c>
       <c r="X20">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Y20">
         <v>1.5</v>
       </c>
       <c r="Z20">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AA20">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AB20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD20">
         <v>3</v>
@@ -6597,19 +6305,19 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AK20">
         <v>1</v>
       </c>
       <c r="AL20">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AM20">
         <v>1</v>
       </c>
       <c r="AN20">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -6620,7 +6328,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AR20">
         <v>2</v>
@@ -6629,7 +6337,7 @@
         <v>5</v>
       </c>
       <c r="AT20">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AU20">
         <v>1</v>
@@ -6643,34 +6351,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">smack</t>
+          <t xml:space="preserve">shallop</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armed smack</t>
+          <t xml:space="preserve">Armed shallop</t>
         </is>
       </c>
       <c r="D21">
-        <v>340</v>
+        <v>130</v>
       </c>
       <c r="E21">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="F21">
         <v>25</v>
       </c>
       <c r="G21">
-        <v>0.79</v>
+        <v>0.64</v>
       </c>
       <c r="H21">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="I21">
-        <v>0.42</v>
+        <v>0.18</v>
       </c>
       <c r="J21">
-        <v>1.04</v>
+        <v>0.47</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -6683,7 +6391,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/boat main/small</t>
+          <t xml:space="preserve">bowsprit/boat fore/boat main/boat</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -6693,57 +6401,57 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1750-1815</t>
+          <t xml:space="preserve">1600-1720</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britain</t>
+          <t xml:space="preserve">North Europe</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tender, revenue and dispatch</t>
+          <t xml:space="preserve">Coastal and colonial patrol</t>
         </is>
       </c>
       <c r="T21">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="U21">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="V21">
+        <v>10</v>
+      </c>
+      <c r="W21">
+        <v>3.5</v>
+      </c>
+      <c r="X21">
+        <v>4</v>
+      </c>
+      <c r="Y21">
+        <v>2</v>
+      </c>
+      <c r="Z21">
+        <v>3.4</v>
+      </c>
+      <c r="AA21">
+        <v>2.9</v>
+      </c>
+      <c r="AB21">
         <v>15</v>
       </c>
-      <c r="W21">
-        <v>8</v>
-      </c>
-      <c r="X21">
-        <v>8</v>
-      </c>
-      <c r="Y21">
-        <v>3</v>
-      </c>
-      <c r="Z21">
-        <v>3.5</v>
-      </c>
-      <c r="AA21">
-        <v>1.9</v>
-      </c>
-      <c r="AB21">
-        <v>55</v>
-      </c>
       <c r="AC21">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="AD21">
         <v>3</v>
       </c>
       <c r="AE21">
+        <v>1</v>
+      </c>
+      <c r="AF21">
         <v>2</v>
-      </c>
-      <c r="AF21">
-        <v>3</v>
       </c>
       <c r="AG21">
         <v>2</v>
@@ -6757,19 +6465,19 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AK21">
         <v>1</v>
       </c>
       <c r="AL21">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AM21">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AN21">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -6780,19 +6488,19 @@
         <v>1</v>
       </c>
       <c r="AQ21">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AR21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AS21">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AT21">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AU21">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -6803,47 +6511,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">hoy</t>
+          <t xml:space="preserve">yawl</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoy</t>
+          <t xml:space="preserve">Yawl</t>
         </is>
       </c>
       <c r="D22">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="E22">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>25</v>
       </c>
       <c r="G22">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="H22">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I22">
-        <v>0.51</v>
+        <v>0.09</v>
       </c>
       <c r="J22">
-        <v>1.4</v>
+        <v>0.23</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/boat main/small</t>
+          <t xml:space="preserve">bowsprit/boat main/boat</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -6853,54 +6561,54 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600-1800</t>
+          <t xml:space="preserve">1650-1865</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britain</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coastal supply and guard</t>
+          <t xml:space="preserve">Ship's boat and dispatch</t>
         </is>
       </c>
       <c r="T22">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="U22">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="V22">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="W22">
+        <v>2.5</v>
+      </c>
+      <c r="X22">
+        <v>2.5</v>
+      </c>
+      <c r="Y22">
+        <v>1.5</v>
+      </c>
+      <c r="Z22">
+        <v>3.4</v>
+      </c>
+      <c r="AA22">
+        <v>2.8</v>
+      </c>
+      <c r="AB22">
+        <v>5</v>
+      </c>
+      <c r="AC22">
         <v>7</v>
       </c>
-      <c r="X22">
-        <v>8</v>
-      </c>
-      <c r="Y22">
-        <v>3.5</v>
-      </c>
-      <c r="Z22">
-        <v>3.2</v>
-      </c>
-      <c r="AA22">
-        <v>2.6</v>
-      </c>
-      <c r="AB22">
-        <v>75</v>
-      </c>
-      <c r="AC22">
-        <v>95</v>
-      </c>
       <c r="AD22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF22">
         <v>2</v>
@@ -6913,46 +6621,46 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Round</t>
+          <t xml:space="preserve">Transom</t>
         </is>
       </c>
       <c r="AJ22">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AK22">
         <v>1</v>
       </c>
       <c r="AL22">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="AM22">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AN22">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oak</t>
+          <t xml:space="preserve">Pine</t>
         </is>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="AQ22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AR22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AS22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT22">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AU22">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -6963,34 +6671,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">gundalow</t>
+          <t xml:space="preserve">smack</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gundalow</t>
+          <t xml:space="preserve">Armed smack</t>
         </is>
       </c>
       <c r="D23">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="E23">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="F23">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="G23">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
       <c r="H23">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="I23">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="J23">
-        <v>0.92</v>
+        <v>1.04</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -7003,81 +6711,81 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t xml:space="preserve">main/small</t>
+          <t xml:space="preserve">bowsprit/boat main/small</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1770-1815</t>
+          <t xml:space="preserve">1750-1815</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t xml:space="preserve">American lakes</t>
+          <t xml:space="preserve">Britain</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Floating gun battery</t>
+          <t xml:space="preserve">Tender, revenue and dispatch</t>
         </is>
       </c>
       <c r="T23">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="U23">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V23">
         <v>15</v>
       </c>
       <c r="W23">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Z23">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB23">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AC23">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AD23">
+        <v>3</v>
+      </c>
+      <c r="AE23">
         <v>2</v>
       </c>
-      <c r="AE23">
-        <v>1</v>
-      </c>
       <c r="AF23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH23">
         <v>1</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scow</t>
+          <t xml:space="preserve">Transom</t>
         </is>
       </c>
       <c r="AJ23">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="AK23">
         <v>1</v>
@@ -7089,30 +6797,30 @@
         <v>1.5</v>
       </c>
       <c r="AN23">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pine</t>
+          <t xml:space="preserve">Oak</t>
         </is>
       </c>
       <c r="AP23">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ23">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AR23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AS23">
+        <v>9</v>
+      </c>
+      <c r="AT23">
+        <v>91</v>
+      </c>
+      <c r="AU23">
         <v>4</v>
-      </c>
-      <c r="AT23">
-        <v>63</v>
-      </c>
-      <c r="AU23">
-        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -7123,47 +6831,47 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">tartane</t>
+          <t xml:space="preserve">hoy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tartane</t>
+          <t xml:space="preserve">Hoy</t>
         </is>
       </c>
       <c r="D24">
-        <v>370</v>
+        <v>130</v>
       </c>
       <c r="E24">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="F24">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G24">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="H24">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="I24">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="J24">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="K24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <v>1</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/boat fore/small main/small</t>
+          <t xml:space="preserve">bowsprit/boat main/small</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -7173,57 +6881,57 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600-1820</t>
+          <t xml:space="preserve">1600-1800</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mediterranean</t>
+          <t xml:space="preserve">Britain</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coastal patrol and corsair</t>
+          <t xml:space="preserve">Coastal supply and guard</t>
         </is>
       </c>
       <c r="T24">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="U24">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="V24">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W24">
         <v>7</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Z24">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA24">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AB24">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AC24">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AD24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE24">
         <v>2</v>
       </c>
       <c r="AF24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG24">
         <v>2</v>
@@ -7233,11 +6941,11 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transom</t>
+          <t xml:space="preserve">Round</t>
         </is>
       </c>
       <c r="AJ24">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AK24">
         <v>1</v>
@@ -7249,7 +6957,7 @@
         <v>1.5</v>
       </c>
       <c r="AN24">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -7260,19 +6968,19 @@
         <v>1</v>
       </c>
       <c r="AQ24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AR24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT24">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AU24">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -7283,156 +6991,156 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">gunboat</t>
+          <t xml:space="preserve">gundalow</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gunboat</t>
+          <t xml:space="preserve">Gundalow</t>
         </is>
       </c>
       <c r="D25">
-        <v>510</v>
+        <v>280</v>
       </c>
       <c r="E25">
-        <v>197</v>
+        <v>132</v>
       </c>
       <c r="F25">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G25">
+        <v>0.55</v>
+      </c>
+      <c r="H25">
+        <v>1.09</v>
+      </c>
+      <c r="I25">
+        <v>0.38</v>
+      </c>
+      <c r="J25">
+        <v>0.92</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">main/small</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1770-1815</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">American lakes</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Floating gun battery</t>
+        </is>
+      </c>
+      <c r="T25">
+        <v>54</v>
+      </c>
+      <c r="U25">
+        <v>50</v>
+      </c>
+      <c r="V25">
+        <v>15</v>
+      </c>
+      <c r="W25">
+        <v>4</v>
+      </c>
+      <c r="X25">
+        <v>5</v>
+      </c>
+      <c r="Y25">
+        <v>2.5</v>
+      </c>
+      <c r="Z25">
+        <v>3.6</v>
+      </c>
+      <c r="AA25">
+        <v>3.8</v>
+      </c>
+      <c r="AB25">
+        <v>45</v>
+      </c>
+      <c r="AC25">
+        <v>60</v>
+      </c>
+      <c r="AD25">
+        <v>2</v>
+      </c>
+      <c r="AE25">
+        <v>1</v>
+      </c>
+      <c r="AF25">
+        <v>1</v>
+      </c>
+      <c r="AG25">
+        <v>1</v>
+      </c>
+      <c r="AH25">
+        <v>1</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scow</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>0.7</v>
       </c>
-      <c r="H25">
-        <v>1.22</v>
-      </c>
-      <c r="I25">
-        <v>0.49</v>
-      </c>
-      <c r="J25">
-        <v>1.15</v>
-      </c>
-      <c r="K25">
-        <v>1</v>
-      </c>
-      <c r="L25">
-        <v>1</v>
-      </c>
-      <c r="M25">
-        <v>1</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bowsprit/boat main/small</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1795-1820</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">United States</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Harbour defence</t>
-        </is>
-      </c>
-      <c r="T25">
-        <v>60</v>
-      </c>
-      <c r="U25">
-        <v>56</v>
-      </c>
-      <c r="V25">
-        <v>16</v>
-      </c>
-      <c r="W25">
-        <v>5</v>
-      </c>
-      <c r="X25">
-        <v>6</v>
-      </c>
-      <c r="Y25">
-        <v>3</v>
-      </c>
-      <c r="Z25">
-        <v>3.75</v>
-      </c>
-      <c r="AA25">
-        <v>3.2</v>
-      </c>
-      <c r="AB25">
-        <v>70</v>
-      </c>
-      <c r="AC25">
-        <v>90</v>
-      </c>
-      <c r="AD25">
-        <v>3</v>
-      </c>
-      <c r="AE25">
-        <v>1</v>
-      </c>
-      <c r="AF25">
-        <v>2</v>
-      </c>
-      <c r="AG25">
-        <v>1</v>
-      </c>
-      <c r="AH25">
-        <v>1</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>0.9</v>
-      </c>
       <c r="AK25">
         <v>1</v>
       </c>
       <c r="AL25">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AM25">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AN25">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oak</t>
+          <t xml:space="preserve">Pine</t>
         </is>
       </c>
       <c r="AP25">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="AQ25">
         <v>20</v>
       </c>
       <c r="AR25">
+        <v>2</v>
+      </c>
+      <c r="AS25">
         <v>4</v>
       </c>
-      <c r="AS25">
-        <v>7</v>
-      </c>
       <c r="AT25">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="AU25">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -7443,110 +7151,110 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">bermudaSloop</t>
+          <t xml:space="preserve">tartane</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bermuda sloop</t>
+          <t xml:space="preserve">Tartane</t>
         </is>
       </c>
       <c r="D26">
-        <v>1400</v>
+        <v>370</v>
       </c>
       <c r="E26">
-        <v>244</v>
+        <v>178</v>
       </c>
       <c r="F26">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="G26">
-        <v>0.97</v>
+        <v>0.76</v>
       </c>
       <c r="H26">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="I26">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
       <c r="J26">
-        <v>1.66</v>
+        <v>1.17</v>
       </c>
       <c r="K26">
+        <v>2</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowsprit/boat fore/small main/small</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1600-1820</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mediterranean</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coastal patrol and corsair</t>
+        </is>
+      </c>
+      <c r="T26">
+        <v>55</v>
+      </c>
+      <c r="U26">
+        <v>50</v>
+      </c>
+      <c r="V26">
+        <v>16</v>
+      </c>
+      <c r="W26">
+        <v>7</v>
+      </c>
+      <c r="X26">
+        <v>7</v>
+      </c>
+      <c r="Y26">
         <v>3</v>
       </c>
-      <c r="L26">
-        <v>1</v>
-      </c>
-      <c r="M26">
-        <v>1</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bowsprit/small main/medium</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1700-1820</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Caribbean</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fast dispatch and privateer</t>
-        </is>
-      </c>
-      <c r="T26">
-        <v>70</v>
-      </c>
-      <c r="U26">
-        <v>64</v>
-      </c>
-      <c r="V26">
-        <v>20</v>
-      </c>
-      <c r="W26">
-        <v>10</v>
-      </c>
-      <c r="X26">
-        <v>10</v>
-      </c>
-      <c r="Y26">
-        <v>4</v>
-      </c>
       <c r="Z26">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA26">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AB26">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AC26">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AD26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE26">
         <v>2</v>
       </c>
       <c r="AF26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH26">
         <v>1</v>
@@ -7557,42 +7265,42 @@
         </is>
       </c>
       <c r="AJ26">
+        <v>1</v>
+      </c>
+      <c r="AK26">
+        <v>1</v>
+      </c>
+      <c r="AL26">
+        <v>2.5</v>
+      </c>
+      <c r="AM26">
         <v>1.5</v>
       </c>
-      <c r="AK26">
-        <v>1</v>
-      </c>
-      <c r="AL26">
-        <v>3</v>
-      </c>
-      <c r="AM26">
-        <v>2</v>
-      </c>
       <c r="AN26">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cedar</t>
+          <t xml:space="preserve">Oak</t>
         </is>
       </c>
       <c r="AP26">
         <v>1</v>
       </c>
       <c r="AQ26">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AR26">
+        <v>5</v>
+      </c>
+      <c r="AS26">
         <v>8</v>
       </c>
-      <c r="AS26">
-        <v>12</v>
-      </c>
       <c r="AT26">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AU26">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -7603,37 +7311,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">barcaLonga</t>
+          <t xml:space="preserve">gunboat</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barca-longa</t>
+          <t xml:space="preserve">Gunboat</t>
         </is>
       </c>
       <c r="D27">
-        <v>340</v>
+        <v>510</v>
       </c>
       <c r="E27">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="F27">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G27">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="H27">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="I27">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="J27">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="K27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27">
         <v>1</v>
@@ -7643,7 +7351,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/boat fore/small main/small</t>
+          <t xml:space="preserve">bowsprit/boat main/small</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -7653,30 +7361,30 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650-1800</t>
+          <t xml:space="preserve">1795-1820</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spain</t>
+          <t xml:space="preserve">United States</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coastal patrol and privateer</t>
+          <t xml:space="preserve">Harbour defence</t>
         </is>
       </c>
       <c r="T27">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U27">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="V27">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -7685,28 +7393,28 @@
         <v>3</v>
       </c>
       <c r="Z27">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AA27">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AB27">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AC27">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AD27">
         <v>3</v>
       </c>
       <c r="AE27">
+        <v>1</v>
+      </c>
+      <c r="AF27">
         <v>2</v>
       </c>
-      <c r="AF27">
-        <v>3</v>
-      </c>
       <c r="AG27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH27">
         <v>1</v>
@@ -7723,13 +7431,13 @@
         <v>1</v>
       </c>
       <c r="AL27">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AM27">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AN27">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -7740,19 +7448,19 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AR27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT27">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AU27">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -7763,37 +7471,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">cutter</t>
+          <t xml:space="preserve">bermudaSloop</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cutter</t>
+          <t xml:space="preserve">Bermuda sloop</t>
         </is>
       </c>
       <c r="D28">
-        <v>2500</v>
+        <v>1400</v>
       </c>
       <c r="E28">
-        <v>361</v>
+        <v>244</v>
       </c>
       <c r="F28">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G28">
         <v>0.97</v>
       </c>
       <c r="H28">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>0.66</v>
       </c>
       <c r="J28">
-        <v>2.82</v>
+        <v>1.66</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L28">
         <v>1</v>
@@ -7813,48 +7521,48 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1760-1830</t>
+          <t xml:space="preserve">1700-1820</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britain</t>
+          <t xml:space="preserve">Caribbean</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revenue, dispatch and patrol</t>
+          <t xml:space="preserve">Fast dispatch and privateer</t>
         </is>
       </c>
       <c r="T28">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="U28">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="V28">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="W28">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>4</v>
       </c>
       <c r="Z28">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA28">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB28">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AC28">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="AD28">
         <v>4</v>
@@ -7866,7 +7574,7 @@
         <v>4</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH28">
         <v>1</v>
@@ -7877,30 +7585,30 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AK28">
         <v>1</v>
       </c>
       <c r="AL28">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AM28">
         <v>2</v>
       </c>
       <c r="AN28">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oak</t>
+          <t xml:space="preserve">Cedar</t>
         </is>
       </c>
       <c r="AP28">
         <v>1</v>
       </c>
       <c r="AQ28">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AR28">
         <v>8</v>
@@ -7909,46 +7617,51 @@
         <v>12</v>
       </c>
       <c r="AT28">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AU28">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">lugger</t>
+          <t xml:space="preserve">barcaLonga</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lugger</t>
+          <t xml:space="preserve">Barca-longa</t>
         </is>
       </c>
       <c r="D29">
-        <v>1950</v>
+        <v>340</v>
       </c>
       <c r="E29">
-        <v>277</v>
+        <v>163</v>
       </c>
       <c r="F29">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="G29">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="H29">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="I29">
-        <v>0.81</v>
+        <v>0.4</v>
       </c>
       <c r="J29">
-        <v>2.03</v>
+        <v>1.05</v>
       </c>
       <c r="K29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L29">
         <v>1</v>
@@ -7958,7 +7671,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/small fore/medium main/medium</t>
+          <t xml:space="preserve">bowsprit/boat fore/small main/small</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -7968,51 +7681,51 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1750-1815</t>
+          <t xml:space="preserve">1650-1800</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Channel</t>
+          <t xml:space="preserve">Spain</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Privateer and smuggler</t>
+          <t xml:space="preserve">Coastal patrol and privateer</t>
         </is>
       </c>
       <c r="T29">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U29">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="V29">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z29">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA29">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB29">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="AC29">
-        <v>190</v>
+        <v>65</v>
       </c>
       <c r="AD29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE29">
         <v>2</v>
@@ -8032,19 +7745,19 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AK29">
         <v>1</v>
       </c>
       <c r="AL29">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AM29">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AN29">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -8055,55 +7768,60 @@
         <v>1</v>
       </c>
       <c r="AQ29">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AR29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AS29">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AT29">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AU29">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ketch</t>
+          <t xml:space="preserve">cutter</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ketch</t>
+          <t xml:space="preserve">Cutter</t>
         </is>
       </c>
       <c r="D30">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="E30">
-        <v>415</v>
+        <v>361</v>
       </c>
       <c r="F30">
         <v>60</v>
       </c>
       <c r="G30">
-        <v>0.79</v>
+        <v>0.97</v>
       </c>
       <c r="H30">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="I30">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="K30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L30">
         <v>1</v>
@@ -8113,7 +7831,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/small main/medium mizzen/small</t>
+          <t xml:space="preserve">bowsprit/small main/medium</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -8123,76 +7841,74 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650-1810</t>
+          <t xml:space="preserve">1760-1830</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t xml:space="preserve">North Europe</t>
+          <t xml:space="preserve">Britain</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrol and raiding</t>
+          <t xml:space="preserve">Revenue, dispatch and patrol</t>
         </is>
       </c>
       <c r="T30">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="U30">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="V30">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="W30">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X30">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z30">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA30">
         <v>2.2</v>
       </c>
       <c r="AB30">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AC30">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="AD30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Round</t>
+          <t xml:space="preserve">Transom</t>
         </is>
       </c>
       <c r="AJ30">
-        <v>1.1</v>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1-2</t>
-        </is>
+        <v>1.4</v>
+      </c>
+      <c r="AK30">
+        <v>1</v>
       </c>
       <c r="AL30">
         <v>3.5</v>
@@ -8201,7 +7917,7 @@
         <v>2</v>
       </c>
       <c r="AN30">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -8215,54 +7931,49 @@
         <v>30</v>
       </c>
       <c r="AR30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AS30">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AT30">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AU30">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">brigantine</t>
+          <t xml:space="preserve">lugger</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brigantine</t>
+          <t xml:space="preserve">Lugger</t>
         </is>
       </c>
       <c r="D31">
-        <v>3250</v>
+        <v>1950</v>
       </c>
       <c r="E31">
-        <v>397</v>
+        <v>277</v>
       </c>
       <c r="F31">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G31">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="H31">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="I31">
-        <v>1.1</v>
+        <v>0.81</v>
       </c>
       <c r="J31">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="K31">
         <v>4</v>
@@ -8285,83 +7996,83 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690-1850</t>
+          <t xml:space="preserve">1750-1815</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Americas</t>
+          <t xml:space="preserve">The Channel</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrol, escort and privateer</t>
+          <t xml:space="preserve">Privateer and smuggler</t>
         </is>
       </c>
       <c r="T31">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="U31">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="V31">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="W31">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z31">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA31">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB31">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="AC31">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="AD31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF31">
         <v>3</v>
       </c>
       <c r="AG31">
+        <v>2</v>
+      </c>
+      <c r="AH31">
+        <v>1</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transom</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1</v>
+      </c>
+      <c r="AK31">
+        <v>1</v>
+      </c>
+      <c r="AL31">
         <v>3</v>
       </c>
-      <c r="AH31">
-        <v>2</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.1</v>
-      </c>
-      <c r="AK31">
-        <v>1</v>
-      </c>
-      <c r="AL31">
-        <v>3.5</v>
-      </c>
       <c r="AM31">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AN31">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -8372,57 +8083,52 @@
         <v>1</v>
       </c>
       <c r="AQ31">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AR31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT31">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="AU31">
         <v>14</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">topsailSchooner</t>
+          <t xml:space="preserve">ketch</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topsail schooner</t>
+          <t xml:space="preserve">Ketch</t>
         </is>
       </c>
       <c r="D32">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="E32">
-        <v>370</v>
+        <v>415</v>
       </c>
       <c r="F32">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G32">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="H32">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="I32">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="J32">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="K32">
         <v>3</v>
@@ -8435,7 +8141,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/small fore/medium main/medium</t>
+          <t xml:space="preserve">bowsprit/small main/medium mizzen/small</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -8445,74 +8151,76 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1750-1865</t>
+          <t xml:space="preserve">1650-1810</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Americas</t>
+          <t xml:space="preserve">North Europe</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fast patrol and dispatch</t>
+          <t xml:space="preserve">Patrol and raiding</t>
         </is>
       </c>
       <c r="T32">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="U32">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="V32">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="W32">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X32">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y32">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Z32">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AA32">
         <v>2.2</v>
       </c>
       <c r="AB32">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AC32">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="AD32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF32">
         <v>3</v>
       </c>
       <c r="AG32">
+        <v>3</v>
+      </c>
+      <c r="AH32">
         <v>2</v>
       </c>
-      <c r="AH32">
-        <v>1</v>
-      </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transom</t>
+          <t xml:space="preserve">Round</t>
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
-      </c>
-      <c r="AK32">
-        <v>1</v>
+        <v>1.1</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1-2</t>
+        </is>
       </c>
       <c r="AL32">
         <v>3.5</v>
@@ -8521,7 +8229,7 @@
         <v>2</v>
       </c>
       <c r="AN32">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -8535,16 +8243,16 @@
         <v>30</v>
       </c>
       <c r="AR32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AS32">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT32">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AU32">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -8555,37 +8263,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">baltimoreClipper</t>
+          <t xml:space="preserve">brigantine</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore clipper</t>
+          <t xml:space="preserve">Brigantine</t>
         </is>
       </c>
       <c r="D33">
-        <v>2700</v>
+        <v>3250</v>
       </c>
       <c r="E33">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="F33">
         <v>100</v>
       </c>
       <c r="G33">
-        <v>1.03</v>
+        <v>0.85</v>
       </c>
       <c r="H33">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="I33">
         <v>1.1</v>
       </c>
       <c r="J33">
-        <v>2.29</v>
+        <v>2.6</v>
       </c>
       <c r="K33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L33">
         <v>1</v>
@@ -8605,42 +8313,42 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1795-1850</t>
+          <t xml:space="preserve">1690-1850</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chesapeake</t>
+          <t xml:space="preserve">The Americas</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Privateer and blockade runner</t>
+          <t xml:space="preserve">Patrol, escort and privateer</t>
         </is>
       </c>
       <c r="T33">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="U33">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="V33">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W33">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X33">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z33">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA33">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB33">
         <v>230</v>
@@ -8649,27 +8357,27 @@
         <v>300</v>
       </c>
       <c r="AD33">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG33">
         <v>3</v>
       </c>
       <c r="AH33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Raking transom</t>
+          <t xml:space="preserve">Transom</t>
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK33">
         <v>1</v>
@@ -8681,7 +8389,7 @@
         <v>2</v>
       </c>
       <c r="AN33">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -8695,208 +8403,218 @@
         <v>40</v>
       </c>
       <c r="AR33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AS33">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AT33">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="AU33">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">snow</t>
+          <t xml:space="preserve">topsailSchooner</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snow</t>
+          <t xml:space="preserve">Topsail schooner</t>
         </is>
       </c>
       <c r="D34">
-        <v>4300</v>
+        <v>2200</v>
       </c>
       <c r="E34">
-        <v>482</v>
+        <v>370</v>
       </c>
       <c r="F34">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G34">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="H34">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="I34">
-        <v>1.29</v>
+        <v>1.03</v>
       </c>
       <c r="J34">
-        <v>3.13</v>
+        <v>2.25</v>
       </c>
       <c r="K34">
+        <v>3</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowsprit/small fore/medium main/medium</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1750-1865</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Americas</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fast patrol and dispatch</t>
+        </is>
+      </c>
+      <c r="T34">
+        <v>95</v>
+      </c>
+      <c r="U34">
+        <v>86</v>
+      </c>
+      <c r="V34">
+        <v>24</v>
+      </c>
+      <c r="W34">
+        <v>11</v>
+      </c>
+      <c r="X34">
+        <v>11</v>
+      </c>
+      <c r="Y34">
+        <v>4.5</v>
+      </c>
+      <c r="Z34">
         <v>4</v>
       </c>
-      <c r="L34">
-        <v>1</v>
-      </c>
-      <c r="M34">
-        <v>1</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bowsprit/medium fore/large main/large</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1690-1815</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">North Atlantic</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sloop of war and escort</t>
-        </is>
-      </c>
-      <c r="T34">
-        <v>96</v>
-      </c>
-      <c r="U34">
-        <v>88</v>
-      </c>
-      <c r="V34">
-        <v>27</v>
-      </c>
-      <c r="W34">
-        <v>13</v>
-      </c>
-      <c r="X34">
-        <v>13</v>
-      </c>
-      <c r="Y34">
-        <v>5</v>
-      </c>
-      <c r="Z34">
-        <v>3.6</v>
-      </c>
       <c r="AA34">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB34">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="AC34">
-        <v>380</v>
+        <v>270</v>
       </c>
       <c r="AD34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF34">
         <v>3</v>
       </c>
       <c r="AG34">
+        <v>2</v>
+      </c>
+      <c r="AH34">
+        <v>1</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transom</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>1.2</v>
+      </c>
+      <c r="AK34">
+        <v>1</v>
+      </c>
+      <c r="AL34">
+        <v>3.5</v>
+      </c>
+      <c r="AM34">
+        <v>2</v>
+      </c>
+      <c r="AN34">
+        <v>1.8</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AP34">
+        <v>1</v>
+      </c>
+      <c r="AQ34">
+        <v>30</v>
+      </c>
+      <c r="AR34">
+        <v>7</v>
+      </c>
+      <c r="AS34">
+        <v>11</v>
+      </c>
+      <c r="AT34">
+        <v>85</v>
+      </c>
+      <c r="AU34">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">baltimoreClipper</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baltimore clipper</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>2700</v>
+      </c>
+      <c r="E35">
+        <v>405</v>
+      </c>
+      <c r="F35">
+        <v>100</v>
+      </c>
+      <c r="G35">
+        <v>1.03</v>
+      </c>
+      <c r="H35">
+        <v>1.11</v>
+      </c>
+      <c r="I35">
+        <v>1.1</v>
+      </c>
+      <c r="J35">
+        <v>2.29</v>
+      </c>
+      <c r="K35">
         <v>3</v>
       </c>
-      <c r="AH34">
-        <v>2</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transom</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.1</v>
-      </c>
-      <c r="AK34">
-        <v>1</v>
-      </c>
-      <c r="AL34">
-        <v>4</v>
-      </c>
-      <c r="AM34">
-        <v>2.25</v>
-      </c>
-      <c r="AN34">
-        <v>1.9</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oak</t>
-        </is>
-      </c>
-      <c r="AP34">
-        <v>1</v>
-      </c>
-      <c r="AQ34">
-        <v>60</v>
-      </c>
-      <c r="AR34">
-        <v>6</v>
-      </c>
-      <c r="AS34">
-        <v>10</v>
-      </c>
-      <c r="AT34">
-        <v>66</v>
-      </c>
-      <c r="AU34">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brigSloop</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Brig-sloop</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>6150</v>
-      </c>
-      <c r="E35">
-        <v>574</v>
-      </c>
-      <c r="F35">
-        <v>130</v>
-      </c>
-      <c r="G35">
-        <v>0.88</v>
-      </c>
-      <c r="H35">
-        <v>0.95</v>
-      </c>
-      <c r="I35">
-        <v>1.5</v>
-      </c>
-      <c r="J35">
-        <v>3.99</v>
-      </c>
-      <c r="K35">
-        <v>5</v>
-      </c>
       <c r="L35">
         <v>1</v>
       </c>
@@ -8905,7 +8623,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/medium fore/large main/large</t>
+          <t xml:space="preserve">bowsprit/small fore/medium main/medium</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -8915,83 +8633,83 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1770-1850</t>
+          <t xml:space="preserve">1795-1850</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Chesapeake</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Escort and commerce war</t>
+          <t xml:space="preserve">Privateer and blockade runner</t>
         </is>
       </c>
       <c r="T35">
         <v>100</v>
       </c>
       <c r="U35">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V35">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="W35">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X35">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y35">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="Z35">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA35">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB35">
-        <v>380</v>
+        <v>230</v>
       </c>
       <c r="AC35">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="AD35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG35">
         <v>3</v>
       </c>
       <c r="AH35">
+        <v>1</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Raking transom</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.3</v>
+      </c>
+      <c r="AK35">
+        <v>1</v>
+      </c>
+      <c r="AL35">
+        <v>3.5</v>
+      </c>
+      <c r="AM35">
         <v>2</v>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Round</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.1</v>
-      </c>
-      <c r="AK35">
-        <v>1</v>
-      </c>
-      <c r="AL35">
-        <v>4</v>
-      </c>
-      <c r="AM35">
-        <v>2.5</v>
-      </c>
       <c r="AN35">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -9002,65 +8720,65 @@
         <v>1</v>
       </c>
       <c r="AQ35">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AR35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AS35">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT35">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="AU35">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">gunBrig</t>
+          <t xml:space="preserve">snow</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gun-brig</t>
+          <t xml:space="preserve">Snow</t>
         </is>
       </c>
       <c r="D36">
-        <v>1650</v>
+        <v>4300</v>
       </c>
       <c r="E36">
-        <v>334</v>
+        <v>482</v>
       </c>
       <c r="F36">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G36">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="H36">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="I36">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="J36">
-        <v>2.12</v>
+        <v>3.13</v>
       </c>
       <c r="K36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36">
         <v>1</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/small fore/medium main/medium</t>
+          <t xml:space="preserve">bowsprit/medium fore/large main/large</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -9070,83 +8788,83 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1795-1815</t>
+          <t xml:space="preserve">1690-1815</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britain</t>
+          <t xml:space="preserve">North Atlantic</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inshore and convoy work</t>
+          <t xml:space="preserve">Sloop of war and escort</t>
         </is>
       </c>
       <c r="T36">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="U36">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="V36">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Y36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z36">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA36">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AB36">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="AC36">
-        <v>230</v>
+        <v>380</v>
       </c>
       <c r="AD36">
         <v>3</v>
       </c>
       <c r="AE36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF36">
         <v>3</v>
       </c>
       <c r="AG36">
+        <v>3</v>
+      </c>
+      <c r="AH36">
         <v>2</v>
       </c>
-      <c r="AH36">
-        <v>1</v>
-      </c>
       <c r="AI36" t="inlineStr">
         <is>
           <t xml:space="preserve">Transom</t>
         </is>
       </c>
       <c r="AJ36">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AK36">
         <v>1</v>
       </c>
       <c r="AL36">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AM36">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AN36">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -9157,70 +8875,65 @@
         <v>1</v>
       </c>
       <c r="AQ36">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AR36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT36">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="AU36">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">bombVessel</t>
+          <t xml:space="preserve">brigSloop</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bomb vessel</t>
+          <t xml:space="preserve">Brig-sloop</t>
         </is>
       </c>
       <c r="D37">
-        <v>2600</v>
+        <v>6150</v>
       </c>
       <c r="E37">
-        <v>600</v>
+        <v>574</v>
       </c>
       <c r="F37">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="G37">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="H37">
-        <v>1.01</v>
+        <v>0.95</v>
       </c>
       <c r="I37">
         <v>1.5</v>
       </c>
       <c r="J37">
-        <v>4.12</v>
+        <v>3.99</v>
       </c>
       <c r="K37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37">
         <v>1</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/medium main/large mizzen/medium</t>
+          <t xml:space="preserve">bowsprit/medium fore/large main/large</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -9230,27 +8943,27 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690-1855</t>
+          <t xml:space="preserve">1770-1850</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britain and France</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shore bombardment</t>
+          <t xml:space="preserve">Escort and commerce war</t>
         </is>
       </c>
       <c r="T37">
+        <v>100</v>
+      </c>
+      <c r="U37">
         <v>92</v>
       </c>
-      <c r="U37">
-        <v>84</v>
-      </c>
       <c r="V37">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="W37">
         <v>13</v>
@@ -9259,13 +8972,13 @@
         <v>13</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Z37">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA37">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB37">
         <v>380</v>
@@ -9274,16 +8987,16 @@
         <v>480</v>
       </c>
       <c r="AD37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE37">
         <v>3</v>
       </c>
       <c r="AF37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH37">
         <v>2</v>
@@ -9294,16 +9007,16 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AK37">
         <v>1</v>
       </c>
       <c r="AL37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM37">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AN37">
         <v>1.9</v>
@@ -9317,42 +9030,37 @@
         <v>1</v>
       </c>
       <c r="AQ37">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AR37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS37">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AT37">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AU37">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">pinnace</t>
+          <t xml:space="preserve">gunBrig</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pinnace</t>
+          <t xml:space="preserve">Gun-brig</t>
         </is>
       </c>
       <c r="D38">
-        <v>560</v>
+        <v>1650</v>
       </c>
       <c r="E38">
-        <v>187</v>
+        <v>334</v>
       </c>
       <c r="F38">
         <v>60</v>
@@ -9361,26 +9069,26 @@
         <v>0.79</v>
       </c>
       <c r="H38">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="I38">
-        <v>0.46</v>
+        <v>0.92</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>2.12</v>
       </c>
       <c r="K38">
+        <v>3</v>
+      </c>
+      <c r="L38">
         <v>2</v>
       </c>
-      <c r="L38">
-        <v>1</v>
-      </c>
       <c r="M38">
         <v>1</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/boat fore/small main/small mizzen/small</t>
+          <t xml:space="preserve">bowsprit/small fore/medium main/medium</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -9390,67 +9098,67 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1550-1650</t>
+          <t xml:space="preserve">1795-1815</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t xml:space="preserve">England</t>
+          <t xml:space="preserve">Britain</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scout and light warship</t>
+          <t xml:space="preserve">Inshore and convoy work</t>
         </is>
       </c>
       <c r="T38">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="U38">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="V38">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y38">
         <v>4</v>
       </c>
       <c r="Z38">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA38">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB38">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="AC38">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="AD38">
         <v>3</v>
       </c>
       <c r="AE38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF38">
         <v>3</v>
       </c>
       <c r="AG38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Square</t>
+          <t xml:space="preserve">Transom</t>
         </is>
       </c>
       <c r="AJ38">
@@ -9460,10 +9168,10 @@
         <v>1</v>
       </c>
       <c r="AL38">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AM38">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AN38">
         <v>1.8</v>
@@ -9477,7 +9185,7 @@
         <v>1</v>
       </c>
       <c r="AQ38">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AR38">
         <v>5</v>
@@ -9486,10 +9194,10 @@
         <v>9</v>
       </c>
       <c r="AT38">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="AU38">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
@@ -9500,47 +9208,47 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">xebec</t>
+          <t xml:space="preserve">bombVessel</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xebec</t>
+          <t xml:space="preserve">Bomb vessel</t>
         </is>
       </c>
       <c r="D39">
-        <v>14000</v>
+        <v>2600</v>
       </c>
       <c r="E39">
-        <v>532</v>
+        <v>600</v>
       </c>
       <c r="F39">
-        <v>350</v>
+        <v>110</v>
       </c>
       <c r="G39">
-        <v>0.94</v>
+        <v>0.73</v>
       </c>
       <c r="H39">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="I39">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="J39">
-        <v>3.08</v>
+        <v>4.12</v>
       </c>
       <c r="K39">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium</t>
+          <t xml:space="preserve">bowsprit/medium main/large mizzen/medium</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -9550,212 +9258,217 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650-1830</t>
+          <t xml:space="preserve">1690-1855</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbary coast</t>
+          <t xml:space="preserve">Britain and France</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corsair and coastal warship</t>
+          <t xml:space="preserve">Shore bombardment</t>
         </is>
       </c>
       <c r="T39">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="U39">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="V39">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W39">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="X39">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y39">
         <v>5</v>
       </c>
       <c r="Z39">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA39">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB39">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="AC39">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="AD39">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH39">
         <v>2</v>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overhanging</t>
+          <t xml:space="preserve">Round</t>
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AK39">
         <v>1</v>
       </c>
       <c r="AL39">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AM39">
+        <v>3</v>
+      </c>
+      <c r="AN39">
+        <v>1.9</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AP39">
+        <v>1</v>
+      </c>
+      <c r="AQ39">
+        <v>60</v>
+      </c>
+      <c r="AR39">
+        <v>4</v>
+      </c>
+      <c r="AS39">
+        <v>8</v>
+      </c>
+      <c r="AT39">
+        <v>68</v>
+      </c>
+      <c r="AU39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pinnace</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pinnace</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>560</v>
+      </c>
+      <c r="E40">
+        <v>187</v>
+      </c>
+      <c r="F40">
+        <v>60</v>
+      </c>
+      <c r="G40">
+        <v>0.79</v>
+      </c>
+      <c r="H40">
+        <v>1.01</v>
+      </c>
+      <c r="I40">
+        <v>0.46</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40">
         <v>2</v>
       </c>
-      <c r="AN39">
-        <v>1.8</v>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oak</t>
-        </is>
-      </c>
-      <c r="AP39">
-        <v>1</v>
-      </c>
-      <c r="AQ39">
-        <v>120</v>
-      </c>
-      <c r="AR39">
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowsprit/boat fore/small main/small mizzen/small</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1550-1650</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">England</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scout and light warship</t>
+        </is>
+      </c>
+      <c r="T40">
+        <v>60</v>
+      </c>
+      <c r="U40">
+        <v>54</v>
+      </c>
+      <c r="V40">
+        <v>15</v>
+      </c>
+      <c r="W40">
         <v>7</v>
       </c>
-      <c r="AS39">
-        <v>12</v>
-      </c>
-      <c r="AT39">
-        <v>82</v>
-      </c>
-      <c r="AU39">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fluyt</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Armed fluyt</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>3400</v>
-      </c>
-      <c r="E40">
-        <v>487</v>
-      </c>
-      <c r="F40">
-        <v>70</v>
-      </c>
-      <c r="G40">
-        <v>0.73</v>
-      </c>
-      <c r="H40">
-        <v>0.87</v>
-      </c>
-      <c r="I40">
-        <v>1.33</v>
-      </c>
-      <c r="J40">
-        <v>2.78</v>
-      </c>
-      <c r="K40">
+      <c r="X40">
+        <v>7</v>
+      </c>
+      <c r="Y40">
         <v>4</v>
       </c>
-      <c r="L40">
-        <v>1</v>
-      </c>
-      <c r="M40">
-        <v>1</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1600-1720</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dutch Republic</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Armed transport and escort</t>
-        </is>
-      </c>
-      <c r="T40">
-        <v>100</v>
-      </c>
-      <c r="U40">
-        <v>92</v>
-      </c>
-      <c r="V40">
-        <v>24</v>
-      </c>
-      <c r="W40">
-        <v>11</v>
-      </c>
-      <c r="X40">
-        <v>12</v>
-      </c>
-      <c r="Y40">
-        <v>5</v>
-      </c>
       <c r="Z40">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA40">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB40">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="AC40">
-        <v>400</v>
+        <v>80</v>
       </c>
       <c r="AD40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG40">
         <v>3</v>
@@ -9765,154 +9478,157 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pear</t>
+          <t xml:space="preserve">Square</t>
         </is>
       </c>
       <c r="AJ40">
         <v>1</v>
       </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1-2</t>
-        </is>
+      <c r="AK40">
+        <v>1</v>
       </c>
       <c r="AL40">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AM40">
+        <v>1.75</v>
+      </c>
+      <c r="AN40">
+        <v>1.8</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AP40">
+        <v>1</v>
+      </c>
+      <c r="AQ40">
+        <v>20</v>
+      </c>
+      <c r="AR40">
+        <v>5</v>
+      </c>
+      <c r="AS40">
+        <v>9</v>
+      </c>
+      <c r="AT40">
+        <v>66</v>
+      </c>
+      <c r="AU40">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xebec</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xebec</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>14000</v>
+      </c>
+      <c r="E41">
+        <v>532</v>
+      </c>
+      <c r="F41">
+        <v>350</v>
+      </c>
+      <c r="G41">
+        <v>0.94</v>
+      </c>
+      <c r="H41">
+        <v>1.07</v>
+      </c>
+      <c r="I41">
+        <v>1.44</v>
+      </c>
+      <c r="J41">
+        <v>3.08</v>
+      </c>
+      <c r="K41">
+        <v>8</v>
+      </c>
+      <c r="L41">
         <v>2</v>
       </c>
-      <c r="AN40">
-        <v>1.9</v>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oak</t>
-        </is>
-      </c>
-      <c r="AP40">
-        <v>1</v>
-      </c>
-      <c r="AQ40">
-        <v>30</v>
-      </c>
-      <c r="AR40">
+      <c r="M41">
         <v>4</v>
       </c>
-      <c r="AS40">
-        <v>8</v>
-      </c>
-      <c r="AT40">
-        <v>49</v>
-      </c>
-      <c r="AU40">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barque</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Armed barque</t>
-        </is>
-      </c>
-      <c r="D41">
-        <v>4450</v>
-      </c>
-      <c r="E41">
-        <v>563</v>
-      </c>
-      <c r="F41">
-        <v>95</v>
-      </c>
-      <c r="G41">
-        <v>0.79</v>
-      </c>
-      <c r="H41">
-        <v>0.95</v>
-      </c>
-      <c r="I41">
-        <v>1.48</v>
-      </c>
-      <c r="J41">
-        <v>3.51</v>
-      </c>
-      <c r="K41">
+      <c r="N41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1650-1830</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Barbary coast</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corsair and coastal warship</t>
+        </is>
+      </c>
+      <c r="T41">
+        <v>115</v>
+      </c>
+      <c r="U41">
+        <v>104</v>
+      </c>
+      <c r="V41">
+        <v>28</v>
+      </c>
+      <c r="W41">
+        <v>10</v>
+      </c>
+      <c r="X41">
+        <v>11</v>
+      </c>
+      <c r="Y41">
+        <v>5</v>
+      </c>
+      <c r="Z41">
+        <v>4.1</v>
+      </c>
+      <c r="AA41">
+        <v>2.8</v>
+      </c>
+      <c r="AB41">
+        <v>350</v>
+      </c>
+      <c r="AC41">
+        <v>450</v>
+      </c>
+      <c r="AD41">
+        <v>5</v>
+      </c>
+      <c r="AE41">
+        <v>1</v>
+      </c>
+      <c r="AF41">
         <v>4</v>
-      </c>
-      <c r="L41">
-        <v>1</v>
-      </c>
-      <c r="M41">
-        <v>1</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1650-1865</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Global</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Escort and armed trader</t>
-        </is>
-      </c>
-      <c r="T41">
-        <v>106</v>
-      </c>
-      <c r="U41">
-        <v>98</v>
-      </c>
-      <c r="V41">
-        <v>29</v>
-      </c>
-      <c r="W41">
-        <v>13</v>
-      </c>
-      <c r="X41">
-        <v>13</v>
-      </c>
-      <c r="Y41">
-        <v>5.5</v>
-      </c>
-      <c r="Z41">
-        <v>3.7</v>
-      </c>
-      <c r="AA41">
-        <v>2.2</v>
-      </c>
-      <c r="AB41">
-        <v>370</v>
-      </c>
-      <c r="AC41">
-        <v>470</v>
-      </c>
-      <c r="AD41">
-        <v>3</v>
-      </c>
-      <c r="AE41">
-        <v>3</v>
-      </c>
-      <c r="AF41">
-        <v>3</v>
       </c>
       <c r="AG41">
         <v>3</v>
@@ -9922,180 +9638,177 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Round</t>
+          <t xml:space="preserve">Overhanging</t>
         </is>
       </c>
       <c r="AJ41">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK41">
         <v>1</v>
       </c>
       <c r="AL41">
+        <v>3.5</v>
+      </c>
+      <c r="AM41">
+        <v>2</v>
+      </c>
+      <c r="AN41">
+        <v>1.8</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AP41">
+        <v>1</v>
+      </c>
+      <c r="AQ41">
+        <v>120</v>
+      </c>
+      <c r="AR41">
+        <v>7</v>
+      </c>
+      <c r="AS41">
+        <v>12</v>
+      </c>
+      <c r="AT41">
+        <v>82</v>
+      </c>
+      <c r="AU41">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fluyt</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armed fluyt</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>3400</v>
+      </c>
+      <c r="E42">
+        <v>487</v>
+      </c>
+      <c r="F42">
+        <v>70</v>
+      </c>
+      <c r="G42">
+        <v>0.73</v>
+      </c>
+      <c r="H42">
+        <v>0.87</v>
+      </c>
+      <c r="I42">
+        <v>1.33</v>
+      </c>
+      <c r="J42">
+        <v>2.78</v>
+      </c>
+      <c r="K42">
         <v>4</v>
       </c>
-      <c r="AM41">
-        <v>2.25</v>
-      </c>
-      <c r="AN41">
-        <v>1.9</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oak</t>
-        </is>
-      </c>
-      <c r="AP41">
-        <v>1</v>
-      </c>
-      <c r="AQ41">
-        <v>40</v>
-      </c>
-      <c r="AR41">
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1600-1720</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dutch Republic</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armed transport and escort</t>
+        </is>
+      </c>
+      <c r="T42">
+        <v>100</v>
+      </c>
+      <c r="U42">
+        <v>92</v>
+      </c>
+      <c r="V42">
+        <v>24</v>
+      </c>
+      <c r="W42">
+        <v>11</v>
+      </c>
+      <c r="X42">
+        <v>12</v>
+      </c>
+      <c r="Y42">
         <v>5</v>
       </c>
-      <c r="AS41">
-        <v>9</v>
-      </c>
-      <c r="AT41">
-        <v>63</v>
-      </c>
-      <c r="AU41">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">corvette</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Corvette</t>
-        </is>
-      </c>
-      <c r="D42">
-        <v>7950</v>
-      </c>
-      <c r="E42">
-        <v>655</v>
-      </c>
-      <c r="F42">
-        <v>170</v>
-      </c>
-      <c r="G42">
-        <v>0.91</v>
-      </c>
-      <c r="H42">
-        <v>0.95</v>
-      </c>
-      <c r="I42">
-        <v>1.69</v>
-      </c>
-      <c r="J42">
-        <v>3.99</v>
-      </c>
-      <c r="K42">
-        <v>6</v>
-      </c>
-      <c r="L42">
-        <v>1</v>
-      </c>
-      <c r="M42">
-        <v>2</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1740-1860</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Global</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Patrol, escort, commerce war</t>
-        </is>
-      </c>
-      <c r="T42">
-        <v>115</v>
-      </c>
-      <c r="U42">
-        <v>106</v>
-      </c>
-      <c r="V42">
-        <v>31</v>
-      </c>
-      <c r="W42">
-        <v>14</v>
-      </c>
-      <c r="X42">
-        <v>14</v>
-      </c>
-      <c r="Y42">
-        <v>6</v>
-      </c>
       <c r="Z42">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AA42">
         <v>2.2</v>
       </c>
       <c r="AB42">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="AC42">
-        <v>570</v>
+        <v>400</v>
       </c>
       <c r="AD42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG42">
         <v>3</v>
       </c>
       <c r="AH42">
+        <v>3</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pear</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>1</v>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1-2</t>
+        </is>
+      </c>
+      <c r="AL42">
+        <v>3.5</v>
+      </c>
+      <c r="AM42">
         <v>2</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Round</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.2</v>
-      </c>
-      <c r="AK42">
-        <v>1</v>
-      </c>
-      <c r="AL42">
-        <v>4</v>
-      </c>
-      <c r="AM42">
-        <v>2.5</v>
       </c>
       <c r="AN42">
         <v>1.9</v>
@@ -10109,174 +9822,174 @@
         <v>1</v>
       </c>
       <c r="AQ42">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AR42">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AS42">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AT42">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="AU42">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrack</t>
+          <t xml:space="preserve">barque</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carrack</t>
+          <t xml:space="preserve">Armed barque</t>
         </is>
       </c>
       <c r="D43">
-        <v>20000</v>
+        <v>4450</v>
       </c>
       <c r="E43">
-        <v>976</v>
+        <v>563</v>
       </c>
       <c r="F43">
-        <v>400</v>
+        <v>95</v>
       </c>
       <c r="G43">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="H43">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="I43">
-        <v>2.29</v>
+        <v>1.48</v>
       </c>
       <c r="J43">
-        <v>6.68</v>
+        <v>3.51</v>
       </c>
       <c r="K43">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L43">
         <v>1</v>
       </c>
       <c r="M43">
+        <v>1</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1650-1865</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Global</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escort and armed trader</t>
+        </is>
+      </c>
+      <c r="T43">
+        <v>106</v>
+      </c>
+      <c r="U43">
+        <v>98</v>
+      </c>
+      <c r="V43">
+        <v>29</v>
+      </c>
+      <c r="W43">
+        <v>13</v>
+      </c>
+      <c r="X43">
+        <v>13</v>
+      </c>
+      <c r="Y43">
+        <v>5.5</v>
+      </c>
+      <c r="Z43">
+        <v>3.7</v>
+      </c>
+      <c r="AA43">
+        <v>2.2</v>
+      </c>
+      <c r="AB43">
+        <v>370</v>
+      </c>
+      <c r="AC43">
+        <v>470</v>
+      </c>
+      <c r="AD43">
+        <v>3</v>
+      </c>
+      <c r="AE43">
+        <v>3</v>
+      </c>
+      <c r="AF43">
+        <v>3</v>
+      </c>
+      <c r="AG43">
+        <v>3</v>
+      </c>
+      <c r="AH43">
+        <v>2</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>1.1</v>
+      </c>
+      <c r="AK43">
+        <v>1</v>
+      </c>
+      <c r="AL43">
         <v>4</v>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium bonaventure/small</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1450-1570</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Iberia</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flagship and armed trader</t>
-        </is>
-      </c>
-      <c r="T43">
-        <v>120</v>
-      </c>
-      <c r="U43">
-        <v>108</v>
-      </c>
-      <c r="V43">
+      <c r="AM43">
+        <v>2.25</v>
+      </c>
+      <c r="AN43">
+        <v>1.9</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AP43">
+        <v>1</v>
+      </c>
+      <c r="AQ43">
         <v>40</v>
       </c>
-      <c r="W43">
-        <v>16</v>
-      </c>
-      <c r="X43">
-        <v>20</v>
-      </c>
-      <c r="Y43">
-        <v>12</v>
-      </c>
-      <c r="Z43">
-        <v>3</v>
-      </c>
-      <c r="AA43">
-        <v>2.5</v>
-      </c>
-      <c r="AB43">
-        <v>700</v>
-      </c>
-      <c r="AC43">
-        <v>900</v>
-      </c>
-      <c r="AD43">
-        <v>1</v>
-      </c>
-      <c r="AE43">
-        <v>4</v>
-      </c>
-      <c r="AF43">
-        <v>2</v>
-      </c>
-      <c r="AG43">
+      <c r="AR43">
         <v>5</v>
       </c>
-      <c r="AH43">
-        <v>5</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Square castle</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>0.9</v>
-      </c>
-      <c r="AK43">
-        <v>2</v>
-      </c>
-      <c r="AL43">
-        <v>5</v>
-      </c>
-      <c r="AM43">
-        <v>3</v>
-      </c>
-      <c r="AN43">
-        <v>2</v>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oak</t>
-        </is>
-      </c>
-      <c r="AP43">
-        <v>1</v>
-      </c>
-      <c r="AQ43">
-        <v>100</v>
-      </c>
-      <c r="AR43">
-        <v>3</v>
-      </c>
       <c r="AS43">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AT43">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="AU43">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
@@ -10287,40 +10000,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">sixthRate</t>
+          <t xml:space="preserve">corvette</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">6th rate</t>
+          <t xml:space="preserve">Corvette</t>
         </is>
       </c>
       <c r="D44">
-        <v>10500</v>
+        <v>7950</v>
       </c>
       <c r="E44">
-        <v>736</v>
+        <v>655</v>
       </c>
       <c r="F44">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="G44">
         <v>0.91</v>
       </c>
       <c r="H44">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="I44">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="J44">
-        <v>4.66</v>
+        <v>3.99</v>
       </c>
       <c r="K44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44">
         <v>2</v>
@@ -10337,48 +10050,48 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1700-1820</t>
+          <t xml:space="preserve">1740-1860</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britain</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cruiser, escort and patrol</t>
+          <t xml:space="preserve">Patrol, escort, commerce war</t>
         </is>
       </c>
       <c r="T44">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U44">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="V44">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="W44">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X44">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y44">
         <v>6</v>
       </c>
       <c r="Z44">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA44">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB44">
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="AC44">
-        <v>660</v>
+        <v>570</v>
       </c>
       <c r="AD44">
         <v>4</v>
@@ -10403,10 +10116,8 @@
       <c r="AJ44">
         <v>1.2</v>
       </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1-2</t>
-        </is>
+      <c r="AK44">
+        <v>1</v>
       </c>
       <c r="AL44">
         <v>4</v>
@@ -10426,7 +10137,7 @@
         <v>1</v>
       </c>
       <c r="AQ44">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AR44">
         <v>7</v>
@@ -10435,56 +10146,56 @@
         <v>11</v>
       </c>
       <c r="AT44">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AU44">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">raceGalleon</t>
+          <t xml:space="preserve">carrack</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Race-built galleon</t>
+          <t xml:space="preserve">Carrack</t>
         </is>
       </c>
       <c r="D45">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="E45">
-        <v>729</v>
+        <v>976</v>
       </c>
       <c r="F45">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="G45">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="H45">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="I45">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="J45">
-        <v>3.8</v>
+        <v>6.68</v>
       </c>
       <c r="K45">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M45">
         <v>4</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium</t>
+          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium bonaventure/small</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -10494,80 +10205,80 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1570-1620</t>
+          <t xml:space="preserve">1450-1570</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t xml:space="preserve">England</t>
+          <t xml:space="preserve">Iberia</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Line and cruiser warship</t>
+          <t xml:space="preserve">Flagship and armed trader</t>
         </is>
       </c>
       <c r="T45">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="U45">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="V45">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="W45">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X45">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Y45">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z45">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AA45">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB45">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AC45">
-        <v>640</v>
+        <v>900</v>
       </c>
       <c r="AD45">
+        <v>1</v>
+      </c>
+      <c r="AE45">
         <v>4</v>
       </c>
-      <c r="AE45">
-        <v>3</v>
-      </c>
       <c r="AF45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Square gallery</t>
+          <t xml:space="preserve">Square castle</t>
         </is>
       </c>
       <c r="AJ45">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AK45">
         <v>2</v>
       </c>
       <c r="AL45">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AM45">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AN45">
         <v>2</v>
@@ -10581,65 +10292,70 @@
         <v>1</v>
       </c>
       <c r="AQ45">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AR45">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AS45">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AT45">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="AU45">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">galleon</t>
+          <t xml:space="preserve">sixthRate</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Galleon</t>
+          <t xml:space="preserve">6th rate</t>
         </is>
       </c>
       <c r="D46">
-        <v>26500</v>
+        <v>10500</v>
       </c>
       <c r="E46">
-        <v>976</v>
+        <v>736</v>
       </c>
       <c r="F46">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="G46">
-        <v>0.73</v>
+        <v>0.91</v>
       </c>
       <c r="H46">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="I46">
-        <v>2.29</v>
+        <v>1.86</v>
       </c>
       <c r="J46">
-        <v>5.89</v>
+        <v>4.66</v>
       </c>
       <c r="K46">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L46">
         <v>2</v>
       </c>
       <c r="M46">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium bonaventure/small</t>
+          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -10649,83 +10365,85 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1550-1650</t>
+          <t xml:space="preserve">1700-1820</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spain and Portugal</t>
+          <t xml:space="preserve">Britain</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warship and treasure escort</t>
+          <t xml:space="preserve">Cruiser, escort and patrol</t>
         </is>
       </c>
       <c r="T46">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="U46">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="V46">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="W46">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="X46">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Y46">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Z46">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA46">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="AB46">
-        <v>700</v>
+        <v>520</v>
       </c>
       <c r="AC46">
-        <v>900</v>
+        <v>660</v>
       </c>
       <c r="AD46">
+        <v>4</v>
+      </c>
+      <c r="AE46">
         <v>3</v>
-      </c>
-      <c r="AE46">
-        <v>4</v>
       </c>
       <c r="AF46">
         <v>3</v>
       </c>
       <c r="AG46">
+        <v>3</v>
+      </c>
+      <c r="AH46">
+        <v>2</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>1.2</v>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1-2</t>
+        </is>
+      </c>
+      <c r="AL46">
         <v>4</v>
       </c>
-      <c r="AH46">
-        <v>4</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Square gallery</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>0.95</v>
-      </c>
-      <c r="AK46">
-        <v>2</v>
-      </c>
-      <c r="AL46">
-        <v>5</v>
-      </c>
       <c r="AM46">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AN46">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -10736,57 +10454,52 @@
         <v>1</v>
       </c>
       <c r="AQ46">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="AR46">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AS46">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AT46">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="AU46">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">fifthRate</t>
+          <t xml:space="preserve">raceGalleon</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5th rate</t>
+          <t xml:space="preserve">Race-built galleon</t>
         </is>
       </c>
       <c r="D47">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="E47">
-        <v>1235</v>
+        <v>729</v>
       </c>
       <c r="F47">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H47">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="I47">
-        <v>2.77</v>
+        <v>1.82</v>
       </c>
       <c r="J47">
-        <v>6.47</v>
+        <v>3.8</v>
       </c>
       <c r="K47">
         <v>10</v>
@@ -10795,11 +10508,11 @@
         <v>2</v>
       </c>
       <c r="M47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/large fore/heavy main/heavy mizzen/large</t>
+          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -10809,48 +10522,48 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740-1840</t>
+          <t xml:space="preserve">1570-1620</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">England</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cruiser and commerce war</t>
+          <t xml:space="preserve">Line and cruiser warship</t>
         </is>
       </c>
       <c r="T47">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="U47">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="V47">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="W47">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X47">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y47">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z47">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AB47">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AC47">
-        <v>1200</v>
+        <v>640</v>
       </c>
       <c r="AD47">
         <v>4</v>
@@ -10862,18 +10575,18 @@
         <v>3</v>
       </c>
       <c r="AG47">
+        <v>4</v>
+      </c>
+      <c r="AH47">
         <v>3</v>
       </c>
-      <c r="AH47">
-        <v>2</v>
-      </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gallery</t>
+          <t xml:space="preserve">Square gallery</t>
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AK47">
         <v>2</v>
@@ -10885,7 +10598,7 @@
         <v>2.75</v>
       </c>
       <c r="AN47">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -10896,216 +10609,221 @@
         <v>1</v>
       </c>
       <c r="AQ47">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AR47">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AS47">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AT47">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="AU47">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">clipper</t>
+          <t xml:space="preserve">galleon</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armed clipper</t>
+          <t xml:space="preserve">Galleon</t>
         </is>
       </c>
       <c r="D48">
-        <v>10500</v>
+        <v>26500</v>
       </c>
       <c r="E48">
-        <v>1609</v>
+        <v>976</v>
       </c>
       <c r="F48">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="G48">
-        <v>1.15</v>
+        <v>0.73</v>
       </c>
       <c r="H48">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="I48">
-        <v>3.07</v>
+        <v>2.29</v>
       </c>
       <c r="J48">
-        <v>5.38</v>
+        <v>5.89</v>
       </c>
       <c r="K48">
+        <v>12</v>
+      </c>
+      <c r="L48">
+        <v>2</v>
+      </c>
+      <c r="M48">
+        <v>5</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium bonaventure/small</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1550-1650</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spain and Portugal</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warship and treasure escort</t>
+        </is>
+      </c>
+      <c r="T48">
+        <v>130</v>
+      </c>
+      <c r="U48">
+        <v>118</v>
+      </c>
+      <c r="V48">
+        <v>38</v>
+      </c>
+      <c r="W48">
+        <v>17</v>
+      </c>
+      <c r="X48">
+        <v>18</v>
+      </c>
+      <c r="Y48">
+        <v>12</v>
+      </c>
+      <c r="Z48">
+        <v>3.4</v>
+      </c>
+      <c r="AA48">
+        <v>2.2</v>
+      </c>
+      <c r="AB48">
+        <v>700</v>
+      </c>
+      <c r="AC48">
+        <v>900</v>
+      </c>
+      <c r="AD48">
         <v>3</v>
       </c>
-      <c r="L48">
-        <v>1</v>
-      </c>
-      <c r="M48">
-        <v>1</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bowsprit/large fore/heavy main/heavy mizzen/large</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1840-1865</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">China trade</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fast armed trader</t>
-        </is>
-      </c>
-      <c r="T48">
-        <v>200</v>
-      </c>
-      <c r="U48">
-        <v>180</v>
-      </c>
-      <c r="V48">
-        <v>40</v>
-      </c>
-      <c r="W48">
-        <v>21</v>
-      </c>
-      <c r="X48">
-        <v>21</v>
-      </c>
-      <c r="Y48">
-        <v>7</v>
-      </c>
-      <c r="Z48">
-        <v>5</v>
-      </c>
-      <c r="AA48">
-        <v>1.9</v>
-      </c>
-      <c r="AB48">
-        <v>1100</v>
-      </c>
-      <c r="AC48">
-        <v>1400</v>
-      </c>
-      <c r="AD48">
-        <v>5</v>
-      </c>
       <c r="AE48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF48">
+        <v>3</v>
+      </c>
+      <c r="AG48">
         <v>4</v>
       </c>
-      <c r="AG48">
-        <v>3</v>
-      </c>
       <c r="AH48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elliptical</t>
+          <t xml:space="preserve">Square gallery</t>
         </is>
       </c>
       <c r="AJ48">
-        <v>1.5</v>
+        <v>0.95</v>
       </c>
       <c r="AK48">
         <v>2</v>
       </c>
       <c r="AL48">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AM48">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AN48">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teak</t>
+          <t xml:space="preserve">Oak</t>
         </is>
       </c>
       <c r="AP48">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AQ48">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="AR48">
+        <v>4</v>
+      </c>
+      <c r="AS48">
+        <v>8</v>
+      </c>
+      <c r="AT48">
+        <v>43</v>
+      </c>
+      <c r="AU48">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fifthRate</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5th rate</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>24000</v>
+      </c>
+      <c r="E49">
+        <v>1235</v>
+      </c>
+      <c r="F49">
+        <v>300</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>0.83</v>
+      </c>
+      <c r="I49">
+        <v>2.77</v>
+      </c>
+      <c r="J49">
+        <v>6.47</v>
+      </c>
+      <c r="K49">
         <v>10</v>
-      </c>
-      <c r="AS48">
-        <v>16</v>
-      </c>
-      <c r="AT48">
-        <v>59</v>
-      </c>
-      <c r="AU48">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eastIndiaman</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">East Indiaman</t>
-        </is>
-      </c>
-      <c r="D49">
-        <v>22500</v>
-      </c>
-      <c r="E49">
-        <v>1698</v>
-      </c>
-      <c r="F49">
-        <v>220</v>
-      </c>
-      <c r="G49">
-        <v>0.79</v>
-      </c>
-      <c r="H49">
-        <v>0.7</v>
-      </c>
-      <c r="I49">
-        <v>3.22</v>
-      </c>
-      <c r="J49">
-        <v>7.22</v>
-      </c>
-      <c r="K49">
-        <v>8</v>
       </c>
       <c r="L49">
         <v>2</v>
       </c>
       <c r="M49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -11119,63 +10837,63 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690-1830</t>
+          <t xml:space="preserve">1740-1840</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britain</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armed trader and convoy</t>
+          <t xml:space="preserve">Cruiser and commerce war</t>
         </is>
       </c>
       <c r="T49">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="U49">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="V49">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="W49">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="X49">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Y49">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z49">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA49">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AB49">
+        <v>950</v>
+      </c>
+      <c r="AC49">
         <v>1200</v>
       </c>
-      <c r="AC49">
-        <v>1500</v>
-      </c>
       <c r="AD49">
+        <v>4</v>
+      </c>
+      <c r="AE49">
         <v>3</v>
       </c>
-      <c r="AE49">
-        <v>4</v>
-      </c>
       <c r="AF49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG49">
         <v>3</v>
       </c>
       <c r="AH49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
@@ -11183,89 +10901,84 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK49">
         <v>2</v>
       </c>
       <c r="AL49">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AM49">
+        <v>2.75</v>
+      </c>
+      <c r="AN49">
+        <v>1.9</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AP49">
+        <v>1</v>
+      </c>
+      <c r="AQ49">
+        <v>200</v>
+      </c>
+      <c r="AR49">
+        <v>8</v>
+      </c>
+      <c r="AS49">
+        <v>13</v>
+      </c>
+      <c r="AT49">
+        <v>59</v>
+      </c>
+      <c r="AU49">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clipper</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armed clipper</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>10500</v>
+      </c>
+      <c r="E50">
+        <v>1609</v>
+      </c>
+      <c r="F50">
+        <v>120</v>
+      </c>
+      <c r="G50">
+        <v>1.15</v>
+      </c>
+      <c r="H50">
+        <v>0.87</v>
+      </c>
+      <c r="I50">
+        <v>3.07</v>
+      </c>
+      <c r="J50">
+        <v>5.38</v>
+      </c>
+      <c r="K50">
         <v>3</v>
       </c>
-      <c r="AN49">
-        <v>2</v>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Teak</t>
-        </is>
-      </c>
-      <c r="AP49">
-        <v>1.12</v>
-      </c>
-      <c r="AQ49">
-        <v>80</v>
-      </c>
-      <c r="AR49">
-        <v>5</v>
-      </c>
-      <c r="AS49">
-        <v>9</v>
-      </c>
-      <c r="AT49">
-        <v>41</v>
-      </c>
-      <c r="AU49">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">heavyFrigate</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heavy frigate</t>
-        </is>
-      </c>
-      <c r="D50">
-        <v>54000</v>
-      </c>
-      <c r="E50">
-        <v>2230</v>
-      </c>
-      <c r="F50">
-        <v>480</v>
-      </c>
-      <c r="G50">
-        <v>1.03</v>
-      </c>
-      <c r="H50">
-        <v>0.74</v>
-      </c>
-      <c r="I50">
-        <v>3.77</v>
-      </c>
-      <c r="J50">
-        <v>8.24</v>
-      </c>
-      <c r="K50">
-        <v>13</v>
-      </c>
       <c r="L50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -11279,148 +10992,148 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1794-1855</t>
+          <t xml:space="preserve">1840-1865</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t xml:space="preserve">United States</t>
+          <t xml:space="preserve">China trade</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Super cruiser and duellist</t>
+          <t xml:space="preserve">Fast armed trader</t>
         </is>
       </c>
       <c r="T50">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="U50">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="V50">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="W50">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="X50">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Y50">
         <v>7</v>
       </c>
       <c r="Z50">
+        <v>5</v>
+      </c>
+      <c r="AA50">
+        <v>1.9</v>
+      </c>
+      <c r="AB50">
+        <v>1100</v>
+      </c>
+      <c r="AC50">
+        <v>1400</v>
+      </c>
+      <c r="AD50">
+        <v>5</v>
+      </c>
+      <c r="AE50">
+        <v>2</v>
+      </c>
+      <c r="AF50">
         <v>4</v>
-      </c>
-      <c r="AA50">
-        <v>3.1</v>
-      </c>
-      <c r="AB50">
-        <v>1500</v>
-      </c>
-      <c r="AC50">
-        <v>1900</v>
-      </c>
-      <c r="AD50">
-        <v>4</v>
-      </c>
-      <c r="AE50">
-        <v>3</v>
-      </c>
-      <c r="AF50">
-        <v>3</v>
       </c>
       <c r="AG50">
         <v>3</v>
       </c>
       <c r="AH50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gallery</t>
+          <t xml:space="preserve">Elliptical</t>
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK50">
         <v>2</v>
       </c>
       <c r="AL50">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AM50">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AN50">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Live oak</t>
+          <t xml:space="preserve">Teak</t>
         </is>
       </c>
       <c r="AP50">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AQ50">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="AR50">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS50">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AT50">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="AU50">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">razee</t>
+          <t xml:space="preserve">eastIndiaman</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Razee frigate</t>
+          <t xml:space="preserve">East Indiaman</t>
         </is>
       </c>
       <c r="D51">
-        <v>43000</v>
+        <v>22500</v>
       </c>
       <c r="E51">
-        <v>1827</v>
+        <v>1698</v>
       </c>
       <c r="F51">
-        <v>480</v>
+        <v>220</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="H51">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="I51">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="J51">
-        <v>9</v>
+        <v>7.22</v>
       </c>
       <c r="K51">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L51">
         <v>2</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -11434,7 +11147,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1794-1845</t>
+          <t xml:space="preserve">1690-1830</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -11444,53 +11157,53 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heavy cruiser, cut down</t>
+          <t xml:space="preserve">Armed trader and convoy</t>
         </is>
       </c>
       <c r="T51">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="U51">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="V51">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="W51">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="X51">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y51">
         <v>8</v>
       </c>
       <c r="Z51">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA51">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB51">
-        <v>1450</v>
+        <v>1200</v>
       </c>
       <c r="AC51">
-        <v>1850</v>
+        <v>1500</v>
       </c>
       <c r="AD51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE51">
         <v>4</v>
       </c>
       <c r="AF51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG51">
         <v>3</v>
       </c>
       <c r="AH51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
@@ -11498,42 +11211,42 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK51">
         <v>2</v>
       </c>
       <c r="AL51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM51">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AN51">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oak</t>
+          <t xml:space="preserve">Teak</t>
         </is>
       </c>
       <c r="AP51">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ51">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="AR51">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AS51">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AT51">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="AU51">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52">
@@ -11544,37 +11257,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">fourthRate</t>
+          <t xml:space="preserve">heavyFrigate</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4th rate</t>
+          <t xml:space="preserve">Heavy frigate</t>
         </is>
       </c>
       <c r="D52">
-        <v>37500</v>
+        <v>54000</v>
       </c>
       <c r="E52">
-        <v>1379</v>
+        <v>2230</v>
       </c>
       <c r="F52">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="G52">
-        <v>0.85</v>
+        <v>1.03</v>
       </c>
       <c r="H52">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="I52">
-        <v>3</v>
+        <v>3.77</v>
       </c>
       <c r="J52">
-        <v>7.29</v>
+        <v>8.24</v>
       </c>
       <c r="K52">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L52">
         <v>2</v>
@@ -11594,63 +11307,63 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650-1780</t>
+          <t xml:space="preserve">1794-1855</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britain</t>
+          <t xml:space="preserve">United States</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Small liner and flag cruiser</t>
+          <t xml:space="preserve">Super cruiser and duellist</t>
         </is>
       </c>
       <c r="T52">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="U52">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="V52">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W52">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="X52">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Y52">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z52">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AA52">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB52">
-        <v>1050</v>
+        <v>1500</v>
       </c>
       <c r="AC52">
-        <v>1350</v>
+        <v>1900</v>
       </c>
       <c r="AD52">
+        <v>4</v>
+      </c>
+      <c r="AE52">
         <v>3</v>
-      </c>
-      <c r="AE52">
-        <v>4</v>
       </c>
       <c r="AF52">
         <v>3</v>
       </c>
       <c r="AG52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
@@ -11658,7 +11371,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
         <v>2</v>
@@ -11670,77 +11383,72 @@
         <v>3.25</v>
       </c>
       <c r="AN52">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oak</t>
+          <t xml:space="preserve">Live oak</t>
         </is>
       </c>
       <c r="AP52">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ52">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="AR52">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS52">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AT52">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AU52">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">thirdRate</t>
+          <t xml:space="preserve">razee</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3rd rate</t>
+          <t xml:space="preserve">Razee frigate</t>
         </is>
       </c>
       <c r="D53">
-        <v>78500</v>
+        <v>43000</v>
       </c>
       <c r="E53">
-        <v>2188</v>
+        <v>1827</v>
       </c>
       <c r="F53">
-        <v>720</v>
+        <v>480</v>
       </c>
       <c r="G53">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="I53">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="J53">
-        <v>9.83</v>
+        <v>9</v>
       </c>
       <c r="K53">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L53">
         <v>2</v>
       </c>
       <c r="M53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -11754,51 +11462,51 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1750-1860</t>
+          <t xml:space="preserve">1794-1845</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global</t>
+          <t xml:space="preserve">Britain</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Backbone of the line</t>
+          <t xml:space="preserve">Heavy cruiser, cut down</t>
         </is>
       </c>
       <c r="T53">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="U53">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="V53">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W53">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X53">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y53">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z53">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA53">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AB53">
-        <v>1700</v>
+        <v>1450</v>
       </c>
       <c r="AC53">
-        <v>2200</v>
+        <v>1850</v>
       </c>
       <c r="AD53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE53">
         <v>4</v>
@@ -11807,10 +11515,10 @@
         <v>3</v>
       </c>
       <c r="AG53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
@@ -11818,21 +11526,19 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.15</v>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2-3</t>
-        </is>
+        <v>1.2</v>
+      </c>
+      <c r="AK53">
+        <v>2</v>
       </c>
       <c r="AL53">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AM53">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AN53">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -11843,19 +11549,19 @@
         <v>1</v>
       </c>
       <c r="AQ53">
-        <v>500</v>
+        <v>280</v>
       </c>
       <c r="AR53">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS53">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AT53">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AU53">
-        <v>74</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54">
@@ -11866,43 +11572,43 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">secondRate</t>
+          <t xml:space="preserve">fourthRate</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2nd rate</t>
+          <t xml:space="preserve">4th rate</t>
         </is>
       </c>
       <c r="D54">
-        <v>104000</v>
+        <v>37500</v>
       </c>
       <c r="E54">
-        <v>2834</v>
+        <v>1379</v>
       </c>
       <c r="F54">
-        <v>850</v>
+        <v>420</v>
       </c>
       <c r="G54">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="H54">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="I54">
-        <v>4.99</v>
+        <v>3</v>
       </c>
       <c r="J54">
-        <v>11.5</v>
+        <v>7.29</v>
       </c>
       <c r="K54">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L54">
         <v>2</v>
       </c>
       <c r="M54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -11916,7 +11622,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690-1850</t>
+          <t xml:space="preserve">1650-1780</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -11926,44 +11632,44 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fleet flagship</t>
+          <t xml:space="preserve">Small liner and flag cruiser</t>
         </is>
       </c>
       <c r="T54">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="U54">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="V54">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="W54">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="X54">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Y54">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z54">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA54">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AB54">
-        <v>2200</v>
+        <v>1050</v>
       </c>
       <c r="AC54">
-        <v>2900</v>
+        <v>1350</v>
       </c>
       <c r="AD54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF54">
         <v>3</v>
@@ -11972,7 +11678,7 @@
         <v>4</v>
       </c>
       <c r="AH54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
@@ -11983,13 +11689,13 @@
         <v>1.1</v>
       </c>
       <c r="AK54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL54">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AM54">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="AN54">
         <v>2</v>
@@ -12003,19 +11709,19 @@
         <v>1</v>
       </c>
       <c r="AQ54">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="AR54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS54">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT54">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="AU54">
-        <v>98</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55">
@@ -12026,37 +11732,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">firstRate</t>
+          <t xml:space="preserve">thirdRate</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1st rate</t>
+          <t xml:space="preserve">3rd rate</t>
         </is>
       </c>
       <c r="D55">
-        <v>120000</v>
+        <v>78500</v>
       </c>
       <c r="E55">
-        <v>3290</v>
+        <v>2188</v>
       </c>
       <c r="F55">
-        <v>950</v>
+        <v>720</v>
       </c>
       <c r="G55">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="H55">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="I55">
-        <v>5.55</v>
+        <v>4.15</v>
       </c>
       <c r="J55">
-        <v>12.46</v>
+        <v>9.83</v>
       </c>
       <c r="K55">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L55">
         <v>2</v>
@@ -12076,54 +11782,54 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650-1860</t>
+          <t xml:space="preserve">1750-1860</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britain and France</t>
+          <t xml:space="preserve">Global</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fleet flagship</t>
+          <t xml:space="preserve">Backbone of the line</t>
         </is>
       </c>
       <c r="T55">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="U55">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="V55">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="W55">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="X55">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y55">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z55">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AA55">
         <v>2.3</v>
       </c>
       <c r="AB55">
-        <v>2500</v>
+        <v>1700</v>
       </c>
       <c r="AC55">
-        <v>3400</v>
+        <v>2200</v>
       </c>
       <c r="AD55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF55">
         <v>3</v>
@@ -12132,24 +11838,26 @@
         <v>4</v>
       </c>
       <c r="AH55">
+        <v>3</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gallery</t>
+        </is>
+      </c>
+      <c r="AJ55">
+        <v>1.15</v>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-3</t>
+        </is>
+      </c>
+      <c r="AL55">
+        <v>6.5</v>
+      </c>
+      <c r="AM55">
         <v>4</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gallery</t>
-        </is>
-      </c>
-      <c r="AJ55">
-        <v>1.1</v>
-      </c>
-      <c r="AK55">
-        <v>3</v>
-      </c>
-      <c r="AL55">
-        <v>7.5</v>
-      </c>
-      <c r="AM55">
-        <v>5</v>
       </c>
       <c r="AN55">
         <v>2</v>
@@ -12163,18 +11871,338 @@
         <v>1</v>
       </c>
       <c r="AQ55">
+        <v>500</v>
+      </c>
+      <c r="AR55">
+        <v>6</v>
+      </c>
+      <c r="AS55">
+        <v>10</v>
+      </c>
+      <c r="AT55">
+        <v>45</v>
+      </c>
+      <c r="AU55">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">secondRate</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2nd rate</t>
+        </is>
+      </c>
+      <c r="D56">
+        <v>104000</v>
+      </c>
+      <c r="E56">
+        <v>2834</v>
+      </c>
+      <c r="F56">
+        <v>850</v>
+      </c>
+      <c r="G56">
+        <v>0.79</v>
+      </c>
+      <c r="H56">
+        <v>0.68</v>
+      </c>
+      <c r="I56">
+        <v>4.99</v>
+      </c>
+      <c r="J56">
+        <v>11.5</v>
+      </c>
+      <c r="K56">
+        <v>20</v>
+      </c>
+      <c r="L56">
+        <v>2</v>
+      </c>
+      <c r="M56">
+        <v>6</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowsprit/large fore/heavy main/heavy mizzen/large</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1690-1850</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britain</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fleet flagship</t>
+        </is>
+      </c>
+      <c r="T56">
+        <v>195</v>
+      </c>
+      <c r="U56">
+        <v>185</v>
+      </c>
+      <c r="V56">
+        <v>51</v>
+      </c>
+      <c r="W56">
+        <v>22</v>
+      </c>
+      <c r="X56">
+        <v>23</v>
+      </c>
+      <c r="Y56">
+        <v>12</v>
+      </c>
+      <c r="Z56">
+        <v>3.8</v>
+      </c>
+      <c r="AA56">
+        <v>2.3</v>
+      </c>
+      <c r="AB56">
+        <v>2200</v>
+      </c>
+      <c r="AC56">
+        <v>2900</v>
+      </c>
+      <c r="AD56">
+        <v>2</v>
+      </c>
+      <c r="AE56">
+        <v>5</v>
+      </c>
+      <c r="AF56">
+        <v>3</v>
+      </c>
+      <c r="AG56">
+        <v>4</v>
+      </c>
+      <c r="AH56">
+        <v>4</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gallery</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>1.1</v>
+      </c>
+      <c r="AK56">
+        <v>3</v>
+      </c>
+      <c r="AL56">
+        <v>7</v>
+      </c>
+      <c r="AM56">
+        <v>4.5</v>
+      </c>
+      <c r="AN56">
+        <v>2</v>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AP56">
+        <v>1</v>
+      </c>
+      <c r="AQ56">
+        <v>650</v>
+      </c>
+      <c r="AR56">
+        <v>5</v>
+      </c>
+      <c r="AS56">
+        <v>9</v>
+      </c>
+      <c r="AT56">
+        <v>41</v>
+      </c>
+      <c r="AU56">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firstRate</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1st rate</t>
+        </is>
+      </c>
+      <c r="D57">
+        <v>120000</v>
+      </c>
+      <c r="E57">
+        <v>3290</v>
+      </c>
+      <c r="F57">
+        <v>950</v>
+      </c>
+      <c r="G57">
+        <v>0.79</v>
+      </c>
+      <c r="H57">
+        <v>0.62</v>
+      </c>
+      <c r="I57">
+        <v>5.55</v>
+      </c>
+      <c r="J57">
+        <v>12.46</v>
+      </c>
+      <c r="K57">
+        <v>20</v>
+      </c>
+      <c r="L57">
+        <v>2</v>
+      </c>
+      <c r="M57">
+        <v>6</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowsprit/large fore/heavy main/heavy mizzen/large</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1650-1860</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britain and France</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fleet flagship</t>
+        </is>
+      </c>
+      <c r="T57">
+        <v>205</v>
+      </c>
+      <c r="U57">
+        <v>195</v>
+      </c>
+      <c r="V57">
+        <v>53</v>
+      </c>
+      <c r="W57">
+        <v>23</v>
+      </c>
+      <c r="X57">
+        <v>24</v>
+      </c>
+      <c r="Y57">
+        <v>13</v>
+      </c>
+      <c r="Z57">
+        <v>3.9</v>
+      </c>
+      <c r="AA57">
+        <v>2.3</v>
+      </c>
+      <c r="AB57">
+        <v>2500</v>
+      </c>
+      <c r="AC57">
+        <v>3400</v>
+      </c>
+      <c r="AD57">
+        <v>2</v>
+      </c>
+      <c r="AE57">
+        <v>5</v>
+      </c>
+      <c r="AF57">
+        <v>3</v>
+      </c>
+      <c r="AG57">
+        <v>4</v>
+      </c>
+      <c r="AH57">
+        <v>4</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gallery</t>
+        </is>
+      </c>
+      <c r="AJ57">
+        <v>1.1</v>
+      </c>
+      <c r="AK57">
+        <v>3</v>
+      </c>
+      <c r="AL57">
+        <v>7.5</v>
+      </c>
+      <c r="AM57">
+        <v>5</v>
+      </c>
+      <c r="AN57">
+        <v>2</v>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oak</t>
+        </is>
+      </c>
+      <c r="AP57">
+        <v>1</v>
+      </c>
+      <c r="AQ57">
         <v>750</v>
       </c>
-      <c r="AR55">
+      <c r="AR57">
         <v>5</v>
       </c>
-      <c r="AS55">
+      <c r="AS57">
         <v>9</v>
       </c>
-      <c r="AT55">
+      <c r="AT57">
         <v>38</v>
       </c>
-      <c r="AU55">
+      <c r="AU57">
         <v>104</v>
       </c>
     </row>

--- a/data/ships.xlsx
+++ b/data/ships.xlsx
@@ -827,21 +827,21 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">decks       (drawn) how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is</t>
+          <t xml:space="preserve">decks       how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is not a</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">            not a number. It is how many tiers her ports are drawn on, the last figure counting, so</t>
+          <t xml:space="preserve">            number. Recorded description now: `battery` says deck by deck where her guns actually</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">            a 2-3 is a three-decker and her battery is split three ways up her side.</t>
+          <t xml:space="preserve">            stood, and that is what her ports are drawn from.</t>
         </is>
       </c>
     </row>
@@ -918,712 +918,803 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">histGuns    (drawn) how many guns she really carried, of every sort. She shows HALF OF THEM as</t>
+          <t xml:space="preserve">histGuns    (drawn) how many guns she really carried, of every sort. Half of them is exactly her</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">            gunports a side, spread over the tiers `decks` gives her, so a first rate's hundred</t>
+          <t xml:space="preserve">            `broadside` bearing for every class in the fleet, which is how the ports and the guns</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">            guns are fifty ports a side over three decks. That half is exactly her `broadside`</t>
+          <t xml:space="preserve">            that fire out of them agree without the catalogue and the reference ever meeting.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">            bearing for every class in the fleet, which is how the ports and the guns that fire</t>
+          <t xml:space="preserve">            `battery` says where those guns stood and has to add up to this.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">            out of them agree without the catalogue and the reference ever meeting.</t>
+          <t xml:space="preserve">battery     (drawn) her establishment, deck by deck, as guns aboard rather than a side. Gun decks</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            first and lowest deck first, then what she carried on her upper works after a plus:</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masts, from data/masts.tsv</t>
+          <t xml:space="preserve">            "10" is a cutter's ten on one open deck, "28+8/2" a frigate with a gun deck of 28 and</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            ten more on her quarterdeck and forecastle, "28/28/30+12/2" a first rate. The figures</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE MASTS. One row per type, and a type is a SHAPE OF RIG, not a size.</t>
+          <t xml:space="preserve">            sum to histGuns and every gun deck takes an even number, half of them a side.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+          <t xml:space="preserve">            A GUN DECK AND AN UPPER WORKS ARE NOT THE SAME FITTING, which is the whole reason this</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            column exists. A gun deck is a continuous battery pierced through her side, so its</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">A mast's berths are fixed the moment it is built and never change. That is the whole point of the</t>
+          <t xml:space="preserve">            ports run the length of her, under the castles the way a lower deck really did. Her</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">part: buying a mast is choosing what she will be able to carry, so a mast with one lugsail berth</t>
+          <t xml:space="preserve">            quarterdeck and forecastle guns stood in the open behind a bulwark, with no lidded</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">will never carry two square ones however much a captain spends. It is why the fleet wants a type</t>
+          <t xml:space="preserve">            port to show, and drawn as such they are what leaves a two-decker's waist empty.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">per configuration rather than one mast with a number of slots.</t>
+          <t xml:space="preserve">            After the plus, two figures are the quarterdeck and the forecastle in that order, with</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            her waist bare between them. One figure is a battery that ran the whole length of her</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">A TYPE IS NOT TIED TO A STATION. A mast that carries three square sails is that mast wherever she</t>
+          <t xml:space="preserve">            upper works, which is what a spar-decked heavy frigate had. Write "2/0" rather than</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">steps it, so the fore and main of a brig are one part bought twice rather than two parts. What</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">decides where it can go is the size rung and nothing else.</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BERTHS RUN DECK UPWARD, and a fore-and-aft driving sail sharing the lowest level with a course</t>
+          <t xml:space="preserve">            "2" for a ship who carried hers aft only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Masts, from data/masts.tsv</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">takes berth 0 with the square canvas above it. A spanker and a course are both set at the deck, one</t>
+          <t xml:space="preserve">THE MASTS. One row per type, and a type is a SHAPE OF RIG, not a size.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">abaft the mast and one on a yard across it, and the model has one sail to a band: putting the</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spanker lowest is what keeps a brig's rig reading bottom to top the way she is really rigged.</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A mast's berths are fixed the moment it is built and never change. That is the whole point of the</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">id       short camelCase name, unique.</t>
+          <t xml:space="preserve">part: buying a mast is choosing what she will be able to carry, so a mast with one lugsail berth</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">name     what a captain reads.</t>
+          <t xml:space="preserve">will never carry two square ones however much a captain spends. It is why the fleet wants a type</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">price    coins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">size     the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor</t>
+          <t xml:space="preserve">per configuration rather than one mast with a number of slots.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">         choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
+          <t xml:space="preserve">A TYPE IS NOT TIED TO A STATION. A mast that carries three square sails is that mast wherever she</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">spar     yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the</t>
+          <t xml:space="preserve">steps it, so the fore and main of a brig are one part bought twice rather than two parts. What</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">         bowsprit and nowhere else. A spar and a mast are different sorts of thing and are</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         matched as such, or a jibboom would be legal as somebody's main mast.</t>
+          <t xml:space="preserve">decides where it can go is the size rung and nothing else.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">height   how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts</t>
+          <t xml:space="preserve">BERTHS RUN DECK UPWARD, and a fore-and-aft driving sail sharing the lowest level with a course</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">         the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
+          <t xml:space="preserve">takes berth 0 with the square canvas above it. A spanker and a course are both set at the deck, one</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">berths   the sails she can carry, DECK UPWARD, as category labels separated by spaces.</t>
+          <t xml:space="preserve">abaft the mast and one on a yard across it, and the model has one sail to a band: putting the</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">         LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         Five is the most the renderer can place up one mast in bands of their own, and the bench</t>
+          <t xml:space="preserve">spanker lowest is what keeps a brig's rig reading bottom to top the way she is really rigged.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">         fails a mast that asks for more.</t>
+          <t xml:space="preserve">id       short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">         STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set,</t>
+          <t xml:space="preserve">name     what a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">         so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
+          <t xml:space="preserve">price    coins.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb    one line a captain reads.</t>
+          <t xml:space="preserve">size     the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sails, from data/sails.tsv</t>
+          <t xml:space="preserve">spar     yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         bowsprit and nowhere else. A spar and a mast are different sorts of thing and are</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE SAILS. One row per sail a captain can buy.</t>
+          <t xml:space="preserve">         matched as such, or a jibboom would be legal as somebody's main mast.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+          <t xml:space="preserve">height   how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">A sail belongs to ONE category and fits a berth of that category. That is the whole fitting rule.</t>
+          <t xml:space="preserve">berths   the sails she can carry, DECK UPWARD, as category labels separated by spaces.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Area is not the category: a topgallant is nearly four times a skysail and both are SSQ.</t>
+          <t xml:space="preserve">         LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         Five is the most the renderer can place up one mast in bands of their own, and the bench</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LSQ  Large square    courses, lower topsails            driving power, low on the mast</t>
+          <t xml:space="preserve">         fails a mast that asks for more.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SSQ  Small square    topgallants, royals, skysails,     light-air lift, high up</t>
+          <t xml:space="preserve">         STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set,</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       spritsails, sprit-topsails</t>
+          <t xml:space="preserve">         so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TRI  Headsail        jibs, flying jibs, staysails       set on a stay forward: balance, pointing</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  LAT  Lateen          lateen yards, Bermuda mainsails    triangular canvas driving from a mast</t>
+          <t xml:space="preserve">blurb    one line a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">  GAF  Gaff            gaff mainsails, spankers,          fore-and-aft drive aft, manoeuvre</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                       drivers, trysails, gaff topsails</t>
+          <t xml:space="preserve">Sails, from data/sails.tsv</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LUG  Lugsail         dipping and standing lug,          the main drive of a lugger</t>
+          <t xml:space="preserve">THE SAILS. One row per sail a captain can buy.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       lug topsail</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STU  Studdingsail    boomed-out extensions             ADDITIVE. Not a berth: see below.</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A sail belongs to ONE category and fits a berth of that category. That is the whole fitting rule.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">A LATEEN IS NOT A HEADSAIL. Both are triangles and they were one category until the bowsprit became</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a station: the moment a jib had a berth of its own a lateen fitted it and pulled better, so the</t>
+          <t xml:space="preserve">Area is not the category: a topgallant is nearly four times a skysail and both are SSQ.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice made itself. They do different work, so they are different categories.</t>
+          <t xml:space="preserve">  LSQ  Large square    courses, lower topsails            driving power, low on the mast</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SSQ  Small square    topgallants, royals, skysails,     light-air lift, high up</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU does not go in a berth. A studdingsail booms out beyond a square sail that is already set and</t>
+          <t xml:space="preserve">                       spritsails, sprit-topsails</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">its area comes off that sail, so it is an attachment rather than a place in the rig: a square sail</t>
+          <t xml:space="preserve">  TRI  Headsail        jibs, flying jibs, staysails       set on a stay forward: balance, pointing</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">carries at most one, matched by LEVEL, and `npm run catalogue` still refuses a berth that asks for</t>
+          <t xml:space="preserve">  LAT  Lateen          lateen yards, Bermuda mainsails    triangular canvas driving from a mast</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">one, deliberately, so that a mast cannot pretend to carry studdingsails in a slot.</t>
+          <t xml:space="preserve">  GAF  Gaff            gaff mainsails, spankers,          fore-and-aft drive aft, manoeuvre</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                       drivers, trysails, gaff topsails</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">id      short camelCase name, unique.</t>
+          <t xml:space="preserve">  LUG  Lugsail         dipping and standing lug,          the main drive of a lugger</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">name    what a captain reads.</t>
+          <t xml:space="preserve">                       lug topsail</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind    one of the seven labels above.</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">price   coins.</t>
+          <t xml:space="preserve">  STU  Studdingsail    boomed-out extensions             ADDITIVE. Not a berth: see below.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">drive   what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area</t>
+          <t xml:space="preserve">A LATEEN IS NOT A HEADSAIL. Both are triangles and they were one category until the bowsprit became</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">        is where this number starts and the proportions are: course 1.00, lower topsail 0.70,</t>
+          <t xml:space="preserve">a station: the moment a jib had a berth of its own a lateen fitted it and pulled better, so the</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">        topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it,</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        which is why two sails of one area can differ here.</t>
+          <t xml:space="preserve">choice made itself. They do different work, so they are different categories.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">        FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80),</t>
+          <t xml:space="preserve">STU does not go in a berth. A studdingsail booms out beyond a square sail that is already set and</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">        because its area comes off that sail rather than off a place in the rig.</t>
+          <t xml:space="preserve">its area comes off that sail, so it is an attachment rather than a place in the rig: a square sail</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">hand    what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft</t>
+          <t xml:space="preserve">carries at most one, matched by LEVEL, and `npm run catalogue` still refuses a berth that asks for</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">        canvas helps her round, so it is positive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">level   STU only, and blank everywhere else. Which square sail up the mast it booms out from,</t>
+          <t xml:space="preserve">one, deliberately, so that a mast cannot pretend to carry studdingsails in a slot.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">        counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it;</t>
+          <t xml:space="preserve">id      short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2 the topgallant. The berth number is not the level, because a driver mast's course sits</t>
+          <t xml:space="preserve">name    what a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">        at berth 1 with a spanker under it.</t>
+          <t xml:space="preserve">kind    one of the seven labels above.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb   one line a captain reads.</t>
+          <t xml:space="preserve">price   coins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">drive   what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two grades of most of them: the plain one a captain can afford early, and a fine one in heavier</t>
+          <t xml:space="preserve">        is where this number starts and the proportions are: course 1.00, lower topsail 0.70,</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">cloth that is strictly better and priced for it. Prices are placed against each other and have not</t>
+          <t xml:space="preserve">        topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it,</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t xml:space="preserve">been tuned against what a voyage actually pays.</t>
+          <t xml:space="preserve">        which is why two sails of one area can differ here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80),</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guns, from data/guns.tsv</t>
+          <t xml:space="preserve">        because its area comes off that sail rather than off a place in the rig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hand    what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE GUNS. One row per piece a captain can buy.</t>
+          <t xml:space="preserve">        canvas helps her round, so it is positive.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+          <t xml:space="preserve">level   STU only, and blank everywhere else. Which square sail up the mast it booms out from,</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it;</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guns fit BY THE PIECE up to what the hull bears, and `mount` says which of her counts a gun draws</t>
+          <t xml:space="preserve">        2 the topgallant. The berth number is not the level, because a driver mast's course sits</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t xml:space="preserve">against. Broadside is counted A SIDE and mirrored, because that is how a volley fires: one</t>
+          <t xml:space="preserve">        at berth 1 with a spanker under it.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">carriage gun bought is one gun each side and two guns aboard.</t>
+          <t xml:space="preserve">blurb   one line a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Muskets are not in this table and never will be. Small arms come off the crew she musters, with the</t>
+          <t xml:space="preserve">Two grades of most of them: the plain one a captain can afford early, and a fine one in heavier</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t xml:space="preserve">swivels on her rail firing in the same volley, which is `rate()`'s business.</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id      short camelCase name, unique.</t>
+          <t xml:space="preserve">cloth that is strictly better and priced for it. Prices are placed against each other and have not</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">been tuned against what a voyage actually pays.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">name    what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`,</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing</t>
+          <t xml:space="preserve">Guns, from data/guns.tsv</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t xml:space="preserve">        them is arithmetic she should not have to do in words. It is the game's own rule about</t>
+          <t xml:space="preserve">THE GUNS. One row per piece a captain can buy.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t xml:space="preserve">        numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t xml:space="preserve">price   coins.</t>
+          <t xml:space="preserve">Guns fit BY THE PIECE up to what the hull bears, and `mount` says which of her counts a gun draws</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
+          <t xml:space="preserve">against. Broadside is counted A SIDE and mirrored, because that is how a volley fires: one</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
+          <t xml:space="preserve">carriage gun bought is one gun each side and two guns aboard.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t xml:space="preserve">        to leave a port empty.</t>
+          <t xml:space="preserve">Muskets are not in this table and never will be. Small arms come off the crew she musters, with the</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
+          <t xml:space="preserve">swivels on her rail firing in the same volley, which is `rate()`'s business.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+          <t xml:space="preserve">id      short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+          <t xml:space="preserve">name    what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`,</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        them is arithmetic she should not have to do in words. It is the game's own rule about</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price   coins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        to leave a port empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
         <is>
           <t xml:space="preserve">blurb   one line a captain reads.</t>
         </is>
@@ -2469,12 +2560,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Her drawing</t>
+          <t xml:space="preserve">Recorded only</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is not a number. It is how many tiers her ports are drawn on, the last figure counting, so a 2-3 is a three-decker and her battery is split three ways up her side.</t>
+          <t xml:space="preserve">how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is not a number. Recorded description now: `battery` says deck by deck where her guns actually stood, and that is what her ports are drawn from.</t>
         </is>
       </c>
     </row>
@@ -2694,29 +2785,29 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">how many guns she really carried, of every sort. She shows HALF OF THEM as gunports a side, spread over the tiers `decks` gives her, so a first rate's hundred guns are fifty ports a side over three decks. That half is exactly her `broadside` bearing for every class in the fleet, which is how the ports and the guns that fire out of them agree without the catalogue and the reference ever meeting.</t>
+          <t xml:space="preserve">how many guns she really carried, of every sort. Half of them is exactly her `broadside` bearing for every class in the fleet, which is how the ports and the guns that fire out of them agree without the catalogue and the reference ever meeting. `battery` says where those guns stood and has to add up to this.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masts</t>
+          <t xml:space="preserve">Hulls</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">battery</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">The fight</t>
+          <t xml:space="preserve">Her drawing</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">short camelCase name, unique.</t>
+          <t xml:space="preserve">her establishment, deck by deck, as guns aboard rather than a side. Gun decks first and lowest deck first, then what she carried on her upper works after a plus: "10" is a cutter's ten on one open deck, "28+8/2" a frigate with a gun deck of 28 and ten more on her quarterdeck and forecastle, "28/28/30+12/2" a first rate. The figures sum to histGuns and every gun deck takes an even number, half of them a side. A GUN DECK AND AN UPPER WORKS ARE NOT THE SAME FITTING, which is the whole reason this column exists. A gun deck is a continuous battery pierced through her side, so its ports run the length of her, under the castles the way a lower deck really did. Her quarterdeck and forecastle guns stood in the open behind a bulwark, with no lidded port to show, and drawn as such they are what leaves a two-decker's waist empty. After the plus, two figures are the quarterdeck and the forecastle in that order, with her waist bare between them. One figure is a battery that ran the whole length of her upper works, which is what a spar-decked heavy frigate had. Write "2/0" rather than "2" for a ship who carried hers aft only.</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2819,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2738,7 +2829,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">what a captain reads.</t>
+          <t xml:space="preserve">short camelCase name, unique.</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2841,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2760,7 +2851,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">coins.</t>
+          <t xml:space="preserve">what a captain reads.</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2863,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">size</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2782,7 +2873,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
+          <t xml:space="preserve">coins.</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2885,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">spar</t>
+          <t xml:space="preserve">size</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2804,7 +2895,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the bowsprit and nowhere else. A spar and a mast are different sorts of thing and are matched as such, or a jibboom would be legal as somebody's main mast.</t>
+          <t xml:space="preserve">the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2907,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">height</t>
+          <t xml:space="preserve">spar</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2826,7 +2917,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
+          <t xml:space="preserve">yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the bowsprit and nowhere else. A spar and a mast are different sorts of thing and are matched as such, or a jibboom would be legal as somebody's main mast.</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2929,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">berths</t>
+          <t xml:space="preserve">height</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2848,7 +2939,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">the sails she can carry, DECK UPWARD, as category labels separated by spaces. LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail Five is the most the renderer can place up one mast in bands of their own, and the bench fails a mast that asks for more. STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set, so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
+          <t xml:space="preserve">how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2951,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb</t>
+          <t xml:space="preserve">berths</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2870,19 +2961,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">one line a captain reads.</t>
+          <t xml:space="preserve">the sails she can carry, DECK UPWARD, as category labels separated by spaces. LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail Five is the most the renderer can place up one mast in bands of their own, and the bench fails a mast that asks for more. STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set, so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sails</t>
+          <t xml:space="preserve">Masts</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">blurb</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2892,7 +2983,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">short camelCase name, unique.</t>
+          <t xml:space="preserve">one line a captain reads.</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2995,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2914,7 +3005,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">what a captain reads.</t>
+          <t xml:space="preserve">short camelCase name, unique.</t>
         </is>
       </c>
     </row>
@@ -2926,7 +3017,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2936,7 +3027,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of the seven labels above.</t>
+          <t xml:space="preserve">what a captain reads.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +3039,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2958,7 +3049,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">coins.</t>
+          <t xml:space="preserve">one of the seven labels above.</t>
         </is>
       </c>
     </row>
@@ -2970,7 +3061,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">drive</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2980,7 +3071,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area is where this number starts and the proportions are: course 1.00, lower topsail 0.70, topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it, which is why two sails of one area can differ here. FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80), because its area comes off that sail rather than off a place in the rig.</t>
+          <t xml:space="preserve">coins.</t>
         </is>
       </c>
     </row>
@@ -2992,7 +3083,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">hand</t>
+          <t xml:space="preserve">drive</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3002,7 +3093,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft canvas helps her round, so it is positive.</t>
+          <t xml:space="preserve">what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area is where this number starts and the proportions are: course 1.00, lower topsail 0.70, topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it, which is why two sails of one area can differ here. FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80), because its area comes off that sail rather than off a place in the rig.</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3105,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">level</t>
+          <t xml:space="preserve">hand</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3024,7 +3115,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU only, and blank everywhere else. Which square sail up the mast it booms out from, counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it; 2 the topgallant. The berth number is not the level, because a driver mast's course sits at berth 1 with a spanker under it.</t>
+          <t xml:space="preserve">what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft canvas helps her round, so it is positive.</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3127,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb</t>
+          <t xml:space="preserve">level</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3046,19 +3137,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">one line a captain reads.</t>
+          <t xml:space="preserve">STU only, and blank everywhere else. Which square sail up the mast it booms out from, counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it; 2 the topgallant. The berth number is not the level, because a driver mast's course sits at berth 1 with a spanker under it.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guns</t>
+          <t xml:space="preserve">Sails</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">blurb</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3068,7 +3159,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">short camelCase name, unique.</t>
+          <t xml:space="preserve">one line a captain reads.</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3171,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3090,7 +3181,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`, not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing them is arithmetic she should not have to do in words. It is the game's own rule about numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
+          <t xml:space="preserve">short camelCase name, unique.</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3193,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">mount</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3112,7 +3203,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">broadside, bow or swivel.</t>
+          <t xml:space="preserve">what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`, not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing them is arithmetic she should not have to do in words. It is the game's own rule about numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3215,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">mount</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3134,7 +3225,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">coins.</t>
+          <t xml:space="preserve">broadside, bow or swivel.</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3237,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">damage</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3156,7 +3247,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">what one ball takes off a hull.</t>
+          <t xml:space="preserve">coins.</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3259,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">reload</t>
+          <t xml:space="preserve">damage</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3178,7 +3269,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
+          <t xml:space="preserve">what one ball takes off a hull.</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3281,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight</t>
+          <t xml:space="preserve">reload</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3200,7 +3291,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">what she carries for it. Enough of it takes the edge off her handling, which is the reason to leave a port empty.</t>
+          <t xml:space="preserve">seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3303,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">group</t>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3222,7 +3313,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">swivels only, and blank everywhere else. How true one throws, as a share of a musket's own scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel never adds a ball to the volley; what quality buys is that the volley hits harder and lands closer to where the bow points, and this is the second half of that.</t>
+          <t xml:space="preserve">what she carries for it. Enough of it takes the edge off her handling, which is the reason to leave a port empty.</t>
         </is>
       </c>
     </row>
@@ -3234,15 +3325,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t xml:space="preserve">group</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">swivels only, and blank everywhere else. How true one throws, as a share of a musket's own scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel never adds a ball to the volley; what quality buys is that the volley hits harder and lands closer to where the bow points, and this is the second half of that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t xml:space="preserve">blurb</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t xml:space="preserve">The fight</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t xml:space="preserve">one line a captain reads.</t>
         </is>
@@ -3302,6 +3415,7 @@
     <col min="45" max="45" width="10.00" customWidth="1"/>
     <col min="46" max="46" width="11.00" customWidth="1"/>
     <col min="47" max="47" width="10.00" customWidth="1"/>
+    <col min="48" max="48" width="15.00" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3540,6 +3654,11 @@
           <t xml:space="preserve">histGuns</t>
         </is>
       </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3705,6 +3824,9 @@
       <c r="AU2">
         <v>2</v>
       </c>
+      <c r="AV2">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3870,6 +3992,9 @@
       <c r="AU3">
         <v>6</v>
       </c>
+      <c r="AV3">
+        <v>6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4035,6 +4160,9 @@
       <c r="AU4">
         <v>8</v>
       </c>
+      <c r="AV4">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4200,6 +4328,9 @@
       <c r="AU5">
         <v>10</v>
       </c>
+      <c r="AV5">
+        <v>10</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4365,6 +4496,9 @@
       <c r="AU6">
         <v>12</v>
       </c>
+      <c r="AV6">
+        <v>12</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4530,6 +4664,9 @@
       <c r="AU7">
         <v>14</v>
       </c>
+      <c r="AV7">
+        <v>14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4695,6 +4832,9 @@
       <c r="AU8">
         <v>18</v>
       </c>
+      <c r="AV8">
+        <v>18</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4860,6 +5000,9 @@
       <c r="AU9">
         <v>20</v>
       </c>
+      <c r="AV9">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5025,6 +5168,11 @@
       <c r="AU10">
         <v>24</v>
       </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22+2/0</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5155,10 +5303,8 @@
       <c r="AJ11">
         <v>1.2</v>
       </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1-2</t>
-        </is>
+      <c r="AK11">
+        <v>1</v>
       </c>
       <c r="AL11">
         <v>3.5</v>
@@ -5192,6 +5338,9 @@
       <c r="AU11">
         <v>32</v>
       </c>
+      <c r="AV11">
+        <v>32</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5357,6 +5506,11 @@
       <c r="AU12">
         <v>38</v>
       </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28+8/2</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5522,6 +5676,11 @@
       <c r="AU13">
         <v>50</v>
       </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30+20</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5687,6 +5846,11 @@
       <c r="AU14">
         <v>54</v>
       </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24/22+6/2</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5852,6 +6016,11 @@
       <c r="AU15">
         <v>64</v>
       </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26/26+10/2</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6017,6 +6186,11 @@
       <c r="AU16">
         <v>90</v>
       </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26/26/26+10/2</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6181,6 +6355,11 @@
       </c>
       <c r="AU17">
         <v>100</v>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28/28/30+12/2</t>
+        </is>
       </c>
     </row>
     <row r="20">

--- a/data/ships.xlsx
+++ b/data/ships.xlsx
@@ -589,7 +589,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">`hullform.js` is the one reader. The thirteen marked (drawn) are how she is DRAWN, in the menu</t>
+          <t xml:space="preserve">`hullform.js` is the one reader. The fourteen marked (drawn) are how she is DRAWN, in the menu</t>
         </is>
       </c>
     </row>
@@ -862,181 +862,188 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">roomSpace   room and space, feet: from one frame to the next.</t>
+          <t xml:space="preserve">roomSpace   (drawn) room and space, feet: from one frame to the next. A gunport was framed on it,</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">species     (drawn) what she was built of, which is also her colour: Oak, Live oak, Teak, Cedar or</t>
+          <t xml:space="preserve">            running a little over one space wide, so this is the size of every port she shows.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Pine. Any other name is painted as oak.</t>
+          <t xml:space="preserve">species     (drawn) what she was built of, which is also her colour: Oak, Live oak, Teak, Cedar or</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">timber      (drawn) how dense that timber is, oak being 1. Denser timber reads a little darker.</t>
+          <t xml:space="preserve">            Pine. Any other name is painted as oak.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">crewMin     the fewest hands she could be worked with, as against the battle complement in `crew`.</t>
+          <t xml:space="preserve">timber      (drawn) how dense that timber is, oak being 1. Denser timber reads a little darker.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">cruise      her everyday speed, knots.</t>
+          <t xml:space="preserve">crewMin     the fewest hands she could be worked with, as against the battle complement in `crew`.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">topSpeed    the best she was ever driven, knots.</t>
+          <t xml:space="preserve">cruise      her everyday speed, knots.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">manoeuvre   how handy she was, 0 to 100. The reference's own score, and what `hand` came out of.</t>
+          <t xml:space="preserve">topSpeed    the best she was ever driven, knots.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">histGuns    (drawn) how many guns she really carried, of every sort. Half of them is exactly her</t>
+          <t xml:space="preserve">manoeuvre   how handy she was, 0 to 100. The reference's own score, and what `hand` came out of.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">            `broadside` bearing for every class in the fleet, which is how the ports and the guns</t>
+          <t xml:space="preserve">histGuns    (drawn) how many guns she really carried, of every sort. Half of them is exactly her</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">            that fire out of them agree without the catalogue and the reference ever meeting.</t>
+          <t xml:space="preserve">            `broadside` bearing for every class in the fleet, which is how the ports and the guns</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">            `battery` says where those guns stood and has to add up to this.</t>
+          <t xml:space="preserve">            that fire out of them agree without the catalogue and the reference ever meeting.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery     (drawn) her establishment, deck by deck, as guns aboard rather than a side. Gun decks</t>
+          <t xml:space="preserve">            `battery` says where those guns stood and has to add up to this.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">            first and lowest deck first, then what she carried on her upper works after a plus:</t>
+          <t xml:space="preserve">battery     (drawn) her establishment, deck by deck, as guns aboard rather than a side. Gun decks</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">            "10" is a cutter's ten on one open deck, "28+8/2" a frigate with a gun deck of 28 and</t>
+          <t xml:space="preserve">            first and lowest deck first, then what she carried on her upper works after a plus:</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ten more on her quarterdeck and forecastle, "28/28/30+12/2" a first rate. The figures</t>
+          <t xml:space="preserve">            "10" is a cutter's ten on one open deck, "28+8/2" a frigate with a gun deck of 28 and</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">            sum to histGuns and every gun deck takes an even number, half of them a side.</t>
+          <t xml:space="preserve">            ten more on her quarterdeck and forecastle, "28/28/30+12/2" a first rate. The figures</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">            A GUN DECK AND AN UPPER WORKS ARE NOT THE SAME FITTING, which is the whole reason this</t>
+          <t xml:space="preserve">            sum to histGuns and every gun deck takes an even number, half of them a side.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">            column exists. A gun deck is a continuous battery pierced through her side, so its</t>
+          <t xml:space="preserve">            A GUN DECK AND AN UPPER WORKS ARE NOT THE SAME FITTING, which is the whole reason this</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ports run the length of her, under the castles the way a lower deck really did. Her</t>
+          <t xml:space="preserve">            column exists. A gun deck is a continuous battery pierced through her side, so its</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">            quarterdeck and forecastle guns stood in the open behind a bulwark, with no lidded</t>
+          <t xml:space="preserve">            ports run the length of her, under the castles the way a lower deck really did. Her</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">            port to show, and drawn as such they are what leaves a two-decker's waist empty.</t>
+          <t xml:space="preserve">            quarterdeck and forecastle guns stood in the open behind a bulwark, with no lidded</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">            After the plus, two figures are the quarterdeck and the forecastle in that order, with</t>
+          <t xml:space="preserve">            port to show, and drawn as such they are what leaves a two-decker's waist empty.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">            her waist bare between them. One figure is a battery that ran the whole length of her</t>
+          <t xml:space="preserve">            After the plus, two figures are the quarterdeck and the forecastle in that order, with</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">            upper works, which is what a spar-decked heavy frigate had. Write "2/0" rather than</t>
+          <t xml:space="preserve">            her waist bare between them. One figure is a battery that ran the whole length of her</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
+          <t xml:space="preserve">            upper works, which is what a spar-decked heavy frigate had. Write "2/0" rather than</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
           <t xml:space="preserve">            "2" for a ship who carried hers aft only.</t>
         </is>
       </c>
@@ -1044,677 +1051,698 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masts, from data/masts.tsv</t>
+          <t xml:space="preserve">            A BOAT IS NOT PIERCED AT ALL. A lidded port is cut through her topside under the deck</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            above it, and a hull with a castle score of 1 has neither, so her whole battery is</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE MASTS. One row per type, and a type is a SHAPE OF RIG, not a size.</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A mast's berths are fixed the moment it is built and never change. That is the whole point of the</t>
+          <t xml:space="preserve">            drawn standing at her rail however this column is written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Masts, from data/masts.tsv</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">part: buying a mast is choosing what she will be able to carry, so a mast with one lugsail berth</t>
+          <t xml:space="preserve">THE MASTS. One row per type, and a type is a SHAPE OF RIG, not a size.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">will never carry two square ones however much a captain spends. It is why the fleet wants a type</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">per configuration rather than one mast with a number of slots.</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A mast's berths are fixed the moment it is built and never change. That is the whole point of the</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">A TYPE IS NOT TIED TO A STATION. A mast that carries three square sails is that mast wherever she</t>
+          <t xml:space="preserve">part: buying a mast is choosing what she will be able to carry, so a mast with one lugsail berth</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">steps it, so the fore and main of a brig are one part bought twice rather than two parts. What</t>
+          <t xml:space="preserve">will never carry two square ones however much a captain spends. It is why the fleet wants a type</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">decides where it can go is the size rung and nothing else.</t>
+          <t xml:space="preserve">per configuration rather than one mast with a number of slots.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERTHS RUN DECK UPWARD, and a fore-and-aft driving sail sharing the lowest level with a course</t>
+          <t xml:space="preserve">A TYPE IS NOT TIED TO A STATION. A mast that carries three square sails is that mast wherever she</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">takes berth 0 with the square canvas above it. A spanker and a course are both set at the deck, one</t>
+          <t xml:space="preserve">steps it, so the fore and main of a brig are one part bought twice rather than two parts. What</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">abaft the mast and one on a yard across it, and the model has one sail to a band: putting the</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spanker lowest is what keeps a brig's rig reading bottom to top the way she is really rigged.</t>
+          <t xml:space="preserve">decides where it can go is the size rung and nothing else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BERTHS RUN DECK UPWARD, and a fore-and-aft driving sail sharing the lowest level with a course</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">id       short camelCase name, unique.</t>
+          <t xml:space="preserve">takes berth 0 with the square canvas above it. A spanker and a course are both set at the deck, one</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">name     what a captain reads.</t>
+          <t xml:space="preserve">abaft the mast and one on a yard across it, and the model has one sail to a band: putting the</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">price    coins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">size     the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor</t>
+          <t xml:space="preserve">spanker lowest is what keeps a brig's rig reading bottom to top the way she is really rigged.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">         choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
+          <t xml:space="preserve">id       short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">spar     yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the</t>
+          <t xml:space="preserve">name     what a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">         bowsprit and nowhere else. A spar and a mast are different sorts of thing and are</t>
+          <t xml:space="preserve">price    coins.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">         matched as such, or a jibboom would be legal as somebody's main mast.</t>
+          <t xml:space="preserve">size     the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">height   how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts</t>
+          <t xml:space="preserve">         choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">         the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
+          <t xml:space="preserve">spar     yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">berths   the sails she can carry, DECK UPWARD, as category labels separated by spaces.</t>
+          <t xml:space="preserve">         bowsprit and nowhere else. A spar and a mast are different sorts of thing and are</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">         LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail</t>
+          <t xml:space="preserve">         matched as such, or a jibboom would be legal as somebody's main mast.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Five is the most the renderer can place up one mast in bands of their own, and the bench</t>
+          <t xml:space="preserve">height   how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">         fails a mast that asks for more.</t>
+          <t xml:space="preserve">         the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">         STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set,</t>
+          <t xml:space="preserve">berths   the sails she can carry, DECK UPWARD, as category labels separated by spaces.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">         so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
+          <t xml:space="preserve">         LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb    one line a captain reads.</t>
+          <t xml:space="preserve">         Five is the most the renderer can place up one mast in bands of their own, and the bench</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         fails a mast that asks for more.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sails, from data/sails.tsv</t>
+          <t xml:space="preserve">         STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set,</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE SAILS. One row per sail a captain can buy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A sail belongs to ONE category and fits a berth of that category. That is the whole fitting rule.</t>
+          <t xml:space="preserve">blurb    one line a captain reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sails, from data/sails.tsv</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Area is not the category: a topgallant is nearly four times a skysail and both are SSQ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  LSQ  Large square    courses, lower topsails            driving power, low on the mast</t>
+          <t xml:space="preserve">THE SAILS. One row per sail a captain can buy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SSQ  Small square    topgallants, royals, skysails,     light-air lift, high up</t>
+          <t xml:space="preserve">A sail belongs to ONE category and fits a berth of that category. That is the whole fitting rule.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       spritsails, sprit-topsails</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TRI  Headsail        jibs, flying jibs, staysails       set on a stay forward: balance, pointing</t>
+          <t xml:space="preserve">Area is not the category: a topgallant is nearly four times a skysail and both are SSQ.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LAT  Lateen          lateen yards, Bermuda mainsails    triangular canvas driving from a mast</t>
+          <t xml:space="preserve">  LSQ  Large square    courses, lower topsails            driving power, low on the mast</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">  GAF  Gaff            gaff mainsails, spankers,          fore-and-aft drive aft, manoeuvre</t>
+          <t xml:space="preserve">  SSQ  Small square    topgallants, royals, skysails,     light-air lift, high up</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       drivers, trysails, gaff topsails</t>
+          <t xml:space="preserve">                       spritsails, sprit-topsails</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LUG  Lugsail         dipping and standing lug,          the main drive of a lugger</t>
+          <t xml:space="preserve">  TRI  Headsail        jibs, flying jibs, staysails       set on a stay forward: balance, pointing</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       lug topsail</t>
+          <t xml:space="preserve">  LAT  Lateen          lateen yards, Bermuda mainsails    triangular canvas driving from a mast</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STU  Studdingsail    boomed-out extensions             ADDITIVE. Not a berth: see below.</t>
+          <t xml:space="preserve">  GAF  Gaff            gaff mainsails, spankers,          fore-and-aft drive aft, manoeuvre</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                       drivers, trysails, gaff topsails</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">A LATEEN IS NOT A HEADSAIL. Both are triangles and they were one category until the bowsprit became</t>
+          <t xml:space="preserve">  LUG  Lugsail         dipping and standing lug,          the main drive of a lugger</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">a station: the moment a jib had a berth of its own a lateen fitted it and pulled better, so the</t>
+          <t xml:space="preserve">                       lug topsail</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice made itself. They do different work, so they are different categories.</t>
+          <t xml:space="preserve">  STU  Studdingsail    boomed-out extensions             ADDITIVE. Not a berth: see below.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU does not go in a berth. A studdingsail booms out beyond a square sail that is already set and</t>
+          <t xml:space="preserve">A LATEEN IS NOT A HEADSAIL. Both are triangles and they were one category until the bowsprit became</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">its area comes off that sail, so it is an attachment rather than a place in the rig: a square sail</t>
+          <t xml:space="preserve">a station: the moment a jib had a berth of its own a lateen fitted it and pulled better, so the</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">carries at most one, matched by LEVEL, and `npm run catalogue` still refuses a berth that asks for</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one, deliberately, so that a mast cannot pretend to carry studdingsails in a slot.</t>
+          <t xml:space="preserve">choice made itself. They do different work, so they are different categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STU does not go in a berth. A studdingsail booms out beyond a square sail that is already set and</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">id      short camelCase name, unique.</t>
+          <t xml:space="preserve">its area comes off that sail, so it is an attachment rather than a place in the rig: a square sail</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">name    what a captain reads.</t>
+          <t xml:space="preserve">carries at most one, matched by LEVEL, and `npm run catalogue` still refuses a berth that asks for</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind    one of the seven labels above.</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">price   coins.</t>
+          <t xml:space="preserve">one, deliberately, so that a mast cannot pretend to carry studdingsails in a slot.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">drive   what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area</t>
+          <t xml:space="preserve">id      short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">        is where this number starts and the proportions are: course 1.00, lower topsail 0.70,</t>
+          <t xml:space="preserve">name    what a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">        topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it,</t>
+          <t xml:space="preserve">kind    one of the seven labels above.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t xml:space="preserve">        which is why two sails of one area can differ here.</t>
+          <t xml:space="preserve">price   coins.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t xml:space="preserve">        FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80),</t>
+          <t xml:space="preserve">drive   what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">        because its area comes off that sail rather than off a place in the rig.</t>
+          <t xml:space="preserve">        is where this number starts and the proportions are: course 1.00, lower topsail 0.70,</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">hand    what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft</t>
+          <t xml:space="preserve">        topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it,</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">        canvas helps her round, so it is positive.</t>
+          <t xml:space="preserve">        which is why two sails of one area can differ here.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">level   STU only, and blank everywhere else. Which square sail up the mast it booms out from,</t>
+          <t xml:space="preserve">        FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80),</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t xml:space="preserve">        counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it;</t>
+          <t xml:space="preserve">        because its area comes off that sail rather than off a place in the rig.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2 the topgallant. The berth number is not the level, because a driver mast's course sits</t>
+          <t xml:space="preserve">hand    what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t xml:space="preserve">        at berth 1 with a spanker under it.</t>
+          <t xml:space="preserve">        canvas helps her round, so it is positive.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb   one line a captain reads.</t>
+          <t xml:space="preserve">level   STU only, and blank everywhere else. Which square sail up the mast it booms out from,</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it;</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two grades of most of them: the plain one a captain can afford early, and a fine one in heavier</t>
+          <t xml:space="preserve">        2 the topgallant. The berth number is not the level, because a driver mast's course sits</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t xml:space="preserve">cloth that is strictly better and priced for it. Prices are placed against each other and have not</t>
+          <t xml:space="preserve">        at berth 1 with a spanker under it.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">been tuned against what a voyage actually pays.</t>
+          <t xml:space="preserve">blurb   one line a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guns, from data/guns.tsv</t>
+          <t xml:space="preserve">Two grades of most of them: the plain one a captain can afford early, and a fine one in heavier</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cloth that is strictly better and priced for it. Prices are placed against each other and have not</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE GUNS. One row per piece a captain can buy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Guns fit BY THE PIECE up to what the hull bears, and `mount` says which of her counts a gun draws</t>
+          <t xml:space="preserve">been tuned against what a voyage actually pays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns, from data/guns.tsv</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t xml:space="preserve">against. Broadside is counted A SIDE and mirrored, because that is how a volley fires: one</t>
+          <t xml:space="preserve">THE GUNS. One row per piece a captain can buy.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t xml:space="preserve">carriage gun bought is one gun each side and two guns aboard.</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Muskets are not in this table and never will be. Small arms come off the crew she musters, with the</t>
+          <t xml:space="preserve">Guns fit BY THE PIECE up to what the hull bears, and `mount` says which of her counts a gun draws</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t xml:space="preserve">swivels on her rail firing in the same volley, which is `rate()`'s business.</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id      short camelCase name, unique.</t>
+          <t xml:space="preserve">against. Broadside is counted A SIDE and mirrored, because that is how a volley fires: one</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carriage gun bought is one gun each side and two guns aboard.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t xml:space="preserve">name    what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`,</t>
+          <t xml:space="preserve">Muskets are not in this table and never will be. Small arms come off the crew she musters, with the</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t xml:space="preserve">        not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        them is arithmetic she should not have to do in words. It is the game's own rule about</t>
+          <t xml:space="preserve">swivels on her rail firing in the same volley, which is `rate()`'s business.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t xml:space="preserve">        numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
+          <t xml:space="preserve">id      short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
+          <t xml:space="preserve">name    what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`,</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t xml:space="preserve">price   coins.</t>
+          <t xml:space="preserve">        not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
+          <t xml:space="preserve">        them is arithmetic she should not have to do in words. It is the game's own rule about</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
+          <t xml:space="preserve">        numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
+          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t xml:space="preserve">        to leave a port empty.</t>
+          <t xml:space="preserve">price   coins.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
+          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
+          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+          <t xml:space="preserve">        to leave a port empty.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
         <is>
           <t xml:space="preserve">blurb   one line a captain reads.</t>
         </is>
@@ -2626,12 +2654,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recorded only</t>
+          <t xml:space="preserve">Her drawing</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">room and space, feet: from one frame to the next.</t>
+          <t xml:space="preserve">room and space, feet: from one frame to the next. A gunport was framed on it, running a little over one space wide, so this is the size of every port she shows.</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2835,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">her establishment, deck by deck, as guns aboard rather than a side. Gun decks first and lowest deck first, then what she carried on her upper works after a plus: "10" is a cutter's ten on one open deck, "28+8/2" a frigate with a gun deck of 28 and ten more on her quarterdeck and forecastle, "28/28/30+12/2" a first rate. The figures sum to histGuns and every gun deck takes an even number, half of them a side. A GUN DECK AND AN UPPER WORKS ARE NOT THE SAME FITTING, which is the whole reason this column exists. A gun deck is a continuous battery pierced through her side, so its ports run the length of her, under the castles the way a lower deck really did. Her quarterdeck and forecastle guns stood in the open behind a bulwark, with no lidded port to show, and drawn as such they are what leaves a two-decker's waist empty. After the plus, two figures are the quarterdeck and the forecastle in that order, with her waist bare between them. One figure is a battery that ran the whole length of her upper works, which is what a spar-decked heavy frigate had. Write "2/0" rather than "2" for a ship who carried hers aft only.</t>
+          <t xml:space="preserve">her establishment, deck by deck, as guns aboard rather than a side. Gun decks first and lowest deck first, then what she carried on her upper works after a plus: "10" is a cutter's ten on one open deck, "28+8/2" a frigate with a gun deck of 28 and ten more on her quarterdeck and forecastle, "28/28/30+12/2" a first rate. The figures sum to histGuns and every gun deck takes an even number, half of them a side. A GUN DECK AND AN UPPER WORKS ARE NOT THE SAME FITTING, which is the whole reason this column exists. A gun deck is a continuous battery pierced through her side, so its ports run the length of her, under the castles the way a lower deck really did. Her quarterdeck and forecastle guns stood in the open behind a bulwark, with no lidded port to show, and drawn as such they are what leaves a two-decker's waist empty. After the plus, two figures are the quarterdeck and the forecastle in that order, with her waist bare between them. One figure is a battery that ran the whole length of her upper works, which is what a spar-decked heavy frigate had. Write "2/0" rather than "2" for a ship who carried hers aft only. A BOAT IS NOT PIERCED AT ALL. A lidded port is cut through her topside under the deck above it, and a hull with a castle score of 1 has neither, so her whole battery is drawn standing at her rail however this column is written.</t>
         </is>
       </c>
     </row>

--- a/data/ships.xlsx
+++ b/data/ships.xlsx
@@ -512,7 +512,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">masts       where she can step one, "station/size", space separated, bow aft.</t>
+          <t xml:space="preserve">masts       where she can step one, "station/size/family", space separated, bow aft.</t>
         </is>
       </c>
     </row>
@@ -533,1216 +533,1363 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">            The bowsprit takes a SPAR rather than a mast, which is what her headsails hang on.</t>
+          <t xml:space="preserve">            families: the shapes of rig the socket takes, joined with a plus: "main/medium/gaff+spanker".</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit    yes or no. Whether she carries the spar at all.</t>
+          <t xml:space="preserve">                      A mast carries one family in masts.tsv and only a mast of one of these goes in,</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb       one line a captain reads. May be left empty.</t>
+          <t xml:space="preserve">                      so a frigate's fore takes square rig and nothing else however small the mast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      families: square spanker schooner gaff bermuda lateen lug boat headsails spritsail</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">A BLANK IN speed, hand, canvas OR tons IS NOT A DERIVATION. Each falls back to 1, which describes</t>
+          <t xml:space="preserve">            The bowsprit takes a SPAR rather than a mast, which is what her headsails hang on.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">a quick, handy, easily driven ship that can carry nothing, and is right for no class above a boat.</t>
+          <t xml:space="preserve">            A socket that names no family takes any mast of its size, which is how the laid-up rows</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fill them in. Every other gameplay column has to be filled as well.</t>
+          <t xml:space="preserve">            stand; the bench asks every class that sails to say what she takes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bowsprit    yes or no. Whether she carries the spar at all.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE REFERENCE COLUMNS. Everything from `era` rightward is what the class WAS rather than what she</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">does in a fight: no fight reads any of it, `npm run import` writes it to src/shipref.js, and</t>
+          <t xml:space="preserve">blurb       one line a captain reads. May be left empty.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">`hullform.js` is the one reader. The fourteen marked (drawn) are how she is DRAWN, in the menu</t>
+          <t xml:space="preserve">A BLANK IN speed, hand, canvas OR tons IS NOT A DERIVATION. Each falls back to 1, which describes</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">model and at sea. The rest are recorded for whoever comes to refine her form and are read by</t>
+          <t xml:space="preserve">a quick, handy, easily driven ship that can carry nothing, and is right for no class above a boat.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">nothing yet, which is not the same as being free to invent: a wrong figure here is a wrong hull</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the day somebody does read it.</t>
+          <t xml:space="preserve">Fill them in. Every other gameplay column has to be filled as well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THE REFERENCE COLUMNS. Everything from `era` rightward is what the class WAS rather than what she</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lengths are feet and weights are tons. bowFine, tumblehome, deadrise, sheer and castle are 1 to 5</t>
+          <t xml:space="preserve">does in a fight: no fight reads any of it, `npm run import` writes it to src/shipref.js, and</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">judgement scores, 1 for least and 5 for most.</t>
+          <t xml:space="preserve">`hullform.js` is the one reader. The fourteen marked (drawn) are how she is DRAWN, in the menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">model and at sea. The rest are recorded for whoever comes to refine her form and are read by</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">era         the years she was in service, written as a range. Text rather than a number.</t>
+          <t xml:space="preserve">nothing yet, which is not the same as being free to invent: a wrong figure here is a wrong hull</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">region      where she was built and sailed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">role        what she was for.</t>
+          <t xml:space="preserve">the day somebody does read it.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">lod         (drawn) length on deck, feet. With beam, how big she is drawn in both views. Sizes are</t>
+          <t xml:space="preserve">Lengths are feet and weights are tons. bowFine, tumblehome, deadrise, sheer and castle are 1 to 5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">            compressed around the galleon, so twice the length is not twice the ship on screen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lbp         length between perpendiculars, feet. The measured length, shorter than on deck.</t>
+          <t xml:space="preserve">judgement scores, 1 for least and 5 for most.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">beam        (drawn) extreme breadth, feet. Her drawn width, and with her length her collision</t>
+          <t xml:space="preserve">era         the years she was in service, written as a range. Text rather than a number.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ellipse in a fight.</t>
+          <t xml:space="preserve">region      where she was built and sailed.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">draft       how deep she floats, feet.</t>
+          <t xml:space="preserve">role        what she was for.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">depth       depth of hold, feet: keelson to the deck above it.</t>
+          <t xml:space="preserve">lod         (drawn) length on deck, feet. With beam, how big she is drawn in both views. Sizes are</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">freeboard   (drawn) height of side above the water amidships, feet. The depth of side in the model.</t>
+          <t xml:space="preserve">            compressed around the galleon, so twice the length is not twice the ship on screen.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">lb          length to beam, as a ratio. High is long and lean, low is short and beamy.</t>
+          <t xml:space="preserve">lbp         length between perpendiculars, feet. The measured length, shorter than on deck.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd          beam to depth, as a ratio. High is shallow and beamy, low is deep and narrow.</t>
+          <t xml:space="preserve">beam        (drawn) extreme breadth, feet. Her drawn width, and with her length her collision</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">burthen     builder's old measurement tons: what she was rated to carry.</t>
+          <t xml:space="preserve">            ellipse in a fight.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">disp        displacement, tons: what she actually weighs afloat.</t>
+          <t xml:space="preserve">draft       how deep she floats, feet.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowFine     (drawn) how fine her entry is. 5 is a clipper's bow and 1 a carrack's. It narrows her</t>
+          <t xml:space="preserve">depth       depth of hold, feet: keelson to the deck above it.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">            bow and pulls her shoulders aft.</t>
+          <t xml:space="preserve">freeboard   (drawn) height of side above the water amidships, feet. The depth of side in the model.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">tumblehome  (drawn) how far her sides roll inward above the waterline. 5 is a fluyt.</t>
+          <t xml:space="preserve">lb          length to beam, as a ratio. High is long and lean, low is short and beamy.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">deadrise    how sharply her bottom rises from the keel. 1 is a flat floor.</t>
+          <t xml:space="preserve">bd          beam to depth, as a ratio. High is shallow and beamy, low is deep and narrow.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">sheer       (drawn) how much her deck sweeps up towards bow and stern.</t>
+          <t xml:space="preserve">burthen     builder's old measurement tons: what she was rated to carry.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">castle      (drawn) how built up her ends are. 1 is an open boat, 2 raises a quarterdeck, 3 and up</t>
+          <t xml:space="preserve">disp        displacement, tons: what she actually weighs afloat.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">            add a forecastle. It is also what a windowed stern needs before it shows any lights.</t>
+          <t xml:space="preserve">bowFine     (drawn) how fine her entry is. 5 is a clipper's bow and 1 a carrack's. It narrows her</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">stern       (drawn) the shape of her stern, as one of the named types. Scow, Round, Pear,</t>
+          <t xml:space="preserve">            bow and pulls her shoulders aft.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Elliptical, Raking transom, Overhanging and Square each have geometry of their own,</t>
+          <t xml:space="preserve">tumblehome  (drawn) how far her sides roll inward above the waterline. 5 is a fluyt.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">            and any other name draws a plain transom, which is what Transom and Gallery do. A name</t>
+          <t xml:space="preserve">deadrise    how sharply her bottom rises from the keel. 1 is a flat floor.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">            holding "gallery" or "castle" lights her stern windows if her castle is 3 or more.</t>
+          <t xml:space="preserve">sheer       (drawn) how much her deck sweeps up towards bow and stern.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">mastHeight  (drawn) how tall her rig stands, as a multiple of the galleon's. Scales her masts in</t>
+          <t xml:space="preserve">castle      (drawn) how built up her ends are. 1 is an open boat, 2 raises a quarterdeck, 3 and up</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">            both views.</t>
+          <t xml:space="preserve">            add a forecastle. It is also what a windowed stern needs before it shows any lights.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">decks       how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is not a</t>
+          <t xml:space="preserve">stern       (drawn) the shape of her stern, as one of the named types. Scow, Round, Pear,</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">            number. Recorded description now: `battery` says deck by deck where her guns actually</t>
+          <t xml:space="preserve">            Elliptical, Raking transom, Overhanging and Square each have geometry of their own,</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">            stood, and that is what her ports are drawn from.</t>
+          <t xml:space="preserve">            and any other name draws a plain transom, which is what Transom and Gallery do. A name</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">wale        the thickness of her main wale, inches: the heavy belt of timber along her side.</t>
+          <t xml:space="preserve">            holding "gallery" or "castle" lights her stern windows if her castle is 3 or more.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">topside     the thickness of her topside planking, inches.</t>
+          <t xml:space="preserve">mastHeight  (drawn) how tall her rig stands, as a multiple of the galleon's. Scales her masts in</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">roomSpace   (drawn) room and space, feet: from one frame to the next. A gunport was framed on it,</t>
+          <t xml:space="preserve">            both views.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">            running a little over one space wide, so this is the size of every port she shows.</t>
+          <t xml:space="preserve">decks       how many of her decks carry guns: 1, 1-2, 2, 2-3 or 3. Text, because a range is not a</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">species     (drawn) what she was built of, which is also her colour: Oak, Live oak, Teak, Cedar or</t>
+          <t xml:space="preserve">            number. Recorded description now: `battery` says deck by deck where her guns actually</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Pine. Any other name is painted as oak.</t>
+          <t xml:space="preserve">            stood, and that is what her ports are drawn from.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">timber      (drawn) how dense that timber is, oak being 1. Denser timber reads a little darker.</t>
+          <t xml:space="preserve">wale        the thickness of her main wale, inches: the heavy belt of timber along her side.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">crewMin     the fewest hands she could be worked with, as against the battle complement in `crew`.</t>
+          <t xml:space="preserve">topside     the thickness of her topside planking, inches.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">cruise      her everyday speed, knots.</t>
+          <t xml:space="preserve">roomSpace   (drawn) room and space, feet: from one frame to the next. A gunport was framed on it,</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">topSpeed    the best she was ever driven, knots.</t>
+          <t xml:space="preserve">            running a little over one space wide, so this is the size of every port she shows.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">manoeuvre   how handy she was, 0 to 100. The reference's own score, and what `hand` came out of.</t>
+          <t xml:space="preserve">species     (drawn) what she was built of, which is also her colour: Oak, Live oak, Teak, Cedar or</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">histGuns    (drawn) how many guns she really carried, of every sort. Half of them is exactly her</t>
+          <t xml:space="preserve">            Pine. Any other name is painted as oak.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">            `broadside` bearing for every class in the fleet, which is how the ports and the guns</t>
+          <t xml:space="preserve">timber      (drawn) how dense that timber is, oak being 1. Denser timber reads a little darker.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">            that fire out of them agree without the catalogue and the reference ever meeting.</t>
+          <t xml:space="preserve">crewMin     the fewest hands she could be worked with, as against the battle complement in `crew`.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">            `battery` says where those guns stood and has to add up to this.</t>
+          <t xml:space="preserve">cruise      her everyday speed, knots.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery     (drawn) her establishment, deck by deck, as guns aboard rather than a side. Gun decks</t>
+          <t xml:space="preserve">topSpeed    the best she was ever driven, knots.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">            first and lowest deck first, then what she carried on her upper works after a plus:</t>
+          <t xml:space="preserve">manoeuvre   how handy she was, 0 to 100. The reference's own score, and what `hand` came out of.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">            "10" is a cutter's ten on one open deck, "28+8/2" a frigate with a gun deck of 28 and</t>
+          <t xml:space="preserve">histGuns    (drawn) how many guns she really carried, of every sort. Half of them is exactly her</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ten more on her quarterdeck and forecastle, "28/28/30+12/2" a first rate. The figures</t>
+          <t xml:space="preserve">            `broadside` bearing for every class in the fleet, which is how the ports and the guns</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">            sum to histGuns and every gun deck takes an even number, half of them a side.</t>
+          <t xml:space="preserve">            that fire out of them agree without the catalogue and the reference ever meeting.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">            A GUN DECK AND AN UPPER WORKS ARE NOT THE SAME FITTING, which is the whole reason this</t>
+          <t xml:space="preserve">            `battery` says where those guns stood and has to add up to this.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">            column exists. A gun deck is a continuous battery pierced through her side, so its</t>
+          <t xml:space="preserve">battery     (drawn) her establishment, deck by deck, as guns aboard rather than a side. Gun decks</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ports run the length of her, under the castles the way a lower deck really did. Her</t>
+          <t xml:space="preserve">            first and lowest deck first, then what she carried on her upper works after a plus:</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">            quarterdeck and forecastle guns stood in the open behind a bulwark, with no lidded</t>
+          <t xml:space="preserve">            "10" is a cutter's ten on one open deck, "28+8/2" a frigate with a gun deck of 28 and</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">            port to show, and drawn as such they are what leaves a two-decker's waist empty.</t>
+          <t xml:space="preserve">            ten more on her quarterdeck and forecastle, "28/28/30+12/2" a first rate. The figures</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">            After the plus, two figures are the quarterdeck and the forecastle in that order, with</t>
+          <t xml:space="preserve">            sum to histGuns and every gun deck takes an even number, half of them a side.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">            her waist bare between them. One figure is a battery that ran the whole length of her</t>
+          <t xml:space="preserve">            A GUN DECK AND AN UPPER WORKS ARE NOT THE SAME FITTING, which is the whole reason this</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">            upper works, which is what a spar-decked heavy frigate had. Write "2/0" rather than</t>
+          <t xml:space="preserve">            column exists. A gun deck is a continuous battery pierced through her side, so its</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">            "2" for a ship who carried hers aft only.</t>
+          <t xml:space="preserve">            ports run the length of her, under the castles the way a lower deck really did. Her</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">            A BOAT IS NOT PIERCED AT ALL. A lidded port is cut through her topside under the deck</t>
+          <t xml:space="preserve">            quarterdeck and forecastle guns stood in the open behind a bulwark, with no lidded</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">            above it, and a hull with a castle score of 1 has neither, so her whole battery is</t>
+          <t xml:space="preserve">            port to show, and drawn as such they are what leaves a two-decker's waist empty.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">            drawn standing at her rail however this column is written.</t>
+          <t xml:space="preserve">            After the plus, two figures are the quarterdeck and the forecastle in that order, with</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            her waist bare between them. One figure is a battery that ran the whole length of her</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masts, from data/masts.tsv</t>
+          <t xml:space="preserve">            upper works, which is what a spar-decked heavy frigate had. Write "2/0" rather than</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            "2" for a ship who carried hers aft only.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE MASTS. One row per type, and a type is a SHAPE OF RIG, not a size.</t>
+          <t xml:space="preserve">            A BOAT IS NOT PIERCED AT ALL. A lidded port is cut through her topside under the deck</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A mast's berths are fixed the moment it is built and never change. That is the whole point of the</t>
+          <t xml:space="preserve">            above it, and a hull with a castle score of 1 has neither, so her whole battery is</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            drawn standing at her rail however this column is written.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">part: buying a mast is choosing what she will be able to carry, so a mast with one lugsail berth</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">will never carry two square ones however much a captain spends. It is why the fleet wants a type</t>
+          <t xml:space="preserve">Masts, from data/masts.tsv</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">per configuration rather than one mast with a number of slots.</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A TYPE IS NOT TIED TO A STATION. A mast that carries three square sails is that mast wherever she</t>
+          <t xml:space="preserve">THE MASTS. One row per type, and a type is a SHAPE OF RIG, not a size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">steps it, so the fore and main of a brig are one part bought twice rather than two parts. What</t>
+          <t xml:space="preserve">A mast's berths are fixed the moment it is built and never change. That is the whole point of the</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">decides where it can go is the size rung and nothing else.</t>
+          <t xml:space="preserve">part: buying a mast is choosing what she will be able to carry, so a mast with one lugsail berth</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">will never carry two square ones however much a captain spends. It is why the fleet wants a type</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERTHS RUN DECK UPWARD, and a fore-and-aft driving sail sharing the lowest level with a course</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">takes berth 0 with the square canvas above it. A spanker and a course are both set at the deck, one</t>
+          <t xml:space="preserve">per configuration rather than one mast with a number of slots.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">abaft the mast and one on a yard across it, and the model has one sail to a band: putting the</t>
+          <t xml:space="preserve">A TYPE IS NOT TIED TO A STATION. A mast that carries three square sails is that mast wherever she</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">spanker lowest is what keeps a brig's rig reading bottom to top the way she is really rigged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id       short camelCase name, unique.</t>
+          <t xml:space="preserve">steps it, so the fore and main of a brig are one part bought twice rather than two parts. What</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decides where it can go is the size rung and nothing else.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">name     what a captain reads.</t>
+          <t xml:space="preserve">BERTHS RUN DECK UPWARD, and a fore-and-aft driving sail sharing the lowest level with a course</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">price    coins.</t>
+          <t xml:space="preserve">takes berth 0 with the square canvas above it. A spanker and a course are both set at the deck, one</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">size     the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor</t>
+          <t xml:space="preserve">abaft the mast and one on a yard across it, and the model has one sail to a band: putting the</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">         choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spar     yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the</t>
+          <t xml:space="preserve">spanker lowest is what keeps a brig's rig reading bottom to top the way she is really rigged.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">         bowsprit and nowhere else. A spar and a mast are different sorts of thing and are</t>
+          <t xml:space="preserve">id       short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">         matched as such, or a jibboom would be legal as somebody's main mast.</t>
+          <t xml:space="preserve">name     what a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">height   how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts</t>
+          <t xml:space="preserve">price    coins.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">         the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
+          <t xml:space="preserve">size     the SMALLEST socket it fits. A mast also fits any larger socket, which is a legal poor</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">berths   the sails she can carry, DECK UPWARD, as category labels separated by spaces.</t>
+          <t xml:space="preserve">         choice rather than an error: sizes are boat, small, medium, large, heavy.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">         LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail</t>
+          <t xml:space="preserve">spar     yes for a SPAR rather than a mast: a jibboom or a spritsail yard, which goes on the</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Five is the most the renderer can place up one mast in bands of their own, and the bench</t>
+          <t xml:space="preserve">         bowsprit and nowhere else. A spar and a mast are different sorts of thing and are</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">         fails a mast that asks for more.</t>
+          <t xml:space="preserve">         matched as such, or a jibboom would be legal as somebody's main mast.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">         STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set,</t>
+          <t xml:space="preserve">family   the shape of rig this mast is, and a hull's socket says which families it takes, so a</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t xml:space="preserve">         so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
+          <t xml:space="preserve">         lug mast never steps in a frigate and a topgallant mast never steps in a lugger. One</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb    one line a captain reads.</t>
+          <t xml:space="preserve">         family to a mast, matched before the size rung is consulted:</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           square     lower mast up to skysail mast, all square canvas: a ship's fore and main</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sails, from data/sails.tsv</t>
+          <t xml:space="preserve">           spanker    a fore-and-aft driver under square canvas: a ship's mizzen, a cutter's main</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           schooner   gaff sail with a square topsail over it</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE SAILS. One row per sail a captain can buy.</t>
+          <t xml:space="preserve">           gaff       gaff mainsail and gaff topsail</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+          <t xml:space="preserve">           bermuda    one tall triangle</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           lateen     the lateen yard and the lateen mast</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">A sail belongs to ONE category and fits a berth of that category. That is the whole fitting rule.</t>
+          <t xml:space="preserve">           lug        lug mast and lug topmast</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Area is not the category: a topgallant is nearly four times a skysail and both are SSQ.</t>
+          <t xml:space="preserve">           boat       pole and sprit masts, what an open boat steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           headsails  the bowsprit spars that carry jibs and staysails</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LSQ  Large square    courses, lower topsails            driving power, low on the mast</t>
+          <t xml:space="preserve">           spritsail  the old headgear slung under the bowsprit, a carrack's and a galleon's</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SSQ  Small square    topgallants, royals, skysails,     light-air lift, high up</t>
+          <t xml:space="preserve">         Studdingsails boom out from square and schooner rig only; the other families never</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       spritsails, sprit-topsails</t>
+          <t xml:space="preserve">         carried the booms for them.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TRI  Headsail        jibs, flying jibs, staysails       set on a stay forward: balance, pointing</t>
+          <t xml:space="preserve">height   how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LAT  Lateen          lateen yards, Bermuda mainsails    triangular canvas driving from a mast</t>
+          <t xml:space="preserve">         the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">  GAF  Gaff            gaff mainsails, spankers,          fore-and-aft drive aft, manoeuvre</t>
+          <t xml:space="preserve">berths   the sails she can carry, DECK UPWARD, as category labels separated by spaces.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       drivers, trysails, gaff topsails</t>
+          <t xml:space="preserve">         LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LUG  Lugsail         dipping and standing lug,          the main drive of a lugger</t>
+          <t xml:space="preserve">         Five is the most the renderer can place up one mast in bands of their own, and the bench</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">                       lug topsail</t>
+          <t xml:space="preserve">         fails a mast that asks for more.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STU  Studdingsail    boomed-out extensions             ADDITIVE. Not a berth: see below.</t>
+          <t xml:space="preserve">         STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set,</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">A LATEEN IS NOT A HEADSAIL. Both are triangles and they were one category until the bowsprit became</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a station: the moment a jib had a berth of its own a lateen fitted it and pulled better, so the</t>
+          <t xml:space="preserve">blurb    one line a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice made itself. They do different work, so they are different categories.</t>
+          <t xml:space="preserve">Sails, from data/sails.tsv</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU does not go in a berth. A studdingsail booms out beyond a square sail that is already set and</t>
+          <t xml:space="preserve">THE SAILS. One row per sail a captain can buy.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">its area comes off that sail, so it is an attachment rather than a place in the rig: a square sail</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">carries at most one, matched by LEVEL, and `npm run catalogue` still refuses a berth that asks for</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">one, deliberately, so that a mast cannot pretend to carry studdingsails in a slot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id      short camelCase name, unique.</t>
+          <t xml:space="preserve">A sail belongs to ONE category and fits a berth of that category. That is the whole fitting rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Area is not the category: a topgallant is nearly four times a skysail and both are SSQ.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">name    what a captain reads.</t>
+          <t xml:space="preserve">  LSQ  Large square    courses, lower topsails            driving power, low on the mast</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind    one of the seven labels above.</t>
+          <t xml:space="preserve">  SSQ  Small square    topgallants, royals, skysails,     light-air lift, high up</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t xml:space="preserve">price   coins.</t>
+          <t xml:space="preserve">                       spritsails, sprit-topsails</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t xml:space="preserve">drive   what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area</t>
+          <t xml:space="preserve">  TRI  Headsail        jibs, flying jibs, staysails       set on a stay forward: balance, pointing</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">        is where this number starts and the proportions are: course 1.00, lower topsail 0.70,</t>
+          <t xml:space="preserve">  LAT  Lateen          lateen yards, Bermuda mainsails    triangular canvas driving from a mast</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">        topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it,</t>
+          <t xml:space="preserve">  GAF  Gaff            gaff mainsails, spankers,          fore-and-aft drive aft, manoeuvre</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">        which is why two sails of one area can differ here.</t>
+          <t xml:space="preserve">                       drivers, trysails, gaff topsails</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">        FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80),</t>
+          <t xml:space="preserve">  LUG  Lugsail         dipping and standing lug,          the main drive of a lugger</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t xml:space="preserve">        because its area comes off that sail rather than off a place in the rig.</t>
+          <t xml:space="preserve">                       lug topsail</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">hand    what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        canvas helps her round, so it is positive.</t>
+          <t xml:space="preserve">  STU  Studdingsail    boomed-out extensions             ADDITIVE. Not a berth: see below.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">level   STU only, and blank everywhere else. Which square sail up the mast it booms out from,</t>
+          <t xml:space="preserve">A LATEEN IS NOT A HEADSAIL. Both are triangles and they were one category until the bowsprit became</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t xml:space="preserve">        counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it;</t>
+          <t xml:space="preserve">a station: the moment a jib had a berth of its own a lateen fitted it and pulled better, so the</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2 the topgallant. The berth number is not the level, because a driver mast's course sits</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        at berth 1 with a spanker under it.</t>
+          <t xml:space="preserve">choice made itself. They do different work, so they are different categories.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb   one line a captain reads.</t>
+          <t xml:space="preserve">STU does not go in a berth. A studdingsail booms out beyond a square sail that is already set and</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its area comes off that sail, so it is an attachment rather than a place in the rig: a square sail</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two grades of most of them: the plain one a captain can afford early, and a fine one in heavier</t>
+          <t xml:space="preserve">carries at most one, matched by LEVEL, and `npm run catalogue` still refuses a berth that asks for</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">cloth that is strictly better and priced for it. Prices are placed against each other and have not</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">been tuned against what a voyage actually pays.</t>
+          <t xml:space="preserve">one, deliberately, so that a mast cannot pretend to carry studdingsails in a slot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id      short camelCase name, unique.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guns, from data/guns.tsv</t>
+          <t xml:space="preserve">name    what a captain reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind    one of the seven labels above.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t xml:space="preserve">THE GUNS. One row per piece a captain can buy.</t>
+          <t xml:space="preserve">price   coins.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
+          <t xml:space="preserve">drive   what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        is where this number starts and the proportions are: course 1.00, lower topsail 0.70,</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guns fit BY THE PIECE up to what the hull bears, and `mount` says which of her counts a gun draws</t>
+          <t xml:space="preserve">        topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it,</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t xml:space="preserve">against. Broadside is counted A SIDE and mirrored, because that is how a volley fires: one</t>
+          <t xml:space="preserve">        which is why two sails of one area can differ here.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t xml:space="preserve">carriage gun bought is one gun each side and two guns aboard.</t>
+          <t xml:space="preserve">        FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80),</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        because its area comes off that sail rather than off a place in the rig.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Muskets are not in this table and never will be. Small arms come off the crew she musters, with the</t>
+          <t xml:space="preserve">hand    what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t xml:space="preserve">swivels on her rail firing in the same volley, which is `rate()`'s business.</t>
+          <t xml:space="preserve">        canvas helps her round, so it is positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">level   STU only, and blank everywhere else. Which square sail up the mast it booms out from,</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t xml:space="preserve">id      short camelCase name, unique.</t>
+          <t xml:space="preserve">        counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it;</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t xml:space="preserve">name    what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`,</t>
+          <t xml:space="preserve">        2 the topgallant. The berth number is not the level, because a driver mast's course sits</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t xml:space="preserve">        not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing</t>
+          <t xml:space="preserve">        at berth 1 with a spanker under it.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t xml:space="preserve">        them is arithmetic she should not have to do in words. It is the game's own rule about</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
+          <t xml:space="preserve">blurb   one line a captain reads.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
+          <t xml:space="preserve">Two grades of most of them: the plain one a captain can afford early, and a fine one in heavier</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t xml:space="preserve">price   coins.</t>
+          <t xml:space="preserve">cloth that is strictly better and priced for it. Prices are placed against each other and have not</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
+          <t xml:space="preserve">been tuned against what a voyage actually pays.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        to leave a port empty.</t>
+          <t xml:space="preserve">Guns, from data/guns.tsv</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
+          <t xml:space="preserve">THE GUNS. One row per piece a captain can buy.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+          <t xml:space="preserve">Edit here, then: npm run import &amp;&amp; npm run catalogue</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+          <t xml:space="preserve">Guns fit BY THE PIECE up to what the hull bears, and `mount` says which of her counts a gun draws</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">against. Broadside is counted A SIDE and mirrored, because that is how a volley fires: one</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carriage gun bought is one gun each side and two guns aboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Muskets are not in this table and never will be. Small arms come off the crew she musters, with the</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">swivels on her rail firing in the same volley, which is `rate()`'s business.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id      short camelCase name, unique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name    what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`,</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        them is arithmetic she should not have to do in words. It is the game's own rule about</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mount   broadside, bow or swivel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price   coins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damage  what one ball takes off a hull.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reload  seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weight  what she carries for it. Enough of it takes the edge off her handling, which is the reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        to leave a port empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">group   swivels only, and blank everywhere else. How true one throws, as a share of a musket's own</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        never adds a ball to the volley; what quality buys is that the volley hits harder and lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        closer to where the bow points, and this is the second half of that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
         <is>
           <t xml:space="preserve">blurb   one line a captain reads.</t>
         </is>
@@ -2087,7 +2234,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">where she can step one, "station/size", space separated, bow aft. stations: bowsprit fore main mizzen bonaventure sizes:    boat small medium large heavy The bowsprit takes a SPAR rather than a mast, which is what her headsails hang on.</t>
+          <t xml:space="preserve">where she can step one, "station/size/family", space separated, bow aft. stations: bowsprit fore main mizzen bonaventure sizes:    boat small medium large heavy families: the shapes of rig the socket takes, joined with a plus: "main/medium/gaff+spanker". A mast carries one family in masts.tsv and only a mast of one of these goes in, so a frigate's fore takes square rig and nothing else however small the mast. families: square spanker schooner gaff bermuda lateen lug boat headsails spritsail The bowsprit takes a SPAR rather than a mast, which is what her headsails hang on. A socket that names no family takes any mast of its size, which is how the laid-up rows stand; the bench asks every class that sails to say what she takes.</t>
         </is>
       </c>
     </row>
@@ -2957,7 +3104,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">height</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2967,7 +3114,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
+          <t xml:space="preserve">the shape of rig this mast is, and a hull's socket says which families it takes, so a lug mast never steps in a frigate and a topgallant mast never steps in a lugger. One family to a mast, matched before the size rung is consulted: square     lower mast up to skysail mast, all square canvas: a ship's fore and main spanker    a fore-and-aft driver under square canvas: a ship's mizzen, a cutter's main schooner   gaff sail with a square topsail over it gaff       gaff mainsail and gaff topsail bermuda    one tall triangle lateen     the lateen yard and the lateen mast lug        lug mast and lug topmast boat       pole and sprit masts, what an open boat steps headsails  the bowsprit spars that carry jibs and staysails spritsail  the old headgear slung under the bowsprit, a carrack's and a galleon's Studdingsails boom out from square and schooner rig only; the other families never carried the booms for them.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +3126,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">berths</t>
+          <t xml:space="preserve">height</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2989,7 +3136,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">the sails she can carry, DECK UPWARD, as category labels separated by spaces. LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail Five is the most the renderer can place up one mast in bands of their own, and the bench fails a mast that asks for more. STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set, so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
+          <t xml:space="preserve">how tall she stands as a share of a full mast at her station, 0 to 1. The renderer cuts the pole down to the canvas actually bent on it, so this is an upper bound, not a look.</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3148,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb</t>
+          <t xml:space="preserve">berths</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3011,19 +3158,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">one line a captain reads.</t>
+          <t xml:space="preserve">the sails she can carry, DECK UPWARD, as category labels separated by spaces. LSQ large square   SSQ small square   TRI headsail   LAT lateen   GAF gaff   LUG lugsail Five is the most the renderer can place up one mast in bands of their own, and the bench fails a mast that asks for more. STU is a studdingsail and is NOT a berth. It booms out beyond a square sail already set, so it attaches to a sail rather than filling a place in the rig, and the bench refuses it.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sails</t>
+          <t xml:space="preserve">Masts</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">blurb</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3033,7 +3180,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">short camelCase name, unique.</t>
+          <t xml:space="preserve">one line a captain reads.</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3192,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3055,7 +3202,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">what a captain reads.</t>
+          <t xml:space="preserve">short camelCase name, unique.</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3214,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3077,7 +3224,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of the seven labels above.</t>
+          <t xml:space="preserve">what a captain reads.</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3236,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3099,7 +3246,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">coins.</t>
+          <t xml:space="preserve">one of the seven labels above.</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3258,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">drive</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3121,7 +3268,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area is where this number starts and the proportions are: course 1.00, lower topsail 0.70, topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it, which is why two sails of one area can differ here. FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80), because its area comes off that sail rather than off a place in the rig.</t>
+          <t xml:space="preserve">coins.</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3280,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">hand</t>
+          <t xml:space="preserve">drive</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3143,7 +3290,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft canvas helps her round, so it is positive.</t>
+          <t xml:space="preserve">what she pulls, as a share of a course's, which is why a course is exactly 1. Physical area is where this number starts and the proportions are: course 1.00, lower topsail 0.70, topgallant 0.40, royal 0.22, skysail 0.12. Better cloth holds its shape and adds to it, which is why two sails of one area can differ here. FOR A STUDDINGSAIL ONLY, drive is a share of the sail it booms out from (0.50 to 0.80), because its area comes off that sail rather than off a place in the rig.</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3302,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">level</t>
+          <t xml:space="preserve">hand</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3165,7 +3312,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU only, and blank everywhere else. Which square sail up the mast it booms out from, counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it; 2 the topgallant. The berth number is not the level, because a driver mast's course sits at berth 1 with a spanker under it.</t>
+          <t xml:space="preserve">what it does to her helm. Square canvas stiffens her, so it is negative; fore-and-aft canvas helps her round, so it is positive.</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3324,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb</t>
+          <t xml:space="preserve">level</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3187,19 +3334,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">one line a captain reads.</t>
+          <t xml:space="preserve">STU only, and blank everywhere else. Which square sail up the mast it booms out from, counting square canvas from the deck: 0 is the lowest, a course; 1 the topsail over it; 2 the topgallant. The berth number is not the level, because a driver mast's course sits at berth 1 with a spanker under it.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guns</t>
+          <t xml:space="preserve">Sails</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">blurb</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3209,7 +3356,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">short camelCase name, unique.</t>
+          <t xml:space="preserve">one line a captain reads.</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3368,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3231,7 +3378,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`, not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing them is arithmetic she should not have to do in words. It is the game's own rule about numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
+          <t xml:space="preserve">short camelCase name, unique.</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3390,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">mount</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3253,7 +3400,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">broadside, bow or swivel.</t>
+          <t xml:space="preserve">what a captain reads. A GUN IS NAMED BY THE WEIGHT OF HER BALL, IN NUMERALS: `32-pounder`, not `Thirty two pounder`. A captain reads this list to compare ten pieces, and comparing them is arithmetic she should not have to do in words. It is the game's own rule about numerals, and a shelf of guns is where the cost of breaking it shows worst.</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3412,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">mount</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3275,7 +3422,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">coins.</t>
+          <t xml:space="preserve">broadside, bow or swivel.</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3434,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">damage</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3297,7 +3444,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">what one ball takes off a hull.</t>
+          <t xml:space="preserve">coins.</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3456,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">reload</t>
+          <t xml:space="preserve">damage</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3319,7 +3466,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
+          <t xml:space="preserve">what one ball takes off a hull.</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3478,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight</t>
+          <t xml:space="preserve">reload</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3341,7 +3488,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">what she carries for it. Enough of it takes the edge off her handling, which is the reason to leave a port empty.</t>
+          <t xml:space="preserve">seconds between rounds. A mixed battery serves at the pace of its slowest piece.</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3500,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">group</t>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3363,7 +3510,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">swivels only, and blank everywhere else. How true one throws, as a share of a musket's own scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel never adds a ball to the volley; what quality buys is that the volley hits harder and lands closer to where the bow points, and this is the second half of that.</t>
+          <t xml:space="preserve">what she carries for it. Enough of it takes the edge off her handling, which is the reason to leave a port empty.</t>
         </is>
       </c>
     </row>
@@ -3375,15 +3522,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t xml:space="preserve">group</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fight</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">swivels only, and blank everywhere else. How true one throws, as a share of a musket's own scatter: 1 is no better than the hands beside it, and smaller is tighter. A better swivel never adds a ball to the volley; what quality buys is that the volley hits harder and lands closer to where the bow points, and this is the second half of that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guns</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t xml:space="preserve">blurb</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t xml:space="preserve">The fight</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t xml:space="preserve">one line a captain reads.</t>
         </is>
@@ -3736,7 +3905,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">main/small</t>
+          <t xml:space="preserve">main/small/boat+lug+lateen</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -3904,7 +4073,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/small main/medium</t>
+          <t xml:space="preserve">bowsprit/small/headsails main/medium/bermuda</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -4072,7 +4241,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/small main/medium</t>
+          <t xml:space="preserve">bowsprit/small/headsails main/medium/gaff+spanker</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -4240,7 +4409,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/small main/medium</t>
+          <t xml:space="preserve">bowsprit/small/headsails main/medium/gaff+spanker</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -4408,7 +4577,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/small fore/medium main/medium</t>
+          <t xml:space="preserve">bowsprit/small/headsails fore/medium/schooner+gaff main/medium/schooner+gaff</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -4576,7 +4745,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/small fore/medium main/medium</t>
+          <t xml:space="preserve">bowsprit/small/headsails fore/medium/square main/medium/gaff+schooner+spanker</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -4744,7 +4913,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/small fore/medium main/medium</t>
+          <t xml:space="preserve">bowsprit/small/headsails fore/medium/lateen main/medium/lateen</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -4912,7 +5081,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium</t>
+          <t xml:space="preserve">bowsprit/medium/headsails fore/large/square main/large/square mizzen/medium/spanker</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -5080,7 +5249,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium</t>
+          <t xml:space="preserve">bowsprit/medium/headsails fore/large/square main/large/square mizzen/medium/spanker</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -5250,7 +5419,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/medium fore/large main/large mizzen/medium</t>
+          <t xml:space="preserve">bowsprit/medium/headsails fore/large/lateen main/large/lateen mizzen/medium/lateen</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5418,7 +5587,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/large fore/heavy main/heavy mizzen/large</t>
+          <t xml:space="preserve">bowsprit/large/headsails fore/heavy/square main/heavy/square mizzen/large/spanker</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5588,7 +5757,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/large fore/heavy main/heavy mizzen/large</t>
+          <t xml:space="preserve">bowsprit/large/headsails fore/heavy/square main/heavy/square mizzen/large/spanker</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5758,7 +5927,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/large fore/heavy main/heavy mizzen/large</t>
+          <t xml:space="preserve">bowsprit/large/headsails fore/heavy/square main/heavy/square mizzen/large/spanker+lateen</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -5928,7 +6097,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/large fore/heavy main/heavy mizzen/large</t>
+          <t xml:space="preserve">bowsprit/large/headsails fore/heavy/square main/heavy/square mizzen/large/spanker</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6098,7 +6267,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/large fore/heavy main/heavy mizzen/large</t>
+          <t xml:space="preserve">bowsprit/large/headsails fore/heavy/square main/heavy/square mizzen/large/spanker</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -6268,7 +6437,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bowsprit/large fore/heavy main/heavy mizzen/large</t>
+          <t xml:space="preserve">bowsprit/large/headsails fore/heavy/square main/heavy/square mizzen/large/spanker</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -12425,9 +12594,10 @@
     <col min="3" max="3" width="7.00" customWidth="1"/>
     <col min="4" max="4" width="8.00" customWidth="1"/>
     <col min="5" max="5" width="6.00" customWidth="1"/>
-    <col min="6" max="6" width="8.00" customWidth="1"/>
-    <col min="7" max="7" width="21.00" customWidth="1"/>
-    <col min="8" max="8" width="46.00" customWidth="1"/>
+    <col min="6" max="6" width="11.00" customWidth="1"/>
+    <col min="7" max="7" width="8.00" customWidth="1"/>
+    <col min="8" max="8" width="21.00" customWidth="1"/>
+    <col min="9" max="9" width="46.00" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12458,15 +12628,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">family</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">height</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">berths</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">blurb</t>
         </is>
@@ -12496,17 +12671,22 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boat</t>
+        </is>
+      </c>
+      <c r="G2">
         <v>0.6</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">LSQ</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A single spar and a single square sail. Everything starts here.</t>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A single spar and a single square sail. The plainest rig a boat can carry.</t>
         </is>
       </c>
     </row>
@@ -12534,15 +12714,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boat</t>
+        </is>
+      </c>
+      <c r="G3">
         <v>0.56</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">GAF</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">A sprit across one four sided sail. What a boat carries, and what one hand can manage.</t>
         </is>
@@ -12572,15 +12757,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lug</t>
+        </is>
+      </c>
+      <c r="G4">
         <v>0.58</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">LUG</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">A short mast for one lugsail. Cheap, quick, and the whole rig of a fishing boat.</t>
         </is>
@@ -12610,15 +12800,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lateen</t>
+        </is>
+      </c>
+      <c r="G5">
         <v>0.76</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">LAT</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">A long raking yard and one triangular sail. The Mediterranean answer to everything.</t>
         </is>
@@ -12648,15 +12843,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bermuda</t>
+        </is>
+      </c>
+      <c r="G6">
         <v>0.86</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">LAT</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">Tall and bare, cut for one big triangular sail. Points closer to the wind than square canvas.</t>
         </is>
@@ -12686,15 +12886,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gaff</t>
+        </is>
+      </c>
+      <c r="G7">
         <v>0.72</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">GAF GAF</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">A gaff mainsail and a topsail in the space above it. The working rig of a smack.</t>
         </is>
@@ -12724,15 +12929,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lug</t>
+        </is>
+      </c>
+      <c r="G8">
         <v>0.74</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">LUG LUG</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">A standing lug with a second small one over it, for a lugger that means to outrun somebody.</t>
         </is>
@@ -12762,15 +12972,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">square</t>
+        </is>
+      </c>
+      <c r="G9">
         <v>0.68</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">LSQ</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">One heavy square sail on a stout pole. The plain way to move a big hull.</t>
         </is>
@@ -12800,15 +13015,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lateen</t>
+        </is>
+      </c>
+      <c r="G10">
         <v>0.78</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">LAT SSQ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">A long raking yard for the after station, with room for a small square sail above it.</t>
         </is>
@@ -12838,15 +13058,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">square</t>
+        </is>
+      </c>
+      <c r="G11">
         <v>0.86</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">LSQ LSQ</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">A lower mast with a second spar fidded above it: a course below, a topsail over.</t>
         </is>
@@ -12876,15 +13101,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schooner</t>
+        </is>
+      </c>
+      <c r="G12">
         <v>0.84</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">GAF LSQ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">A gaff sail low and a square topsail over it. Weatherly, and quick in stays.</t>
         </is>
@@ -12914,15 +13144,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spanker</t>
+        </is>
+      </c>
+      <c r="G13">
         <v>0.9</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">GAF LSQ SSQ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">A fore-and-aft driver at the deck with square canvas over it. What a cutter carries, and what a ship steers on aft.</t>
         </is>
@@ -12952,15 +13187,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">square</t>
+        </is>
+      </c>
+      <c r="G14">
         <v>0.94</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve">LSQ LSQ SSQ</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">Three spars, and the highest sail is a small one. Every hand aboard is up there in a blow.</t>
         </is>
@@ -12990,15 +13230,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spanker</t>
+        </is>
+      </c>
+      <c r="G15">
         <v>0.96</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">GAF LSQ SSQ SSQ</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">A driver below and three square sails over it, the last a royal. A frigate's mizzen.</t>
         </is>
@@ -13028,15 +13273,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spanker</t>
+        </is>
+      </c>
+      <c r="G16">
         <v>0.97</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">GAF LSQ LSQ SSQ</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">Spanker, course, topsail and topgallant. The after mast of anything that fights in a line.</t>
         </is>
@@ -13066,15 +13316,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">square</t>
+        </is>
+      </c>
+      <c r="G17">
         <v>0.98</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">LSQ LSQ SSQ SSQ</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">Four yards crossed and a royal above the topgallant. A press of canvas for a ship that can carry it.</t>
         </is>
@@ -13104,15 +13359,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">square</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">LSQ LSQ SSQ SSQ SSQ</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">Five yards, the last of them a handkerchief in the clouds. Only the tallest hulls can step one.</t>
         </is>
@@ -13142,15 +13402,20 @@
           <t xml:space="preserve">no</t>
         </is>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spanker</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">GAF LSQ LSQ SSQ SSQ</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">Everything a mast can carry, with a spanker under it. There is nothing above this one.</t>
         </is>
@@ -13180,15 +13445,20 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">headsails</t>
+        </is>
+      </c>
+      <c r="G20">
         <v>0.55</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">TRI</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">The spar over her stem with one staysail hanked to it. Enough to balance her helm.</t>
         </is>
@@ -13218,15 +13488,20 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">headsails</t>
+        </is>
+      </c>
+      <c r="G21">
         <v>0.8</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">TRI TRI</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">Run out beyond the bowsprit, for a jib outside the staysail.</t>
         </is>
@@ -13256,15 +13531,20 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">headsails</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">TRI TRI TRI</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">The whole head of her: staysail, jib, and a flying jib at the boom end.</t>
         </is>
@@ -13294,15 +13574,20 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spritsail</t>
+        </is>
+      </c>
+      <c r="G23">
         <v>0.7</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">SSQ</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">A yard slung under the bowsprit, the way a carrack carried hers.</t>
         </is>
@@ -13332,15 +13617,20 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spritsail</t>
+        </is>
+      </c>
+      <c r="G24">
         <v>0.95</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">SSQ SSQ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">A spritsail and a sprit-topsail above it. Old fashioned, and it pulls her head round.</t>
         </is>
